--- a/output/2025-09-29.xlsx
+++ b/output/2025-09-29.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.85</v>
+        <v>3.34</v>
       </c>
       <c r="F14" t="n">
-        <v>12.27</v>
+        <v>13.19</v>
       </c>
       <c r="G14" t="n">
-        <v>95</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>78</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>102.37</v>
+        <v>174.39</v>
       </c>
       <c r="K14" t="n">
-        <v>-25.19</v>
+        <v>63.15</v>
       </c>
       <c r="L14" t="n">
-        <v>105.43</v>
+        <v>185.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:16:18</t>
+          <t>07:14:44</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="F15" t="n">
-        <v>13.21</v>
+        <v>12.63</v>
       </c>
       <c r="G15" t="n">
-        <v>77.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>82.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-73.84</v>
+        <v>119.05</v>
       </c>
       <c r="K15" t="n">
-        <v>17.45</v>
+        <v>-22.91</v>
       </c>
       <c r="L15" t="n">
-        <v>75.87</v>
+        <v>121.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:17:10</t>
+          <t>07:17:05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.31</v>
+        <v>4.21</v>
       </c>
       <c r="F16" t="n">
-        <v>13.51</v>
+        <v>12.09</v>
       </c>
       <c r="G16" t="n">
-        <v>77.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>79.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>12.32</v>
+        <v>-264.08</v>
       </c>
       <c r="K16" t="n">
-        <v>-35.05</v>
+        <v>73.37</v>
       </c>
       <c r="L16" t="n">
-        <v>37.15</v>
+        <v>274.09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:21:59</t>
+          <t>07:20:28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.51</v>
+        <v>4.06</v>
       </c>
       <c r="F17" t="n">
-        <v>13.41</v>
+        <v>12.79</v>
       </c>
       <c r="G17" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="H17" t="n">
-        <v>82.8</v>
+        <v>79.3</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>126.36</v>
+        <v>148.67</v>
       </c>
       <c r="K17" t="n">
-        <v>60.76</v>
+        <v>200.37</v>
       </c>
       <c r="L17" t="n">
-        <v>140.21</v>
+        <v>249.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:22:46</t>
+          <t>07:21:47</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.65</v>
+        <v>3.81</v>
       </c>
       <c r="F18" t="n">
-        <v>13.12</v>
+        <v>13.07</v>
       </c>
       <c r="G18" t="n">
-        <v>86.5</v>
+        <v>96.8</v>
       </c>
       <c r="H18" t="n">
-        <v>84.2</v>
+        <v>81.7</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>73.15000000000001</v>
+        <v>-404.2</v>
       </c>
       <c r="K18" t="n">
-        <v>112.69</v>
+        <v>-209.93</v>
       </c>
       <c r="L18" t="n">
-        <v>134.35</v>
+        <v>455.46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:24:58</t>
+          <t>07:22:26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.66</v>
+        <v>4.6</v>
       </c>
       <c r="F19" t="n">
-        <v>13.07</v>
+        <v>12.39</v>
       </c>
       <c r="G19" t="n">
-        <v>85.8</v>
+        <v>94.5</v>
       </c>
       <c r="H19" t="n">
-        <v>81.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J19" t="n">
-        <v>46.54</v>
+        <v>310.17</v>
       </c>
       <c r="K19" t="n">
-        <v>-173.43</v>
+        <v>264.73</v>
       </c>
       <c r="L19" t="n">
-        <v>179.57</v>
+        <v>407.78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:30:16</t>
+          <t>07:27:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.87</v>
+        <v>4.16</v>
       </c>
       <c r="F20" t="n">
-        <v>12.38</v>
+        <v>12.6</v>
       </c>
       <c r="G20" t="n">
-        <v>85.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>84.7</v>
+        <v>85.5</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-172.32</v>
+        <v>-199.92</v>
       </c>
       <c r="K20" t="n">
-        <v>294.18</v>
+        <v>-180.13</v>
       </c>
       <c r="L20" t="n">
-        <v>340.94</v>
+        <v>269.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:32:28</t>
+          <t>07:28:57</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>5.05</v>
+        <v>3.87</v>
       </c>
       <c r="F21" t="n">
-        <v>12.15</v>
+        <v>12.65</v>
       </c>
       <c r="G21" t="n">
-        <v>88</v>
+        <v>67.8</v>
       </c>
       <c r="H21" t="n">
-        <v>84.5</v>
+        <v>80.8</v>
       </c>
       <c r="I21" t="n">
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>377.01</v>
+        <v>74.12</v>
       </c>
       <c r="K21" t="n">
-        <v>118.08</v>
+        <v>-172.4</v>
       </c>
       <c r="L21" t="n">
-        <v>395.07</v>
+        <v>187.66</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:33:50</t>
+          <t>07:30:21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>5.14</v>
+        <v>3.9</v>
       </c>
       <c r="F22" t="n">
-        <v>12.52</v>
+        <v>12.1</v>
       </c>
       <c r="G22" t="n">
-        <v>95.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="H22" t="n">
-        <v>76.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>257.95</v>
+        <v>-183.93</v>
       </c>
       <c r="K22" t="n">
-        <v>111.94</v>
+        <v>91.47</v>
       </c>
       <c r="L22" t="n">
-        <v>281.2</v>
+        <v>205.42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:37:58</t>
+          <t>07:34:23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.44</v>
+        <v>4.48</v>
       </c>
       <c r="F23" t="n">
-        <v>13.16</v>
+        <v>12.43</v>
       </c>
       <c r="G23" t="n">
-        <v>88.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>81</v>
+        <v>90.5</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>190.45</v>
+        <v>-241.91</v>
       </c>
       <c r="K23" t="n">
-        <v>-86.77</v>
+        <v>149.61</v>
       </c>
       <c r="L23" t="n">
-        <v>209.29</v>
+        <v>284.43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:39:05</t>
+          <t>07:35:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.11</v>
+        <v>4.48</v>
       </c>
       <c r="F24" t="n">
-        <v>12.18</v>
+        <v>11.96</v>
       </c>
       <c r="G24" t="n">
-        <v>98</v>
+        <v>97.2</v>
       </c>
       <c r="H24" t="n">
-        <v>88.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>261.16</v>
+        <v>634.9400000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-47.87</v>
+        <v>-624.49</v>
       </c>
       <c r="L24" t="n">
-        <v>265.52</v>
+        <v>890.58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:41:26</t>
+          <t>07:36:42</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.53</v>
+        <v>4.24</v>
       </c>
       <c r="F25" t="n">
-        <v>13.2</v>
+        <v>12.87</v>
       </c>
       <c r="G25" t="n">
-        <v>97.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="H25" t="n">
-        <v>89.2</v>
+        <v>80.8</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>132.07</v>
+        <v>35.29</v>
       </c>
       <c r="K25" t="n">
-        <v>-175.05</v>
+        <v>-169.61</v>
       </c>
       <c r="L25" t="n">
-        <v>219.29</v>
+        <v>173.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:46:24</t>
+          <t>07:42:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.73</v>
+        <v>4.35</v>
       </c>
       <c r="F26" t="n">
-        <v>12.45</v>
+        <v>12.32</v>
       </c>
       <c r="G26" t="n">
-        <v>92.7</v>
+        <v>85.3</v>
       </c>
       <c r="H26" t="n">
-        <v>83.5</v>
+        <v>77.2</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>705.77</v>
+        <v>-710.67</v>
       </c>
       <c r="K26" t="n">
-        <v>595.38</v>
+        <v>-204.2</v>
       </c>
       <c r="L26" t="n">
-        <v>923.36</v>
+        <v>739.42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:47:59</t>
+          <t>07:43:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.43</v>
+        <v>4.91</v>
       </c>
       <c r="F27" t="n">
-        <v>13.03</v>
+        <v>12.84</v>
       </c>
       <c r="G27" t="n">
-        <v>89.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>88.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>143.84</v>
+        <v>755.83</v>
       </c>
       <c r="K27" t="n">
-        <v>19.29</v>
+        <v>147.59</v>
       </c>
       <c r="L27" t="n">
-        <v>145.12</v>
+        <v>770.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:49:01</t>
+          <t>07:44:32</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.42</v>
+        <v>4.45</v>
       </c>
       <c r="F28" t="n">
-        <v>12.9</v>
+        <v>13.15</v>
       </c>
       <c r="G28" t="n">
-        <v>76.09999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>83.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-11.43</v>
+        <v>-277.51</v>
       </c>
       <c r="K28" t="n">
-        <v>186.87</v>
+        <v>812.52</v>
       </c>
       <c r="L28" t="n">
-        <v>187.22</v>
+        <v>858.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:59:34</t>
+          <t>07:52:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.96</v>
+        <v>4.53</v>
       </c>
       <c r="F29" t="n">
-        <v>12.85</v>
+        <v>12.44</v>
       </c>
       <c r="G29" t="n">
-        <v>92.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>84.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I29" t="n">
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>78.81</v>
+        <v>72.94</v>
       </c>
       <c r="K29" t="n">
-        <v>-123.19</v>
+        <v>-108.71</v>
       </c>
       <c r="L29" t="n">
-        <v>146.24</v>
+        <v>130.91</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:01:09</t>
+          <t>07:54:56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.86</v>
+        <v>5.37</v>
       </c>
       <c r="F30" t="n">
-        <v>12.4</v>
+        <v>12.35</v>
       </c>
       <c r="G30" t="n">
-        <v>101.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>79.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-115.46</v>
+        <v>62.21</v>
       </c>
       <c r="K30" t="n">
-        <v>-121.87</v>
+        <v>-283.34</v>
       </c>
       <c r="L30" t="n">
-        <v>167.88</v>
+        <v>290.09</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:03:05</t>
+          <t>07:57:03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.72</v>
+        <v>4.46</v>
       </c>
       <c r="F31" t="n">
-        <v>13.14</v>
+        <v>12.9</v>
       </c>
       <c r="G31" t="n">
-        <v>73</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>87.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-142.69</v>
+        <v>259.43</v>
       </c>
       <c r="K31" t="n">
-        <v>-207.39</v>
+        <v>-147.27</v>
       </c>
       <c r="L31" t="n">
-        <v>251.74</v>
+        <v>298.32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:07:01</t>
+          <t>08:03:32</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.45</v>
+        <v>4.99</v>
       </c>
       <c r="F32" t="n">
-        <v>11.92</v>
+        <v>13.51</v>
       </c>
       <c r="G32" t="n">
-        <v>71.09999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="H32" t="n">
-        <v>81</v>
+        <v>80.7</v>
       </c>
       <c r="I32" t="n">
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>296.69</v>
+        <v>97.89</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.85</v>
+        <v>15.46</v>
       </c>
       <c r="L32" t="n">
-        <v>296.71</v>
+        <v>99.11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:08:28</t>
+          <t>08:05:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.75</v>
+        <v>4.93</v>
       </c>
       <c r="F33" t="n">
-        <v>13.05</v>
+        <v>12.61</v>
       </c>
       <c r="G33" t="n">
-        <v>92.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="H33" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
       <c r="I33" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>74.53</v>
+        <v>-366.15</v>
       </c>
       <c r="K33" t="n">
-        <v>278.24</v>
+        <v>-273.65</v>
       </c>
       <c r="L33" t="n">
-        <v>288.05</v>
+        <v>457.11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:09:42</t>
+          <t>08:07:06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.34</v>
+        <v>4.39</v>
       </c>
       <c r="F34" t="n">
-        <v>11.97</v>
+        <v>12.86</v>
       </c>
       <c r="G34" t="n">
-        <v>83.3</v>
+        <v>78.5</v>
       </c>
       <c r="H34" t="n">
-        <v>78.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-29.61</v>
+        <v>304</v>
       </c>
       <c r="K34" t="n">
-        <v>-37.21</v>
+        <v>163.76</v>
       </c>
       <c r="L34" t="n">
-        <v>47.55</v>
+        <v>345.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:14:23</t>
+          <t>08:12:12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.57</v>
+        <v>4.23</v>
       </c>
       <c r="F35" t="n">
-        <v>12.79</v>
+        <v>12.02</v>
       </c>
       <c r="G35" t="n">
-        <v>81.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="H35" t="n">
-        <v>88.8</v>
+        <v>79</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-93.51000000000001</v>
+        <v>314.66</v>
       </c>
       <c r="K35" t="n">
-        <v>101.83</v>
+        <v>41.62</v>
       </c>
       <c r="L35" t="n">
-        <v>138.25</v>
+        <v>317.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:15:38</t>
+          <t>08:12:56</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.63</v>
+        <v>4.39</v>
       </c>
       <c r="F36" t="n">
-        <v>12.54</v>
+        <v>12.89</v>
       </c>
       <c r="G36" t="n">
-        <v>68.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>75.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I36" t="n">
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-152.22</v>
+        <v>358.93</v>
       </c>
       <c r="K36" t="n">
-        <v>-187.55</v>
+        <v>-192.6</v>
       </c>
       <c r="L36" t="n">
-        <v>241.55</v>
+        <v>407.34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:16:49</t>
+          <t>08:14:07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.57</v>
+        <v>4.09</v>
       </c>
       <c r="F37" t="n">
-        <v>12.47</v>
+        <v>12.44</v>
       </c>
       <c r="G37" t="n">
-        <v>86</v>
+        <v>91.5</v>
       </c>
       <c r="H37" t="n">
-        <v>78.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="I37" t="n">
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-206.33</v>
+        <v>-94.02</v>
       </c>
       <c r="K37" t="n">
-        <v>-33.61</v>
+        <v>-212.91</v>
       </c>
       <c r="L37" t="n">
-        <v>209.04</v>
+        <v>232.74</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:21:24</t>
+          <t>08:17:34</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.99</v>
+        <v>4.54</v>
       </c>
       <c r="F38" t="n">
-        <v>12.28</v>
+        <v>12.49</v>
       </c>
       <c r="G38" t="n">
-        <v>74.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="H38" t="n">
-        <v>88.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>-215.39</v>
+        <v>252.78</v>
       </c>
       <c r="K38" t="n">
-        <v>198.78</v>
+        <v>-325.65</v>
       </c>
       <c r="L38" t="n">
-        <v>293.09</v>
+        <v>412.25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:22:26</t>
+          <t>08:19:08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>5.14</v>
+        <v>4.31</v>
       </c>
       <c r="F39" t="n">
-        <v>13.16</v>
+        <v>12.59</v>
       </c>
       <c r="G39" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H39" t="n">
-        <v>79.8</v>
+        <v>80.7</v>
       </c>
       <c r="I39" t="n">
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-95.54000000000001</v>
+        <v>-695.09</v>
       </c>
       <c r="K39" t="n">
-        <v>233.2</v>
+        <v>-51.21</v>
       </c>
       <c r="L39" t="n">
-        <v>252.02</v>
+        <v>696.98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:24:35</t>
+          <t>08:20:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.56</v>
+        <v>5.34</v>
       </c>
       <c r="F40" t="n">
-        <v>12.94</v>
+        <v>12.95</v>
       </c>
       <c r="G40" t="n">
-        <v>97.8</v>
+        <v>89.2</v>
       </c>
       <c r="H40" t="n">
-        <v>87.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>471.9</v>
+        <v>630.86</v>
       </c>
       <c r="K40" t="n">
-        <v>26.98</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>472.68</v>
+        <v>634.95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:29:23</t>
+          <t>08:26:06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="F41" t="n">
-        <v>12.55</v>
+        <v>12.97</v>
       </c>
       <c r="G41" t="n">
-        <v>88.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="H41" t="n">
-        <v>88.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="I41" t="n">
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-75.93000000000001</v>
+        <v>-878.6900000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>-595.91</v>
+        <v>370.92</v>
       </c>
       <c r="L41" t="n">
-        <v>600.73</v>
+        <v>953.77</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:30:46</t>
+          <t>08:28:07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.85</v>
+        <v>4.63</v>
       </c>
       <c r="F42" t="n">
-        <v>12.44</v>
+        <v>13.1</v>
       </c>
       <c r="G42" t="n">
-        <v>91.7</v>
+        <v>83.5</v>
       </c>
       <c r="H42" t="n">
-        <v>79.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I42" t="n">
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>515.89</v>
+        <v>92.27</v>
       </c>
       <c r="K42" t="n">
-        <v>88.09</v>
+        <v>139.06</v>
       </c>
       <c r="L42" t="n">
-        <v>523.35</v>
+        <v>166.89</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:32:35</t>
+          <t>08:29:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.98</v>
+        <v>5.43</v>
       </c>
       <c r="F43" t="n">
-        <v>12.07</v>
+        <v>12.85</v>
       </c>
       <c r="G43" t="n">
-        <v>81.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>87.7</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>51.91</v>
+        <v>467.13</v>
       </c>
       <c r="K43" t="n">
-        <v>-103.91</v>
+        <v>-24.58</v>
       </c>
       <c r="L43" t="n">
-        <v>116.16</v>
+        <v>467.78</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:40:42</t>
+          <t>08:37:59</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.88</v>
+        <v>4.64</v>
       </c>
       <c r="F44" t="n">
-        <v>13.07</v>
+        <v>12.32</v>
       </c>
       <c r="G44" t="n">
-        <v>77.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="H44" t="n">
-        <v>88.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>260.17</v>
+        <v>316.91</v>
       </c>
       <c r="K44" t="n">
-        <v>-103.66</v>
+        <v>141.67</v>
       </c>
       <c r="L44" t="n">
-        <v>280.06</v>
+        <v>347.14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:42:04</t>
+          <t>08:38:57</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.72</v>
+        <v>4.83</v>
       </c>
       <c r="F45" t="n">
-        <v>12.33</v>
+        <v>13.09</v>
       </c>
       <c r="G45" t="n">
-        <v>101.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>83.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>24.55</v>
+        <v>-172.36</v>
       </c>
       <c r="K45" t="n">
-        <v>7.63</v>
+        <v>-213.89</v>
       </c>
       <c r="L45" t="n">
-        <v>25.71</v>
+        <v>274.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:43:40</t>
+          <t>08:39:56</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>5.16</v>
+        <v>5.15</v>
       </c>
       <c r="F46" t="n">
-        <v>12.11</v>
+        <v>12.45</v>
       </c>
       <c r="G46" t="n">
-        <v>89.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>86.2</v>
+        <v>78.8</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>43.4</v>
+        <v>220.05</v>
       </c>
       <c r="K46" t="n">
-        <v>-256.56</v>
+        <v>-24.6</v>
       </c>
       <c r="L46" t="n">
-        <v>260.2</v>
+        <v>221.42</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:48:48</t>
+          <t>08:43:54</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.95</v>
+        <v>5.34</v>
       </c>
       <c r="F47" t="n">
-        <v>12.11</v>
+        <v>12.01</v>
       </c>
       <c r="G47" t="n">
-        <v>78.3</v>
+        <v>105</v>
       </c>
       <c r="H47" t="n">
-        <v>85.3</v>
+        <v>76.7</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>311.73</v>
+        <v>14.18</v>
       </c>
       <c r="K47" t="n">
-        <v>-289.38</v>
+        <v>-64.88</v>
       </c>
       <c r="L47" t="n">
-        <v>425.34</v>
+        <v>66.41</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:51:04</t>
+          <t>08:45:03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.59</v>
+        <v>5.07</v>
       </c>
       <c r="F48" t="n">
-        <v>12.56</v>
+        <v>12.7</v>
       </c>
       <c r="G48" t="n">
-        <v>85.3</v>
+        <v>92.3</v>
       </c>
       <c r="H48" t="n">
-        <v>85.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>67.59999999999999</v>
+        <v>364.6</v>
       </c>
       <c r="K48" t="n">
-        <v>203.51</v>
+        <v>118.73</v>
       </c>
       <c r="L48" t="n">
-        <v>214.44</v>
+        <v>383.44</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:52:08</t>
+          <t>08:46:33</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.58</v>
+        <v>4.52</v>
       </c>
       <c r="F49" t="n">
-        <v>12.51</v>
+        <v>12.3</v>
       </c>
       <c r="G49" t="n">
         <v>89.5</v>
       </c>
       <c r="H49" t="n">
-        <v>85</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>227.37</v>
+        <v>131.29</v>
       </c>
       <c r="K49" t="n">
-        <v>-88.36</v>
+        <v>343.83</v>
       </c>
       <c r="L49" t="n">
-        <v>243.94</v>
+        <v>368.04</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:57:38</t>
+          <t>08:51:05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.42</v>
+        <v>5.12</v>
       </c>
       <c r="F50" t="n">
-        <v>12.34</v>
+        <v>12.45</v>
       </c>
       <c r="G50" t="n">
-        <v>93.7</v>
+        <v>99.2</v>
       </c>
       <c r="H50" t="n">
-        <v>77.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="I50" t="n">
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-223.3</v>
+        <v>-236.05</v>
       </c>
       <c r="K50" t="n">
-        <v>-401.89</v>
+        <v>207.53</v>
       </c>
       <c r="L50" t="n">
-        <v>459.76</v>
+        <v>314.31</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:59:14</t>
+          <t>08:52:40</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>5.17</v>
+        <v>4.91</v>
       </c>
       <c r="F51" t="n">
-        <v>12.51</v>
+        <v>12.37</v>
       </c>
       <c r="G51" t="n">
-        <v>85.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>82.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>348.7</v>
+        <v>-264.29</v>
       </c>
       <c r="K51" t="n">
-        <v>53.45</v>
+        <v>252.64</v>
       </c>
       <c r="L51" t="n">
-        <v>352.77</v>
+        <v>365.62</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:01:00</t>
+          <t>08:53:46</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.09</v>
+        <v>4.47</v>
       </c>
       <c r="F52" t="n">
-        <v>13.07</v>
+        <v>13.3</v>
       </c>
       <c r="G52" t="n">
-        <v>95.8</v>
+        <v>91.5</v>
       </c>
       <c r="H52" t="n">
-        <v>76.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>-115.1</v>
+        <v>369.3</v>
       </c>
       <c r="K52" t="n">
-        <v>-120.8</v>
+        <v>43.93</v>
       </c>
       <c r="L52" t="n">
-        <v>166.85</v>
+        <v>371.91</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:06:05</t>
+          <t>08:57:15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.09</v>
+        <v>4.64</v>
       </c>
       <c r="F53" t="n">
-        <v>13.25</v>
+        <v>12.48</v>
       </c>
       <c r="G53" t="n">
-        <v>81.3</v>
+        <v>82</v>
       </c>
       <c r="H53" t="n">
-        <v>78.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>-76.8</v>
+        <v>573.85</v>
       </c>
       <c r="K53" t="n">
-        <v>-5.5</v>
+        <v>34.24</v>
       </c>
       <c r="L53" t="n">
-        <v>77</v>
+        <v>574.87</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:08:47</t>
+          <t>08:58:20</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.31</v>
+        <v>4.78</v>
       </c>
       <c r="F54" t="n">
-        <v>12.98</v>
+        <v>12.91</v>
       </c>
       <c r="G54" t="n">
-        <v>76.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="H54" t="n">
-        <v>83</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>146.93</v>
+        <v>446.87</v>
       </c>
       <c r="K54" t="n">
-        <v>216.69</v>
+        <v>-393.61</v>
       </c>
       <c r="L54" t="n">
-        <v>261.81</v>
+        <v>595.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:11:13</t>
+          <t>08:59:44</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.6</v>
+        <v>5.15</v>
       </c>
       <c r="F55" t="n">
-        <v>12.66</v>
+        <v>12.3</v>
       </c>
       <c r="G55" t="n">
-        <v>87.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="H55" t="n">
-        <v>83.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>444.71</v>
+        <v>460.69</v>
       </c>
       <c r="K55" t="n">
-        <v>303.33</v>
+        <v>-801.04</v>
       </c>
       <c r="L55" t="n">
-        <v>538.3099999999999</v>
+        <v>924.0700000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:16:06</t>
+          <t>09:04:16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.08</v>
+        <v>4.99</v>
       </c>
       <c r="F56" t="n">
-        <v>13.14</v>
+        <v>12.68</v>
       </c>
       <c r="G56" t="n">
-        <v>91.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="H56" t="n">
-        <v>81.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>86.28</v>
+        <v>1026.7</v>
       </c>
       <c r="K56" t="n">
-        <v>-54.25</v>
+        <v>525.8200000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>101.92</v>
+        <v>1153.52</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:17:46</t>
+          <t>09:05:58</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.97</v>
+        <v>5.28</v>
       </c>
       <c r="F57" t="n">
-        <v>13.02</v>
+        <v>12.73</v>
       </c>
       <c r="G57" t="n">
-        <v>84.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>78.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>681.8099999999999</v>
+        <v>227.41</v>
       </c>
       <c r="K57" t="n">
-        <v>-323.99</v>
+        <v>785.74</v>
       </c>
       <c r="L57" t="n">
-        <v>754.87</v>
+        <v>817.99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:07:12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>5.28</v>
+        <v>4.4</v>
       </c>
       <c r="F58" t="n">
-        <v>12.46</v>
+        <v>12.62</v>
       </c>
       <c r="G58" t="n">
-        <v>74.40000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>83.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-283.71</v>
+        <v>76.02</v>
       </c>
       <c r="K58" t="n">
-        <v>-400.82</v>
+        <v>656.51</v>
       </c>
       <c r="L58" t="n">
-        <v>491.07</v>
+        <v>660.9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:29:17</t>
+          <t>09:18:13</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.21</v>
+        <v>5.33</v>
       </c>
       <c r="F59" t="n">
-        <v>12.66</v>
+        <v>12.83</v>
       </c>
       <c r="G59" t="n">
-        <v>80.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>86.59999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="I59" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-114.82</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>5.32</v>
+        <v>-149.18</v>
       </c>
       <c r="L59" t="n">
-        <v>114.95</v>
+        <v>176.81</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:30:29</t>
+          <t>09:19:02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.7</v>
+        <v>4.81</v>
       </c>
       <c r="F60" t="n">
-        <v>12.47</v>
+        <v>13.14</v>
       </c>
       <c r="G60" t="n">
-        <v>91.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>83.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>-322.24</v>
+        <v>-284.43</v>
       </c>
       <c r="K60" t="n">
-        <v>-95.31999999999999</v>
+        <v>329.88</v>
       </c>
       <c r="L60" t="n">
-        <v>336.04</v>
+        <v>435.57</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:31:23</t>
+          <t>09:21:01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>5.3</v>
+        <v>4.67</v>
       </c>
       <c r="F61" t="n">
-        <v>12.07</v>
+        <v>12.59</v>
       </c>
       <c r="G61" t="n">
-        <v>82.5</v>
+        <v>84.3</v>
       </c>
       <c r="H61" t="n">
-        <v>82.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-222.7</v>
+        <v>-122.91</v>
       </c>
       <c r="K61" t="n">
-        <v>258.74</v>
+        <v>-29.02</v>
       </c>
       <c r="L61" t="n">
-        <v>341.38</v>
+        <v>126.29</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:37:05</t>
+          <t>09:27:02</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.68</v>
+        <v>5.02</v>
       </c>
       <c r="F62" t="n">
-        <v>12.61</v>
+        <v>12.48</v>
       </c>
       <c r="G62" t="n">
-        <v>88.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>85.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>172.97</v>
+        <v>-339.05</v>
       </c>
       <c r="K62" t="n">
-        <v>176.17</v>
+        <v>239.85</v>
       </c>
       <c r="L62" t="n">
-        <v>246.89</v>
+        <v>415.31</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:39:21</t>
+          <t>09:27:43</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.59</v>
+        <v>5.05</v>
       </c>
       <c r="F63" t="n">
-        <v>12.74</v>
+        <v>12.42</v>
       </c>
       <c r="G63" t="n">
-        <v>80.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="H63" t="n">
-        <v>86.2</v>
+        <v>79.8</v>
       </c>
       <c r="I63" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>-120.41</v>
+        <v>107.23</v>
       </c>
       <c r="K63" t="n">
-        <v>-188.65</v>
+        <v>-38.95</v>
       </c>
       <c r="L63" t="n">
-        <v>223.8</v>
+        <v>114.09</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:40:33</t>
+          <t>09:29:31</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.66</v>
+        <v>4.42</v>
       </c>
       <c r="F64" t="n">
-        <v>12.03</v>
+        <v>12.19</v>
       </c>
       <c r="G64" t="n">
-        <v>77.8</v>
+        <v>95.7</v>
       </c>
       <c r="H64" t="n">
-        <v>81.09999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-135.53</v>
+        <v>-159.87</v>
       </c>
       <c r="K64" t="n">
-        <v>11.98</v>
+        <v>-302.02</v>
       </c>
       <c r="L64" t="n">
-        <v>136.06</v>
+        <v>341.72</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:46:41</t>
+          <t>09:34:44</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.65</v>
+        <v>5.78</v>
       </c>
       <c r="F65" t="n">
-        <v>13.12</v>
+        <v>12.18</v>
       </c>
       <c r="G65" t="n">
-        <v>76.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H65" t="n">
-        <v>80.3</v>
+        <v>79.8</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>-18.55</v>
+        <v>109.76</v>
       </c>
       <c r="K65" t="n">
-        <v>19.83</v>
+        <v>378.24</v>
       </c>
       <c r="L65" t="n">
-        <v>27.16</v>
+        <v>393.84</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:47:50</t>
+          <t>09:35:56</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.49</v>
+        <v>4.81</v>
       </c>
       <c r="F66" t="n">
-        <v>12.73</v>
+        <v>13.25</v>
       </c>
       <c r="G66" t="n">
-        <v>77.09999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>89.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-178.27</v>
+        <v>-106.12</v>
       </c>
       <c r="K66" t="n">
-        <v>-141.94</v>
+        <v>-412.92</v>
       </c>
       <c r="L66" t="n">
-        <v>227.88</v>
+        <v>426.34</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:48:54</t>
+          <t>09:37:18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="F67" t="n">
-        <v>12.66</v>
+        <v>12.04</v>
       </c>
       <c r="G67" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>83</v>
+        <v>85.8</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-267.01</v>
+        <v>551.47</v>
       </c>
       <c r="K67" t="n">
-        <v>258.72</v>
+        <v>-243.1</v>
       </c>
       <c r="L67" t="n">
-        <v>371.79</v>
+        <v>602.6799999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:53:31</t>
+          <t>09:42:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.04</v>
+        <v>5.09</v>
       </c>
       <c r="F68" t="n">
-        <v>12.9</v>
+        <v>12.83</v>
       </c>
       <c r="G68" t="n">
-        <v>79.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>79.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>268.06</v>
+        <v>-536.29</v>
       </c>
       <c r="K68" t="n">
-        <v>171.11</v>
+        <v>-256.82</v>
       </c>
       <c r="L68" t="n">
-        <v>318.02</v>
+        <v>594.61</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:54:46</t>
+          <t>09:42:33</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.72</v>
+        <v>5.02</v>
       </c>
       <c r="F69" t="n">
-        <v>12.13</v>
+        <v>12.88</v>
       </c>
       <c r="G69" t="n">
-        <v>84.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>80.7</v>
+        <v>86.5</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>82.65000000000001</v>
+        <v>-404.07</v>
       </c>
       <c r="K69" t="n">
-        <v>237.01</v>
+        <v>-116.55</v>
       </c>
       <c r="L69" t="n">
-        <v>251</v>
+        <v>420.54</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:56:07</t>
+          <t>09:44:45</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.37</v>
+        <v>5.23</v>
       </c>
       <c r="F70" t="n">
-        <v>12.76</v>
+        <v>13.06</v>
       </c>
       <c r="G70" t="n">
-        <v>85.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="H70" t="n">
-        <v>87.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>181.09</v>
+        <v>-204.66</v>
       </c>
       <c r="K70" t="n">
-        <v>-568.52</v>
+        <v>-61.83</v>
       </c>
       <c r="L70" t="n">
-        <v>596.67</v>
+        <v>213.79</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:01:44</t>
+          <t>09:48:40</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.81</v>
+        <v>5.58</v>
       </c>
       <c r="F71" t="n">
-        <v>13.66</v>
+        <v>12.76</v>
       </c>
       <c r="G71" t="n">
-        <v>84</v>
+        <v>89.8</v>
       </c>
       <c r="H71" t="n">
-        <v>81.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>-341.65</v>
+        <v>5.25</v>
       </c>
       <c r="K71" t="n">
-        <v>116.73</v>
+        <v>-160.61</v>
       </c>
       <c r="L71" t="n">
-        <v>361.04</v>
+        <v>160.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:02:41</t>
+          <t>09:50:15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.85</v>
+        <v>5.62</v>
       </c>
       <c r="F72" t="n">
-        <v>12.3</v>
+        <v>13.18</v>
       </c>
       <c r="G72" t="n">
-        <v>80.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H72" t="n">
-        <v>78.3</v>
+        <v>83.2</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>-161.48</v>
+        <v>-22.76</v>
       </c>
       <c r="K72" t="n">
-        <v>-658.28</v>
+        <v>762</v>
       </c>
       <c r="L72" t="n">
-        <v>677.79</v>
+        <v>762.34</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:04:38</t>
+          <t>09:51:19</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="F73" t="n">
-        <v>12.53</v>
+        <v>12.11</v>
       </c>
       <c r="G73" t="n">
-        <v>76.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="H73" t="n">
-        <v>83.7</v>
+        <v>81.7</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-251.45</v>
+        <v>-1212.86</v>
       </c>
       <c r="K73" t="n">
-        <v>256.23</v>
+        <v>457.72</v>
       </c>
       <c r="L73" t="n">
-        <v>359</v>
+        <v>1296.35</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:14:00</t>
+          <t>10:02:24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.98</v>
+        <v>5.52</v>
       </c>
       <c r="F74" t="n">
-        <v>12.81</v>
+        <v>13.11</v>
       </c>
       <c r="G74" t="n">
-        <v>74.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="H74" t="n">
-        <v>86.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>53.98</v>
+        <v>-240.13</v>
       </c>
       <c r="K74" t="n">
-        <v>100.74</v>
+        <v>-26.4</v>
       </c>
       <c r="L74" t="n">
-        <v>114.29</v>
+        <v>241.58</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:15:42</t>
+          <t>10:03:32</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.26</v>
+        <v>5.35</v>
       </c>
       <c r="F75" t="n">
-        <v>12.55</v>
+        <v>12.64</v>
       </c>
       <c r="G75" t="n">
-        <v>76.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="H75" t="n">
-        <v>88.8</v>
+        <v>80.8</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-193.79</v>
+        <v>-19.41</v>
       </c>
       <c r="K75" t="n">
-        <v>-223.54</v>
+        <v>151.07</v>
       </c>
       <c r="L75" t="n">
-        <v>295.85</v>
+        <v>152.31</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:16:57</t>
+          <t>10:05:53</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.04</v>
+        <v>4.61</v>
       </c>
       <c r="F76" t="n">
-        <v>13.08</v>
+        <v>13.37</v>
       </c>
       <c r="G76" t="n">
-        <v>93.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="H76" t="n">
-        <v>84.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="I76" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>20.28</v>
+        <v>-195.96</v>
       </c>
       <c r="K76" t="n">
-        <v>161.95</v>
+        <v>-176.77</v>
       </c>
       <c r="L76" t="n">
-        <v>163.21</v>
+        <v>263.91</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:21:09</t>
+          <t>10:11:48</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.13</v>
+        <v>5.29</v>
       </c>
       <c r="F77" t="n">
-        <v>12.69</v>
+        <v>13.29</v>
       </c>
       <c r="G77" t="n">
-        <v>88.5</v>
+        <v>101.6</v>
       </c>
       <c r="H77" t="n">
-        <v>83.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>22.32</v>
+        <v>-305.69</v>
       </c>
       <c r="K77" t="n">
-        <v>-492.83</v>
+        <v>329.6</v>
       </c>
       <c r="L77" t="n">
-        <v>493.34</v>
+        <v>449.54</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:22:09</t>
+          <t>10:13:59</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.18</v>
+        <v>5.69</v>
       </c>
       <c r="F78" t="n">
-        <v>12.45</v>
+        <v>12.32</v>
       </c>
       <c r="G78" t="n">
-        <v>93.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>78.59999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>155.42</v>
+        <v>-365.17</v>
       </c>
       <c r="K78" t="n">
-        <v>204.6</v>
+        <v>-270.69</v>
       </c>
       <c r="L78" t="n">
-        <v>256.93</v>
+        <v>454.56</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:23:32</t>
+          <t>10:16:18</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.81</v>
+        <v>5.45</v>
       </c>
       <c r="F79" t="n">
-        <v>13.17</v>
+        <v>12.5</v>
       </c>
       <c r="G79" t="n">
-        <v>72.5</v>
+        <v>74.7</v>
       </c>
       <c r="H79" t="n">
-        <v>86.90000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>85.39</v>
+        <v>255.36</v>
       </c>
       <c r="K79" t="n">
-        <v>35.46</v>
+        <v>-33.61</v>
       </c>
       <c r="L79" t="n">
-        <v>92.45999999999999</v>
+        <v>257.56</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:28:12</t>
+          <t>10:20:30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.33</v>
+        <v>5.15</v>
       </c>
       <c r="F80" t="n">
-        <v>13.07</v>
+        <v>12.89</v>
       </c>
       <c r="G80" t="n">
-        <v>80.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>80.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>-70.33</v>
+        <v>239.99</v>
       </c>
       <c r="K80" t="n">
-        <v>-86.18000000000001</v>
+        <v>220.76</v>
       </c>
       <c r="L80" t="n">
-        <v>111.23</v>
+        <v>326.08</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:30:07</t>
+          <t>10:21:50</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>5.46</v>
+        <v>6.14</v>
       </c>
       <c r="F81" t="n">
-        <v>12.81</v>
+        <v>12.45</v>
       </c>
       <c r="G81" t="n">
-        <v>70.7</v>
+        <v>82.8</v>
       </c>
       <c r="H81" t="n">
-        <v>83.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>174.42</v>
+        <v>192.64</v>
       </c>
       <c r="K81" t="n">
-        <v>169.22</v>
+        <v>-360.42</v>
       </c>
       <c r="L81" t="n">
-        <v>243.02</v>
+        <v>408.67</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:31:30</t>
+          <t>10:23:55</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.37</v>
+        <v>4.53</v>
       </c>
       <c r="F82" t="n">
-        <v>13.26</v>
+        <v>12.33</v>
       </c>
       <c r="G82" t="n">
-        <v>96.3</v>
+        <v>90.2</v>
       </c>
       <c r="H82" t="n">
-        <v>79.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-75.03</v>
+        <v>-415.29</v>
       </c>
       <c r="K82" t="n">
-        <v>-119.29</v>
+        <v>-403.96</v>
       </c>
       <c r="L82" t="n">
-        <v>140.92</v>
+        <v>579.35</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:36:37</t>
+          <t>10:28:45</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.11</v>
+        <v>4.96</v>
       </c>
       <c r="F83" t="n">
-        <v>12.31</v>
+        <v>12.61</v>
       </c>
       <c r="G83" t="n">
-        <v>77.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="H83" t="n">
-        <v>79.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>-261.44</v>
+        <v>-525.87</v>
       </c>
       <c r="K83" t="n">
-        <v>162.27</v>
+        <v>117.89</v>
       </c>
       <c r="L83" t="n">
-        <v>307.71</v>
+        <v>538.92</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:38:22</t>
+          <t>10:30:19</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>6.1</v>
+        <v>4.4</v>
       </c>
       <c r="F84" t="n">
-        <v>12.19</v>
+        <v>12.97</v>
       </c>
       <c r="G84" t="n">
-        <v>83</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>78.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-353.73</v>
+        <v>-157.32</v>
       </c>
       <c r="K84" t="n">
-        <v>-219.54</v>
+        <v>524.75</v>
       </c>
       <c r="L84" t="n">
-        <v>416.32</v>
+        <v>547.8200000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:40:31</t>
+          <t>10:32:34</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.7</v>
+        <v>5.03</v>
       </c>
       <c r="F85" t="n">
-        <v>12.65</v>
+        <v>12.92</v>
       </c>
       <c r="G85" t="n">
-        <v>84.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H85" t="n">
-        <v>77.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-212.44</v>
+        <v>-106.49</v>
       </c>
       <c r="K85" t="n">
-        <v>-160.5</v>
+        <v>-597.25</v>
       </c>
       <c r="L85" t="n">
-        <v>266.25</v>
+        <v>606.67</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:44:37</t>
+          <t>10:37:32</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5.43</v>
+        <v>4.69</v>
       </c>
       <c r="F86" t="n">
-        <v>13.02</v>
+        <v>11.99</v>
       </c>
       <c r="G86" t="n">
-        <v>87</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H86" t="n">
-        <v>87.5</v>
+        <v>89.3</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>293.13</v>
+        <v>-326.1</v>
       </c>
       <c r="K86" t="n">
-        <v>93.78</v>
+        <v>-298.44</v>
       </c>
       <c r="L86" t="n">
-        <v>307.77</v>
+        <v>442.05</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:46:49</t>
+          <t>10:39:21</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.97</v>
+        <v>4.95</v>
       </c>
       <c r="F87" t="n">
-        <v>12.32</v>
+        <v>12.78</v>
       </c>
       <c r="G87" t="n">
-        <v>84.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="H87" t="n">
-        <v>83.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="I87" t="n">
         <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>-696.41</v>
+        <v>586.03</v>
       </c>
       <c r="K87" t="n">
-        <v>-109.52</v>
+        <v>-557.77</v>
       </c>
       <c r="L87" t="n">
-        <v>704.97</v>
+        <v>809.03</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:47:46</t>
+          <t>10:40:10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.39</v>
+        <v>5.47</v>
       </c>
       <c r="F88" t="n">
-        <v>12.88</v>
+        <v>13.39</v>
       </c>
       <c r="G88" t="n">
-        <v>83.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H88" t="n">
-        <v>85.3</v>
+        <v>83.7</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-1009.8</v>
+        <v>-416.56</v>
       </c>
       <c r="K88" t="n">
-        <v>464.03</v>
+        <v>-477.47</v>
       </c>
       <c r="L88" t="n">
-        <v>1111.32</v>
+        <v>633.64</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-29.xlsx
+++ b/output/2025-09-29.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>174.39</v>
+        <v>193.53</v>
       </c>
       <c r="K14" t="n">
-        <v>63.15</v>
+        <v>70.08</v>
       </c>
       <c r="L14" t="n">
-        <v>185.47</v>
+        <v>205.82</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>119.05</v>
+        <v>174.46</v>
       </c>
       <c r="K15" t="n">
-        <v>-22.91</v>
+        <v>-33.57</v>
       </c>
       <c r="L15" t="n">
-        <v>121.23</v>
+        <v>177.66</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-264.08</v>
+        <v>-311.49</v>
       </c>
       <c r="K16" t="n">
-        <v>73.37</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>274.09</v>
+        <v>323.29</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>148.67</v>
+        <v>172.75</v>
       </c>
       <c r="K17" t="n">
-        <v>200.37</v>
+        <v>232.82</v>
       </c>
       <c r="L17" t="n">
-        <v>249.5</v>
+        <v>289.91</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>-404.2</v>
+        <v>-402.06</v>
       </c>
       <c r="K18" t="n">
-        <v>-209.93</v>
+        <v>-208.82</v>
       </c>
       <c r="L18" t="n">
-        <v>455.46</v>
+        <v>453.06</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>17</v>
       </c>
       <c r="J19" t="n">
-        <v>310.17</v>
+        <v>372.32</v>
       </c>
       <c r="K19" t="n">
-        <v>264.73</v>
+        <v>317.77</v>
       </c>
       <c r="L19" t="n">
-        <v>407.78</v>
+        <v>489.49</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-199.92</v>
+        <v>-311.58</v>
       </c>
       <c r="K20" t="n">
-        <v>-180.13</v>
+        <v>-280.75</v>
       </c>
       <c r="L20" t="n">
-        <v>269.1</v>
+        <v>419.41</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>74.12</v>
+        <v>122.64</v>
       </c>
       <c r="K21" t="n">
-        <v>-172.4</v>
+        <v>-285.26</v>
       </c>
       <c r="L21" t="n">
-        <v>187.66</v>
+        <v>310.51</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>-183.93</v>
+        <v>-270</v>
       </c>
       <c r="K22" t="n">
-        <v>91.47</v>
+        <v>134.28</v>
       </c>
       <c r="L22" t="n">
-        <v>205.42</v>
+        <v>301.55</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-241.91</v>
+        <v>-400.71</v>
       </c>
       <c r="K23" t="n">
-        <v>149.61</v>
+        <v>247.82</v>
       </c>
       <c r="L23" t="n">
-        <v>284.43</v>
+        <v>471.15</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>634.9400000000001</v>
+        <v>848.09</v>
       </c>
       <c r="K24" t="n">
-        <v>-624.49</v>
+        <v>-834.13</v>
       </c>
       <c r="L24" t="n">
-        <v>890.58</v>
+        <v>1189.55</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>35.29</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-169.61</v>
+        <v>-356.11</v>
       </c>
       <c r="L25" t="n">
-        <v>173.25</v>
+        <v>363.74</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-710.67</v>
+        <v>-979.47</v>
       </c>
       <c r="K26" t="n">
-        <v>-204.2</v>
+        <v>-281.43</v>
       </c>
       <c r="L26" t="n">
-        <v>739.42</v>
+        <v>1019.1</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>755.83</v>
+        <v>1080.94</v>
       </c>
       <c r="K27" t="n">
-        <v>147.59</v>
+        <v>211.08</v>
       </c>
       <c r="L27" t="n">
-        <v>770.1</v>
+        <v>1101.36</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-277.51</v>
+        <v>-405.94</v>
       </c>
       <c r="K28" t="n">
-        <v>812.52</v>
+        <v>1188.57</v>
       </c>
       <c r="L28" t="n">
-        <v>858.6</v>
+        <v>1255.98</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>72.94</v>
+        <v>116.4</v>
       </c>
       <c r="K29" t="n">
-        <v>-108.71</v>
+        <v>-173.49</v>
       </c>
       <c r="L29" t="n">
-        <v>130.91</v>
+        <v>208.92</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>62.21</v>
+        <v>81.53</v>
       </c>
       <c r="K30" t="n">
-        <v>-283.34</v>
+        <v>-371.3</v>
       </c>
       <c r="L30" t="n">
-        <v>290.09</v>
+        <v>380.15</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>259.43</v>
+        <v>296.06</v>
       </c>
       <c r="K31" t="n">
-        <v>-147.27</v>
+        <v>-168.07</v>
       </c>
       <c r="L31" t="n">
-        <v>298.32</v>
+        <v>340.44</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>97.89</v>
+        <v>190.29</v>
       </c>
       <c r="K32" t="n">
-        <v>15.46</v>
+        <v>30.05</v>
       </c>
       <c r="L32" t="n">
-        <v>99.11</v>
+        <v>192.65</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-366.15</v>
+        <v>-448.59</v>
       </c>
       <c r="K33" t="n">
-        <v>-273.65</v>
+        <v>-335.26</v>
       </c>
       <c r="L33" t="n">
-        <v>457.11</v>
+        <v>560.03</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>304</v>
+        <v>348.17</v>
       </c>
       <c r="K34" t="n">
-        <v>163.76</v>
+        <v>187.56</v>
       </c>
       <c r="L34" t="n">
-        <v>345.3</v>
+        <v>395.48</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>314.66</v>
+        <v>400.67</v>
       </c>
       <c r="K35" t="n">
-        <v>41.62</v>
+        <v>53</v>
       </c>
       <c r="L35" t="n">
-        <v>317.4</v>
+        <v>404.16</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>358.93</v>
+        <v>431.22</v>
       </c>
       <c r="K36" t="n">
-        <v>-192.6</v>
+        <v>-231.39</v>
       </c>
       <c r="L36" t="n">
-        <v>407.34</v>
+        <v>489.38</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-94.02</v>
+        <v>-143.61</v>
       </c>
       <c r="K37" t="n">
-        <v>-212.91</v>
+        <v>-325.2</v>
       </c>
       <c r="L37" t="n">
-        <v>232.74</v>
+        <v>355.5</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>252.78</v>
+        <v>366.36</v>
       </c>
       <c r="K38" t="n">
-        <v>-325.65</v>
+        <v>-471.98</v>
       </c>
       <c r="L38" t="n">
-        <v>412.25</v>
+        <v>597.48</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-695.09</v>
+        <v>-883.96</v>
       </c>
       <c r="K39" t="n">
-        <v>-51.21</v>
+        <v>-65.13</v>
       </c>
       <c r="L39" t="n">
-        <v>696.98</v>
+        <v>886.35</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>630.86</v>
+        <v>1000.02</v>
       </c>
       <c r="K40" t="n">
-        <v>71.93000000000001</v>
+        <v>114.03</v>
       </c>
       <c r="L40" t="n">
-        <v>634.95</v>
+        <v>1006.5</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-878.6900000000001</v>
+        <v>-1169.46</v>
       </c>
       <c r="K41" t="n">
-        <v>370.92</v>
+        <v>493.66</v>
       </c>
       <c r="L41" t="n">
-        <v>953.77</v>
+        <v>1269.38</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>92.27</v>
+        <v>248.65</v>
       </c>
       <c r="K42" t="n">
-        <v>139.06</v>
+        <v>374.76</v>
       </c>
       <c r="L42" t="n">
-        <v>166.89</v>
+        <v>449.75</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>467.13</v>
+        <v>852.24</v>
       </c>
       <c r="K43" t="n">
-        <v>-24.58</v>
+        <v>-44.85</v>
       </c>
       <c r="L43" t="n">
-        <v>467.78</v>
+        <v>853.42</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>316.91</v>
+        <v>379.19</v>
       </c>
       <c r="K44" t="n">
-        <v>141.67</v>
+        <v>169.51</v>
       </c>
       <c r="L44" t="n">
-        <v>347.14</v>
+        <v>415.35</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-172.36</v>
+        <v>-225.35</v>
       </c>
       <c r="K45" t="n">
-        <v>-213.89</v>
+        <v>-279.66</v>
       </c>
       <c r="L45" t="n">
-        <v>274.7</v>
+        <v>359.15</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>220.05</v>
+        <v>283.74</v>
       </c>
       <c r="K46" t="n">
-        <v>-24.6</v>
+        <v>-31.72</v>
       </c>
       <c r="L46" t="n">
-        <v>221.42</v>
+        <v>285.51</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>14.18</v>
+        <v>36.81</v>
       </c>
       <c r="K47" t="n">
-        <v>-64.88</v>
+        <v>-168.43</v>
       </c>
       <c r="L47" t="n">
-        <v>66.41</v>
+        <v>172.41</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>364.6</v>
+        <v>409.41</v>
       </c>
       <c r="K48" t="n">
-        <v>118.73</v>
+        <v>133.32</v>
       </c>
       <c r="L48" t="n">
-        <v>383.44</v>
+        <v>430.57</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>131.29</v>
+        <v>157.15</v>
       </c>
       <c r="K49" t="n">
-        <v>343.83</v>
+        <v>411.55</v>
       </c>
       <c r="L49" t="n">
-        <v>368.04</v>
+        <v>440.54</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-236.05</v>
+        <v>-342.88</v>
       </c>
       <c r="K50" t="n">
-        <v>207.53</v>
+        <v>301.45</v>
       </c>
       <c r="L50" t="n">
-        <v>314.31</v>
+        <v>456.55</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-264.29</v>
+        <v>-346.38</v>
       </c>
       <c r="K51" t="n">
-        <v>252.64</v>
+        <v>331.11</v>
       </c>
       <c r="L51" t="n">
-        <v>365.62</v>
+        <v>479.18</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>369.3</v>
+        <v>484.56</v>
       </c>
       <c r="K52" t="n">
-        <v>43.93</v>
+        <v>57.65</v>
       </c>
       <c r="L52" t="n">
-        <v>371.91</v>
+        <v>487.98</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>573.85</v>
+        <v>835.2</v>
       </c>
       <c r="K53" t="n">
-        <v>34.24</v>
+        <v>49.84</v>
       </c>
       <c r="L53" t="n">
-        <v>574.87</v>
+        <v>836.6799999999999</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>446.87</v>
+        <v>652.6</v>
       </c>
       <c r="K54" t="n">
-        <v>-393.61</v>
+        <v>-574.83</v>
       </c>
       <c r="L54" t="n">
-        <v>595.5</v>
+        <v>869.66</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>460.69</v>
+        <v>645.64</v>
       </c>
       <c r="K55" t="n">
-        <v>-801.04</v>
+        <v>-1122.62</v>
       </c>
       <c r="L55" t="n">
-        <v>924.0700000000001</v>
+        <v>1295.04</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>1026.7</v>
+        <v>1341.92</v>
       </c>
       <c r="K56" t="n">
-        <v>525.8200000000001</v>
+        <v>687.26</v>
       </c>
       <c r="L56" t="n">
-        <v>1153.52</v>
+        <v>1507.67</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>227.41</v>
+        <v>359.78</v>
       </c>
       <c r="K57" t="n">
-        <v>785.74</v>
+        <v>1243.1</v>
       </c>
       <c r="L57" t="n">
-        <v>817.99</v>
+        <v>1294.12</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>76.02</v>
+        <v>117.03</v>
       </c>
       <c r="K58" t="n">
-        <v>656.51</v>
+        <v>1010.7</v>
       </c>
       <c r="L58" t="n">
-        <v>660.9</v>
+        <v>1017.45</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>94.90000000000001</v>
+        <v>152.15</v>
       </c>
       <c r="K59" t="n">
-        <v>-149.18</v>
+        <v>-239.18</v>
       </c>
       <c r="L59" t="n">
-        <v>176.81</v>
+        <v>283.48</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>-284.43</v>
+        <v>-322.37</v>
       </c>
       <c r="K60" t="n">
-        <v>329.88</v>
+        <v>373.89</v>
       </c>
       <c r="L60" t="n">
-        <v>435.57</v>
+        <v>493.68</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-122.91</v>
+        <v>-180.78</v>
       </c>
       <c r="K61" t="n">
-        <v>-29.02</v>
+        <v>-42.68</v>
       </c>
       <c r="L61" t="n">
-        <v>126.29</v>
+        <v>185.75</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-339.05</v>
+        <v>-401.39</v>
       </c>
       <c r="K62" t="n">
-        <v>239.85</v>
+        <v>283.96</v>
       </c>
       <c r="L62" t="n">
-        <v>415.31</v>
+        <v>491.68</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>107.23</v>
+        <v>219.55</v>
       </c>
       <c r="K63" t="n">
-        <v>-38.95</v>
+        <v>-79.73999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>114.09</v>
+        <v>233.59</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-159.87</v>
+        <v>-188.8</v>
       </c>
       <c r="K64" t="n">
-        <v>-302.02</v>
+        <v>-356.66</v>
       </c>
       <c r="L64" t="n">
-        <v>341.72</v>
+        <v>403.55</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>109.76</v>
+        <v>174.19</v>
       </c>
       <c r="K65" t="n">
-        <v>378.24</v>
+        <v>600.27</v>
       </c>
       <c r="L65" t="n">
-        <v>393.84</v>
+        <v>625.03</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-106.12</v>
+        <v>-142.44</v>
       </c>
       <c r="K66" t="n">
-        <v>-412.92</v>
+        <v>-554.23</v>
       </c>
       <c r="L66" t="n">
-        <v>426.34</v>
+        <v>572.24</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>551.47</v>
+        <v>687.0700000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-243.1</v>
+        <v>-302.88</v>
       </c>
       <c r="L67" t="n">
-        <v>602.6799999999999</v>
+        <v>750.87</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-536.29</v>
+        <v>-827.38</v>
       </c>
       <c r="K68" t="n">
-        <v>-256.82</v>
+        <v>-396.22</v>
       </c>
       <c r="L68" t="n">
-        <v>594.61</v>
+        <v>917.36</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>-404.07</v>
+        <v>-648.3200000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>-116.55</v>
+        <v>-187</v>
       </c>
       <c r="L69" t="n">
-        <v>420.54</v>
+        <v>674.75</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-204.66</v>
+        <v>-432.8</v>
       </c>
       <c r="K70" t="n">
-        <v>-61.83</v>
+        <v>-130.75</v>
       </c>
       <c r="L70" t="n">
-        <v>213.79</v>
+        <v>452.12</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>5.25</v>
+        <v>18.3</v>
       </c>
       <c r="K71" t="n">
-        <v>-160.61</v>
+        <v>-559.9299999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>160.7</v>
+        <v>560.23</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>-22.76</v>
+        <v>-39.05</v>
       </c>
       <c r="K72" t="n">
-        <v>762</v>
+        <v>1307.12</v>
       </c>
       <c r="L72" t="n">
-        <v>762.34</v>
+        <v>1307.71</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-1212.86</v>
+        <v>-1661.71</v>
       </c>
       <c r="K73" t="n">
-        <v>457.72</v>
+        <v>627.11</v>
       </c>
       <c r="L73" t="n">
-        <v>1296.35</v>
+        <v>1776.1</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-240.13</v>
+        <v>-306.2</v>
       </c>
       <c r="K74" t="n">
-        <v>-26.4</v>
+        <v>-33.67</v>
       </c>
       <c r="L74" t="n">
-        <v>241.58</v>
+        <v>308.05</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-19.41</v>
+        <v>-30.07</v>
       </c>
       <c r="K75" t="n">
-        <v>151.07</v>
+        <v>234.05</v>
       </c>
       <c r="L75" t="n">
-        <v>152.31</v>
+        <v>235.97</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-195.96</v>
+        <v>-218.59</v>
       </c>
       <c r="K76" t="n">
-        <v>-176.77</v>
+        <v>-197.19</v>
       </c>
       <c r="L76" t="n">
-        <v>263.91</v>
+        <v>294.39</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>-305.69</v>
+        <v>-354.9</v>
       </c>
       <c r="K77" t="n">
-        <v>329.6</v>
+        <v>382.66</v>
       </c>
       <c r="L77" t="n">
-        <v>449.54</v>
+        <v>521.9</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-365.17</v>
+        <v>-478.95</v>
       </c>
       <c r="K78" t="n">
-        <v>-270.69</v>
+        <v>-355.03</v>
       </c>
       <c r="L78" t="n">
-        <v>454.56</v>
+        <v>596.1900000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>255.36</v>
+        <v>377.21</v>
       </c>
       <c r="K79" t="n">
-        <v>-33.61</v>
+        <v>-49.64</v>
       </c>
       <c r="L79" t="n">
-        <v>257.56</v>
+        <v>380.47</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>239.99</v>
+        <v>357.8</v>
       </c>
       <c r="K80" t="n">
-        <v>220.76</v>
+        <v>329.13</v>
       </c>
       <c r="L80" t="n">
-        <v>326.08</v>
+        <v>486.16</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>192.64</v>
+        <v>305.37</v>
       </c>
       <c r="K81" t="n">
-        <v>-360.42</v>
+        <v>-571.33</v>
       </c>
       <c r="L81" t="n">
-        <v>408.67</v>
+        <v>647.8200000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-415.29</v>
+        <v>-510.64</v>
       </c>
       <c r="K82" t="n">
-        <v>-403.96</v>
+        <v>-496.71</v>
       </c>
       <c r="L82" t="n">
-        <v>579.35</v>
+        <v>712.37</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>-525.87</v>
+        <v>-830.96</v>
       </c>
       <c r="K83" t="n">
-        <v>117.89</v>
+        <v>186.29</v>
       </c>
       <c r="L83" t="n">
-        <v>538.92</v>
+        <v>851.59</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-157.32</v>
+        <v>-227.38</v>
       </c>
       <c r="K84" t="n">
-        <v>524.75</v>
+        <v>758.45</v>
       </c>
       <c r="L84" t="n">
-        <v>547.8200000000001</v>
+        <v>791.8</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-106.49</v>
+        <v>-151.51</v>
       </c>
       <c r="K85" t="n">
-        <v>-597.25</v>
+        <v>-849.75</v>
       </c>
       <c r="L85" t="n">
-        <v>606.67</v>
+        <v>863.15</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-326.1</v>
+        <v>-631.3099999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>-298.44</v>
+        <v>-577.76</v>
       </c>
       <c r="L86" t="n">
-        <v>442.05</v>
+        <v>855.78</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>586.03</v>
+        <v>833.9400000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>-557.77</v>
+        <v>-793.73</v>
       </c>
       <c r="L87" t="n">
-        <v>809.03</v>
+        <v>1151.29</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-416.56</v>
+        <v>-773.25</v>
       </c>
       <c r="K88" t="n">
-        <v>-477.47</v>
+        <v>-886.3200000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>633.64</v>
+        <v>1176.21</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-29.xlsx
+++ b/output/2025-09-29.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>193.53</v>
+        <v>128.91</v>
       </c>
       <c r="K14" t="n">
-        <v>70.08</v>
+        <v>46.68</v>
       </c>
       <c r="L14" t="n">
-        <v>205.82</v>
+        <v>137.1</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>174.46</v>
+        <v>116.56</v>
       </c>
       <c r="K15" t="n">
-        <v>-33.57</v>
+        <v>-22.43</v>
       </c>
       <c r="L15" t="n">
-        <v>177.66</v>
+        <v>118.7</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-311.49</v>
+        <v>-192.75</v>
       </c>
       <c r="K16" t="n">
-        <v>86.54000000000001</v>
+        <v>53.55</v>
       </c>
       <c r="L16" t="n">
-        <v>323.29</v>
+        <v>200.05</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>172.75</v>
+        <v>113.71</v>
       </c>
       <c r="K17" t="n">
-        <v>232.82</v>
+        <v>153.25</v>
       </c>
       <c r="L17" t="n">
-        <v>289.91</v>
+        <v>190.83</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>-402.06</v>
+        <v>-260.7</v>
       </c>
       <c r="K18" t="n">
-        <v>-208.82</v>
+        <v>-135.4</v>
       </c>
       <c r="L18" t="n">
-        <v>453.06</v>
+        <v>293.77</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>17</v>
       </c>
       <c r="J19" t="n">
-        <v>372.32</v>
+        <v>216.91</v>
       </c>
       <c r="K19" t="n">
-        <v>317.77</v>
+        <v>185.13</v>
       </c>
       <c r="L19" t="n">
-        <v>489.49</v>
+        <v>285.17</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-311.58</v>
+        <v>-157.49</v>
       </c>
       <c r="K20" t="n">
-        <v>-280.75</v>
+        <v>-141.91</v>
       </c>
       <c r="L20" t="n">
-        <v>419.41</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>122.64</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-285.26</v>
+        <v>-152.92</v>
       </c>
       <c r="L21" t="n">
-        <v>310.51</v>
+        <v>166.45</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>-270</v>
+        <v>-156.66</v>
       </c>
       <c r="K22" t="n">
-        <v>134.28</v>
+        <v>77.91</v>
       </c>
       <c r="L22" t="n">
-        <v>301.55</v>
+        <v>174.96</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-400.71</v>
+        <v>-206.94</v>
       </c>
       <c r="K23" t="n">
-        <v>247.82</v>
+        <v>127.98</v>
       </c>
       <c r="L23" t="n">
-        <v>471.15</v>
+        <v>243.32</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>848.09</v>
+        <v>374.2</v>
       </c>
       <c r="K24" t="n">
-        <v>-834.13</v>
+        <v>-368.04</v>
       </c>
       <c r="L24" t="n">
-        <v>1189.55</v>
+        <v>524.86</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>74.09999999999999</v>
+        <v>37.45</v>
       </c>
       <c r="K25" t="n">
-        <v>-356.11</v>
+        <v>-179.98</v>
       </c>
       <c r="L25" t="n">
-        <v>363.74</v>
+        <v>183.84</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-979.47</v>
+        <v>-443.21</v>
       </c>
       <c r="K26" t="n">
-        <v>-281.43</v>
+        <v>-127.35</v>
       </c>
       <c r="L26" t="n">
-        <v>1019.1</v>
+        <v>461.14</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>1080.94</v>
+        <v>487.93</v>
       </c>
       <c r="K27" t="n">
-        <v>211.08</v>
+        <v>95.28</v>
       </c>
       <c r="L27" t="n">
-        <v>1101.36</v>
+        <v>497.15</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-405.94</v>
+        <v>-165.87</v>
       </c>
       <c r="K28" t="n">
-        <v>1188.57</v>
+        <v>485.66</v>
       </c>
       <c r="L28" t="n">
-        <v>1255.98</v>
+        <v>513.21</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>116.4</v>
+        <v>72.83</v>
       </c>
       <c r="K29" t="n">
-        <v>-173.49</v>
+        <v>-108.55</v>
       </c>
       <c r="L29" t="n">
-        <v>208.92</v>
+        <v>130.72</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>81.53</v>
+        <v>49.7</v>
       </c>
       <c r="K30" t="n">
-        <v>-371.3</v>
+        <v>-226.33</v>
       </c>
       <c r="L30" t="n">
-        <v>380.15</v>
+        <v>231.72</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>296.06</v>
+        <v>190.55</v>
       </c>
       <c r="K31" t="n">
-        <v>-168.07</v>
+        <v>-108.17</v>
       </c>
       <c r="L31" t="n">
-        <v>340.44</v>
+        <v>219.11</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>190.29</v>
+        <v>125.9</v>
       </c>
       <c r="K32" t="n">
-        <v>30.05</v>
+        <v>19.88</v>
       </c>
       <c r="L32" t="n">
-        <v>192.65</v>
+        <v>127.46</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-448.59</v>
+        <v>-254.01</v>
       </c>
       <c r="K33" t="n">
-        <v>-335.26</v>
+        <v>-189.84</v>
       </c>
       <c r="L33" t="n">
-        <v>560.03</v>
+        <v>317.11</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>348.17</v>
+        <v>219.53</v>
       </c>
       <c r="K34" t="n">
-        <v>187.56</v>
+        <v>118.26</v>
       </c>
       <c r="L34" t="n">
-        <v>395.48</v>
+        <v>249.35</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>400.67</v>
+        <v>236.42</v>
       </c>
       <c r="K35" t="n">
-        <v>53</v>
+        <v>31.27</v>
       </c>
       <c r="L35" t="n">
-        <v>404.16</v>
+        <v>238.48</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>431.22</v>
+        <v>253</v>
       </c>
       <c r="K36" t="n">
-        <v>-231.39</v>
+        <v>-135.76</v>
       </c>
       <c r="L36" t="n">
-        <v>489.38</v>
+        <v>287.12</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-143.61</v>
+        <v>-78.25</v>
       </c>
       <c r="K37" t="n">
-        <v>-325.2</v>
+        <v>-177.19</v>
       </c>
       <c r="L37" t="n">
-        <v>355.5</v>
+        <v>193.69</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>366.36</v>
+        <v>189.03</v>
       </c>
       <c r="K38" t="n">
-        <v>-471.98</v>
+        <v>-243.52</v>
       </c>
       <c r="L38" t="n">
-        <v>597.48</v>
+        <v>308.28</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-883.96</v>
+        <v>-433.13</v>
       </c>
       <c r="K39" t="n">
-        <v>-65.13</v>
+        <v>-31.91</v>
       </c>
       <c r="L39" t="n">
-        <v>886.35</v>
+        <v>434.3</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>1000.02</v>
+        <v>432.71</v>
       </c>
       <c r="K40" t="n">
-        <v>114.03</v>
+        <v>49.34</v>
       </c>
       <c r="L40" t="n">
-        <v>1006.5</v>
+        <v>435.51</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-1169.46</v>
+        <v>-521.54</v>
       </c>
       <c r="K41" t="n">
-        <v>493.66</v>
+        <v>220.16</v>
       </c>
       <c r="L41" t="n">
-        <v>1269.38</v>
+        <v>566.1</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>248.65</v>
+        <v>117.27</v>
       </c>
       <c r="K42" t="n">
-        <v>374.76</v>
+        <v>176.75</v>
       </c>
       <c r="L42" t="n">
-        <v>449.75</v>
+        <v>212.12</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>852.24</v>
+        <v>379.54</v>
       </c>
       <c r="K43" t="n">
-        <v>-44.85</v>
+        <v>-19.97</v>
       </c>
       <c r="L43" t="n">
-        <v>853.42</v>
+        <v>380.07</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>379.19</v>
+        <v>225.42</v>
       </c>
       <c r="K44" t="n">
-        <v>169.51</v>
+        <v>100.77</v>
       </c>
       <c r="L44" t="n">
-        <v>415.35</v>
+        <v>246.91</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-225.35</v>
+        <v>-133.08</v>
       </c>
       <c r="K45" t="n">
-        <v>-279.66</v>
+        <v>-165.15</v>
       </c>
       <c r="L45" t="n">
-        <v>359.15</v>
+        <v>212.09</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>283.74</v>
+        <v>188.53</v>
       </c>
       <c r="K46" t="n">
-        <v>-31.72</v>
+        <v>-21.07</v>
       </c>
       <c r="L46" t="n">
-        <v>285.51</v>
+        <v>189.71</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>36.81</v>
+        <v>24.13</v>
       </c>
       <c r="K47" t="n">
-        <v>-168.43</v>
+        <v>-110.41</v>
       </c>
       <c r="L47" t="n">
-        <v>172.41</v>
+        <v>113.02</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>409.41</v>
+        <v>270.27</v>
       </c>
       <c r="K48" t="n">
-        <v>133.32</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>430.57</v>
+        <v>284.24</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>157.15</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>411.55</v>
+        <v>245.62</v>
       </c>
       <c r="L49" t="n">
-        <v>440.54</v>
+        <v>262.91</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-342.88</v>
+        <v>-190.86</v>
       </c>
       <c r="K50" t="n">
-        <v>301.45</v>
+        <v>167.8</v>
       </c>
       <c r="L50" t="n">
-        <v>456.55</v>
+        <v>254.14</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-346.38</v>
+        <v>-199.81</v>
       </c>
       <c r="K51" t="n">
-        <v>331.11</v>
+        <v>191</v>
       </c>
       <c r="L51" t="n">
-        <v>479.18</v>
+        <v>276.42</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>484.56</v>
+        <v>267.46</v>
       </c>
       <c r="K52" t="n">
-        <v>57.65</v>
+        <v>31.82</v>
       </c>
       <c r="L52" t="n">
-        <v>487.98</v>
+        <v>269.35</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>835.2</v>
+        <v>385.32</v>
       </c>
       <c r="K53" t="n">
-        <v>49.84</v>
+        <v>22.99</v>
       </c>
       <c r="L53" t="n">
-        <v>836.6799999999999</v>
+        <v>386</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>652.6</v>
+        <v>300.35</v>
       </c>
       <c r="K54" t="n">
-        <v>-574.83</v>
+        <v>-264.56</v>
       </c>
       <c r="L54" t="n">
-        <v>869.66</v>
+        <v>400.25</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>645.64</v>
+        <v>280.68</v>
       </c>
       <c r="K55" t="n">
-        <v>-1122.62</v>
+        <v>-488.03</v>
       </c>
       <c r="L55" t="n">
-        <v>1295.04</v>
+        <v>562.99</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>1341.92</v>
+        <v>604.37</v>
       </c>
       <c r="K56" t="n">
-        <v>687.26</v>
+        <v>309.53</v>
       </c>
       <c r="L56" t="n">
-        <v>1507.67</v>
+        <v>679.02</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>359.78</v>
+        <v>148.38</v>
       </c>
       <c r="K57" t="n">
-        <v>1243.1</v>
+        <v>512.6799999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>1294.12</v>
+        <v>533.72</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>117.03</v>
+        <v>49</v>
       </c>
       <c r="K58" t="n">
-        <v>1010.7</v>
+        <v>423.16</v>
       </c>
       <c r="L58" t="n">
-        <v>1017.45</v>
+        <v>425.98</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>152.15</v>
+        <v>90.63</v>
       </c>
       <c r="K59" t="n">
-        <v>-239.18</v>
+        <v>-142.47</v>
       </c>
       <c r="L59" t="n">
-        <v>283.48</v>
+        <v>168.86</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>-322.37</v>
+        <v>-194.9</v>
       </c>
       <c r="K60" t="n">
-        <v>373.89</v>
+        <v>226.05</v>
       </c>
       <c r="L60" t="n">
-        <v>493.68</v>
+        <v>298.48</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-180.78</v>
+        <v>-125.65</v>
       </c>
       <c r="K61" t="n">
-        <v>-42.68</v>
+        <v>-29.67</v>
       </c>
       <c r="L61" t="n">
-        <v>185.75</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-401.39</v>
+        <v>-243.71</v>
       </c>
       <c r="K62" t="n">
-        <v>283.96</v>
+        <v>172.4</v>
       </c>
       <c r="L62" t="n">
-        <v>491.68</v>
+        <v>298.52</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>219.55</v>
+        <v>129.86</v>
       </c>
       <c r="K63" t="n">
-        <v>-79.73999999999999</v>
+        <v>-47.16</v>
       </c>
       <c r="L63" t="n">
-        <v>233.59</v>
+        <v>138.15</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-188.8</v>
+        <v>-115.76</v>
       </c>
       <c r="K64" t="n">
-        <v>-356.66</v>
+        <v>-218.67</v>
       </c>
       <c r="L64" t="n">
-        <v>403.55</v>
+        <v>247.42</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>174.19</v>
+        <v>86.02</v>
       </c>
       <c r="K65" t="n">
-        <v>600.27</v>
+        <v>296.41</v>
       </c>
       <c r="L65" t="n">
-        <v>625.03</v>
+        <v>308.64</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-142.44</v>
+        <v>-75.68000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>-554.23</v>
+        <v>-294.49</v>
       </c>
       <c r="L66" t="n">
-        <v>572.24</v>
+        <v>304.06</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>687.0700000000001</v>
+        <v>350.42</v>
       </c>
       <c r="K67" t="n">
-        <v>-302.88</v>
+        <v>-154.47</v>
       </c>
       <c r="L67" t="n">
-        <v>750.87</v>
+        <v>382.96</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-827.38</v>
+        <v>-368.58</v>
       </c>
       <c r="K68" t="n">
-        <v>-396.22</v>
+        <v>-176.51</v>
       </c>
       <c r="L68" t="n">
-        <v>917.36</v>
+        <v>408.66</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>-648.3200000000001</v>
+        <v>-312.25</v>
       </c>
       <c r="K69" t="n">
-        <v>-187</v>
+        <v>-90.06999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>674.75</v>
+        <v>324.98</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-432.8</v>
+        <v>-219.78</v>
       </c>
       <c r="K70" t="n">
-        <v>-130.75</v>
+        <v>-66.40000000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>452.12</v>
+        <v>229.59</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>18.3</v>
+        <v>7.9</v>
       </c>
       <c r="K71" t="n">
-        <v>-559.9299999999999</v>
+        <v>-241.57</v>
       </c>
       <c r="L71" t="n">
-        <v>560.23</v>
+        <v>241.7</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>-39.05</v>
+        <v>-15.6</v>
       </c>
       <c r="K72" t="n">
-        <v>1307.12</v>
+        <v>522.09</v>
       </c>
       <c r="L72" t="n">
-        <v>1307.71</v>
+        <v>522.33</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-1661.71</v>
+        <v>-718.21</v>
       </c>
       <c r="K73" t="n">
-        <v>627.11</v>
+        <v>271.04</v>
       </c>
       <c r="L73" t="n">
-        <v>1776.1</v>
+        <v>767.65</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-306.2</v>
+        <v>-207.69</v>
       </c>
       <c r="K74" t="n">
-        <v>-33.67</v>
+        <v>-22.83</v>
       </c>
       <c r="L74" t="n">
-        <v>308.05</v>
+        <v>208.94</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-30.07</v>
+        <v>-19.88</v>
       </c>
       <c r="K75" t="n">
-        <v>234.05</v>
+        <v>154.7</v>
       </c>
       <c r="L75" t="n">
-        <v>235.97</v>
+        <v>155.97</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-218.59</v>
+        <v>-152.27</v>
       </c>
       <c r="K76" t="n">
-        <v>-197.19</v>
+        <v>-137.36</v>
       </c>
       <c r="L76" t="n">
-        <v>294.39</v>
+        <v>205.07</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>-354.9</v>
+        <v>-219.74</v>
       </c>
       <c r="K77" t="n">
-        <v>382.66</v>
+        <v>236.93</v>
       </c>
       <c r="L77" t="n">
-        <v>521.9</v>
+        <v>323.14</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-478.95</v>
+        <v>-266.07</v>
       </c>
       <c r="K78" t="n">
-        <v>-355.03</v>
+        <v>-197.22</v>
       </c>
       <c r="L78" t="n">
-        <v>596.1900000000001</v>
+        <v>331.19</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>377.21</v>
+        <v>220.82</v>
       </c>
       <c r="K79" t="n">
-        <v>-49.64</v>
+        <v>-29.06</v>
       </c>
       <c r="L79" t="n">
-        <v>380.47</v>
+        <v>222.73</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>357.8</v>
+        <v>193.46</v>
       </c>
       <c r="K80" t="n">
-        <v>329.13</v>
+        <v>177.96</v>
       </c>
       <c r="L80" t="n">
-        <v>486.16</v>
+        <v>262.86</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>305.37</v>
+        <v>153.38</v>
       </c>
       <c r="K81" t="n">
-        <v>-571.33</v>
+        <v>-286.97</v>
       </c>
       <c r="L81" t="n">
-        <v>647.8200000000001</v>
+        <v>325.39</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-510.64</v>
+        <v>-266.97</v>
       </c>
       <c r="K82" t="n">
-        <v>-496.71</v>
+        <v>-259.68</v>
       </c>
       <c r="L82" t="n">
-        <v>712.37</v>
+        <v>372.43</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>-830.96</v>
+        <v>-371.45</v>
       </c>
       <c r="K83" t="n">
-        <v>186.29</v>
+        <v>83.28</v>
       </c>
       <c r="L83" t="n">
-        <v>851.59</v>
+        <v>380.67</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-227.38</v>
+        <v>-105.4</v>
       </c>
       <c r="K84" t="n">
-        <v>758.45</v>
+        <v>351.59</v>
       </c>
       <c r="L84" t="n">
-        <v>791.8</v>
+        <v>367.05</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-151.51</v>
+        <v>-72.95</v>
       </c>
       <c r="K85" t="n">
-        <v>-849.75</v>
+        <v>-409.16</v>
       </c>
       <c r="L85" t="n">
-        <v>863.15</v>
+        <v>415.62</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-631.3099999999999</v>
+        <v>-253.22</v>
       </c>
       <c r="K86" t="n">
-        <v>-577.76</v>
+        <v>-231.73</v>
       </c>
       <c r="L86" t="n">
-        <v>855.78</v>
+        <v>343.25</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>833.9400000000001</v>
+        <v>376.01</v>
       </c>
       <c r="K87" t="n">
-        <v>-793.73</v>
+        <v>-357.88</v>
       </c>
       <c r="L87" t="n">
-        <v>1151.29</v>
+        <v>519.1</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-773.25</v>
+        <v>-302.89</v>
       </c>
       <c r="K88" t="n">
-        <v>-886.3200000000001</v>
+        <v>-347.18</v>
       </c>
       <c r="L88" t="n">
-        <v>1176.21</v>
+        <v>460.73</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-29.xlsx
+++ b/output/2025-09-29.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>128.91</v>
+        <v>136.59</v>
       </c>
       <c r="K14" t="n">
-        <v>46.68</v>
+        <v>49.46</v>
       </c>
       <c r="L14" t="n">
-        <v>137.1</v>
+        <v>145.27</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>116.56</v>
+        <v>125.63</v>
       </c>
       <c r="K15" t="n">
-        <v>-22.43</v>
+        <v>-24.18</v>
       </c>
       <c r="L15" t="n">
-        <v>118.7</v>
+        <v>127.94</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-192.75</v>
+        <v>-208.55</v>
       </c>
       <c r="K16" t="n">
-        <v>53.55</v>
+        <v>57.94</v>
       </c>
       <c r="L16" t="n">
-        <v>200.05</v>
+        <v>216.45</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>113.71</v>
+        <v>122.73</v>
       </c>
       <c r="K17" t="n">
-        <v>153.25</v>
+        <v>165.4</v>
       </c>
       <c r="L17" t="n">
-        <v>190.83</v>
+        <v>205.96</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>-260.7</v>
+        <v>-284.09</v>
       </c>
       <c r="K18" t="n">
-        <v>-135.4</v>
+        <v>-147.55</v>
       </c>
       <c r="L18" t="n">
-        <v>293.77</v>
+        <v>320.12</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>17</v>
       </c>
       <c r="J19" t="n">
-        <v>216.91</v>
+        <v>239.07</v>
       </c>
       <c r="K19" t="n">
-        <v>185.13</v>
+        <v>204.05</v>
       </c>
       <c r="L19" t="n">
-        <v>285.17</v>
+        <v>314.31</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-157.49</v>
+        <v>-181.52</v>
       </c>
       <c r="K20" t="n">
-        <v>-141.91</v>
+        <v>-163.56</v>
       </c>
       <c r="L20" t="n">
-        <v>212</v>
+        <v>244.34</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>65.73999999999999</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-152.92</v>
+        <v>-173.76</v>
       </c>
       <c r="L21" t="n">
-        <v>166.45</v>
+        <v>189.14</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>-156.66</v>
+        <v>-176.46</v>
       </c>
       <c r="K22" t="n">
-        <v>77.91</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>174.96</v>
+        <v>197.08</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-206.94</v>
+        <v>-241.02</v>
       </c>
       <c r="K23" t="n">
-        <v>127.98</v>
+        <v>149.06</v>
       </c>
       <c r="L23" t="n">
-        <v>243.32</v>
+        <v>283.39</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>374.2</v>
+        <v>444.76</v>
       </c>
       <c r="K24" t="n">
-        <v>-368.04</v>
+        <v>-437.44</v>
       </c>
       <c r="L24" t="n">
-        <v>524.86</v>
+        <v>623.83</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>37.45</v>
+        <v>43.19</v>
       </c>
       <c r="K25" t="n">
-        <v>-179.98</v>
+        <v>-207.57</v>
       </c>
       <c r="L25" t="n">
-        <v>183.84</v>
+        <v>212.02</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-443.21</v>
+        <v>-523.87</v>
       </c>
       <c r="K26" t="n">
-        <v>-127.35</v>
+        <v>-150.52</v>
       </c>
       <c r="L26" t="n">
-        <v>461.14</v>
+        <v>545.0599999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>487.93</v>
+        <v>578.39</v>
       </c>
       <c r="K27" t="n">
-        <v>95.28</v>
+        <v>112.94</v>
       </c>
       <c r="L27" t="n">
-        <v>497.15</v>
+        <v>589.3099999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-165.87</v>
+        <v>-203.67</v>
       </c>
       <c r="K28" t="n">
-        <v>485.66</v>
+        <v>596.34</v>
       </c>
       <c r="L28" t="n">
-        <v>513.21</v>
+        <v>630.16</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>72.83</v>
+        <v>78.78</v>
       </c>
       <c r="K29" t="n">
-        <v>-108.55</v>
+        <v>-117.41</v>
       </c>
       <c r="L29" t="n">
-        <v>130.72</v>
+        <v>141.39</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>49.7</v>
+        <v>54.59</v>
       </c>
       <c r="K30" t="n">
-        <v>-226.33</v>
+        <v>-248.63</v>
       </c>
       <c r="L30" t="n">
-        <v>231.72</v>
+        <v>254.55</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>190.55</v>
+        <v>207</v>
       </c>
       <c r="K31" t="n">
-        <v>-108.17</v>
+        <v>-117.51</v>
       </c>
       <c r="L31" t="n">
-        <v>219.11</v>
+        <v>238.03</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>125.9</v>
+        <v>135.26</v>
       </c>
       <c r="K32" t="n">
-        <v>19.88</v>
+        <v>21.36</v>
       </c>
       <c r="L32" t="n">
-        <v>127.46</v>
+        <v>136.93</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-254.01</v>
+        <v>-280.24</v>
       </c>
       <c r="K33" t="n">
-        <v>-189.84</v>
+        <v>-209.44</v>
       </c>
       <c r="L33" t="n">
-        <v>317.11</v>
+        <v>349.85</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>219.53</v>
+        <v>237.42</v>
       </c>
       <c r="K34" t="n">
-        <v>118.26</v>
+        <v>127.89</v>
       </c>
       <c r="L34" t="n">
-        <v>249.35</v>
+        <v>269.67</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>236.42</v>
+        <v>263.36</v>
       </c>
       <c r="K35" t="n">
-        <v>31.27</v>
+        <v>34.83</v>
       </c>
       <c r="L35" t="n">
-        <v>238.48</v>
+        <v>265.65</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>253</v>
+        <v>285.74</v>
       </c>
       <c r="K36" t="n">
-        <v>-135.76</v>
+        <v>-153.33</v>
       </c>
       <c r="L36" t="n">
-        <v>287.12</v>
+        <v>324.28</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-78.25</v>
+        <v>-89.69</v>
       </c>
       <c r="K37" t="n">
-        <v>-177.19</v>
+        <v>-203.1</v>
       </c>
       <c r="L37" t="n">
-        <v>193.69</v>
+        <v>222.02</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>189.03</v>
+        <v>217.11</v>
       </c>
       <c r="K38" t="n">
-        <v>-243.52</v>
+        <v>-279.7</v>
       </c>
       <c r="L38" t="n">
-        <v>308.28</v>
+        <v>354.08</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-433.13</v>
+        <v>-501.92</v>
       </c>
       <c r="K39" t="n">
-        <v>-31.91</v>
+        <v>-36.98</v>
       </c>
       <c r="L39" t="n">
-        <v>434.3</v>
+        <v>503.28</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>432.71</v>
+        <v>509.35</v>
       </c>
       <c r="K40" t="n">
-        <v>49.34</v>
+        <v>58.08</v>
       </c>
       <c r="L40" t="n">
-        <v>435.51</v>
+        <v>512.65</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-521.54</v>
+        <v>-619.28</v>
       </c>
       <c r="K41" t="n">
-        <v>220.16</v>
+        <v>261.41</v>
       </c>
       <c r="L41" t="n">
-        <v>566.1</v>
+        <v>672.1900000000001</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>117.27</v>
+        <v>139.55</v>
       </c>
       <c r="K42" t="n">
-        <v>176.75</v>
+        <v>210.33</v>
       </c>
       <c r="L42" t="n">
-        <v>212.12</v>
+        <v>252.42</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>379.54</v>
+        <v>450.16</v>
       </c>
       <c r="K43" t="n">
-        <v>-19.97</v>
+        <v>-23.69</v>
       </c>
       <c r="L43" t="n">
-        <v>380.07</v>
+        <v>450.78</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>225.42</v>
+        <v>248.07</v>
       </c>
       <c r="K44" t="n">
-        <v>100.77</v>
+        <v>110.9</v>
       </c>
       <c r="L44" t="n">
-        <v>246.91</v>
+        <v>271.73</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-133.08</v>
+        <v>-146.24</v>
       </c>
       <c r="K45" t="n">
-        <v>-165.15</v>
+        <v>-181.48</v>
       </c>
       <c r="L45" t="n">
-        <v>212.09</v>
+        <v>233.07</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>188.53</v>
+        <v>202.86</v>
       </c>
       <c r="K46" t="n">
-        <v>-21.07</v>
+        <v>-22.68</v>
       </c>
       <c r="L46" t="n">
-        <v>189.71</v>
+        <v>204.13</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>24.13</v>
+        <v>25.87</v>
       </c>
       <c r="K47" t="n">
-        <v>-110.41</v>
+        <v>-118.36</v>
       </c>
       <c r="L47" t="n">
-        <v>113.02</v>
+        <v>121.15</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>270.27</v>
+        <v>292.47</v>
       </c>
       <c r="K48" t="n">
-        <v>88.01000000000001</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>284.24</v>
+        <v>307.59</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>93.79000000000001</v>
+        <v>102.26</v>
       </c>
       <c r="K49" t="n">
-        <v>245.62</v>
+        <v>267.82</v>
       </c>
       <c r="L49" t="n">
-        <v>262.91</v>
+        <v>286.68</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-190.86</v>
+        <v>-213.08</v>
       </c>
       <c r="K50" t="n">
-        <v>167.8</v>
+        <v>187.33</v>
       </c>
       <c r="L50" t="n">
-        <v>254.14</v>
+        <v>283.71</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-199.81</v>
+        <v>-222.31</v>
       </c>
       <c r="K51" t="n">
-        <v>191</v>
+        <v>212.51</v>
       </c>
       <c r="L51" t="n">
-        <v>276.42</v>
+        <v>307.54</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>267.46</v>
+        <v>302.04</v>
       </c>
       <c r="K52" t="n">
-        <v>31.82</v>
+        <v>35.93</v>
       </c>
       <c r="L52" t="n">
-        <v>269.35</v>
+        <v>304.17</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>385.32</v>
+        <v>448.29</v>
       </c>
       <c r="K53" t="n">
-        <v>22.99</v>
+        <v>26.75</v>
       </c>
       <c r="L53" t="n">
-        <v>386</v>
+        <v>449.09</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>300.35</v>
+        <v>352.3</v>
       </c>
       <c r="K54" t="n">
-        <v>-264.56</v>
+        <v>-310.32</v>
       </c>
       <c r="L54" t="n">
-        <v>400.25</v>
+        <v>469.48</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>280.68</v>
+        <v>332.27</v>
       </c>
       <c r="K55" t="n">
-        <v>-488.03</v>
+        <v>-577.74</v>
       </c>
       <c r="L55" t="n">
-        <v>562.99</v>
+        <v>666.48</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>604.37</v>
+        <v>720.91</v>
       </c>
       <c r="K56" t="n">
-        <v>309.53</v>
+        <v>369.21</v>
       </c>
       <c r="L56" t="n">
-        <v>679.02</v>
+        <v>809.96</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>148.38</v>
+        <v>178.98</v>
       </c>
       <c r="K57" t="n">
-        <v>512.6799999999999</v>
+        <v>618.41</v>
       </c>
       <c r="L57" t="n">
-        <v>533.72</v>
+        <v>643.79</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>49</v>
+        <v>59.78</v>
       </c>
       <c r="K58" t="n">
-        <v>423.16</v>
+        <v>516.28</v>
       </c>
       <c r="L58" t="n">
-        <v>425.98</v>
+        <v>519.73</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>90.63</v>
+        <v>100.09</v>
       </c>
       <c r="K59" t="n">
-        <v>-142.47</v>
+        <v>-157.35</v>
       </c>
       <c r="L59" t="n">
-        <v>168.86</v>
+        <v>186.49</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>-194.9</v>
+        <v>-213.6</v>
       </c>
       <c r="K60" t="n">
-        <v>226.05</v>
+        <v>247.74</v>
       </c>
       <c r="L60" t="n">
-        <v>298.48</v>
+        <v>327.11</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-125.65</v>
+        <v>-133.89</v>
       </c>
       <c r="K61" t="n">
-        <v>-29.67</v>
+        <v>-31.61</v>
       </c>
       <c r="L61" t="n">
-        <v>129.1</v>
+        <v>137.57</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-243.71</v>
+        <v>-265.47</v>
       </c>
       <c r="K62" t="n">
-        <v>172.4</v>
+        <v>187.8</v>
       </c>
       <c r="L62" t="n">
-        <v>298.52</v>
+        <v>325.19</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>129.86</v>
+        <v>141.88</v>
       </c>
       <c r="K63" t="n">
-        <v>-47.16</v>
+        <v>-51.53</v>
       </c>
       <c r="L63" t="n">
-        <v>138.15</v>
+        <v>150.94</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-115.76</v>
+        <v>-126.69</v>
       </c>
       <c r="K64" t="n">
-        <v>-218.67</v>
+        <v>-239.34</v>
       </c>
       <c r="L64" t="n">
-        <v>247.42</v>
+        <v>270.8</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>86.02</v>
+        <v>98</v>
       </c>
       <c r="K65" t="n">
-        <v>296.41</v>
+        <v>337.72</v>
       </c>
       <c r="L65" t="n">
-        <v>308.64</v>
+        <v>351.66</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-75.68000000000001</v>
+        <v>-86.13</v>
       </c>
       <c r="K66" t="n">
-        <v>-294.49</v>
+        <v>-335.15</v>
       </c>
       <c r="L66" t="n">
-        <v>304.06</v>
+        <v>346.04</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>350.42</v>
+        <v>402.46</v>
       </c>
       <c r="K67" t="n">
-        <v>-154.47</v>
+        <v>-177.41</v>
       </c>
       <c r="L67" t="n">
-        <v>382.96</v>
+        <v>439.83</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-368.58</v>
+        <v>-432.48</v>
       </c>
       <c r="K68" t="n">
-        <v>-176.51</v>
+        <v>-207.11</v>
       </c>
       <c r="L68" t="n">
-        <v>408.66</v>
+        <v>479.52</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>-312.25</v>
+        <v>-364.95</v>
       </c>
       <c r="K69" t="n">
-        <v>-90.06999999999999</v>
+        <v>-105.27</v>
       </c>
       <c r="L69" t="n">
-        <v>324.98</v>
+        <v>379.83</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-219.78</v>
+        <v>-251.84</v>
       </c>
       <c r="K70" t="n">
-        <v>-66.40000000000001</v>
+        <v>-76.08</v>
       </c>
       <c r="L70" t="n">
-        <v>229.59</v>
+        <v>263.08</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>7.9</v>
+        <v>9.42</v>
       </c>
       <c r="K71" t="n">
-        <v>-241.57</v>
+        <v>-288.13</v>
       </c>
       <c r="L71" t="n">
-        <v>241.7</v>
+        <v>288.28</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>-15.6</v>
+        <v>-18.73</v>
       </c>
       <c r="K72" t="n">
-        <v>522.09</v>
+        <v>626.9400000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>522.33</v>
+        <v>627.21</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-718.21</v>
+        <v>-851.13</v>
       </c>
       <c r="K73" t="n">
-        <v>271.04</v>
+        <v>321.2</v>
       </c>
       <c r="L73" t="n">
-        <v>767.65</v>
+        <v>909.72</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-207.69</v>
+        <v>-224.82</v>
       </c>
       <c r="K74" t="n">
-        <v>-22.83</v>
+        <v>-24.72</v>
       </c>
       <c r="L74" t="n">
-        <v>208.94</v>
+        <v>226.17</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-19.88</v>
+        <v>-21.49</v>
       </c>
       <c r="K75" t="n">
-        <v>154.7</v>
+        <v>167.25</v>
       </c>
       <c r="L75" t="n">
-        <v>155.97</v>
+        <v>168.63</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-152.27</v>
+        <v>-162.41</v>
       </c>
       <c r="K76" t="n">
-        <v>-137.36</v>
+        <v>-146.51</v>
       </c>
       <c r="L76" t="n">
-        <v>205.07</v>
+        <v>218.73</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>-219.74</v>
+        <v>-237.81</v>
       </c>
       <c r="K77" t="n">
-        <v>236.93</v>
+        <v>256.41</v>
       </c>
       <c r="L77" t="n">
-        <v>323.14</v>
+        <v>349.71</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-266.07</v>
+        <v>-297.54</v>
       </c>
       <c r="K78" t="n">
-        <v>-197.22</v>
+        <v>-220.55</v>
       </c>
       <c r="L78" t="n">
-        <v>331.19</v>
+        <v>370.37</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>220.82</v>
+        <v>242.47</v>
       </c>
       <c r="K79" t="n">
-        <v>-29.06</v>
+        <v>-31.91</v>
       </c>
       <c r="L79" t="n">
-        <v>222.73</v>
+        <v>244.56</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>193.46</v>
+        <v>216.47</v>
       </c>
       <c r="K80" t="n">
-        <v>177.96</v>
+        <v>199.12</v>
       </c>
       <c r="L80" t="n">
-        <v>262.86</v>
+        <v>294.12</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>153.38</v>
+        <v>175.01</v>
       </c>
       <c r="K81" t="n">
-        <v>-286.97</v>
+        <v>-327.44</v>
       </c>
       <c r="L81" t="n">
-        <v>325.39</v>
+        <v>371.27</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-266.97</v>
+        <v>-302.95</v>
       </c>
       <c r="K82" t="n">
-        <v>-259.68</v>
+        <v>-294.69</v>
       </c>
       <c r="L82" t="n">
-        <v>372.43</v>
+        <v>422.64</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>-371.45</v>
+        <v>-437.8</v>
       </c>
       <c r="K83" t="n">
-        <v>83.28</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>380.67</v>
+        <v>448.67</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-105.4</v>
+        <v>-124.06</v>
       </c>
       <c r="K84" t="n">
-        <v>351.59</v>
+        <v>413.82</v>
       </c>
       <c r="L84" t="n">
-        <v>367.05</v>
+        <v>432.02</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-72.95</v>
+        <v>-84.77</v>
       </c>
       <c r="K85" t="n">
-        <v>-409.16</v>
+        <v>-475.47</v>
       </c>
       <c r="L85" t="n">
-        <v>415.62</v>
+        <v>482.97</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-253.22</v>
+        <v>-310.74</v>
       </c>
       <c r="K86" t="n">
-        <v>-231.73</v>
+        <v>-284.38</v>
       </c>
       <c r="L86" t="n">
-        <v>343.25</v>
+        <v>421.23</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>376.01</v>
+        <v>450.77</v>
       </c>
       <c r="K87" t="n">
-        <v>-357.88</v>
+        <v>-429.03</v>
       </c>
       <c r="L87" t="n">
-        <v>519.1</v>
+        <v>622.3099999999999</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-302.89</v>
+        <v>-365.97</v>
       </c>
       <c r="K88" t="n">
-        <v>-347.18</v>
+        <v>-419.48</v>
       </c>
       <c r="L88" t="n">
-        <v>460.73</v>
+        <v>556.6799999999999</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-29.xlsx
+++ b/output/2025-09-29.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.34</v>
+        <v>4.38</v>
       </c>
       <c r="F14" t="n">
-        <v>13.19</v>
+        <v>12.54</v>
       </c>
       <c r="G14" t="n">
-        <v>88.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>136.59</v>
+        <v>-82.48999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>49.46</v>
+        <v>57.69</v>
       </c>
       <c r="L14" t="n">
-        <v>145.27</v>
+        <v>100.66</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:14:44</t>
+          <t>07:15:20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2</v>
+        <v>5.19</v>
       </c>
       <c r="F15" t="n">
-        <v>12.63</v>
+        <v>12.49</v>
       </c>
       <c r="G15" t="n">
-        <v>85.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>86.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>125.63</v>
+        <v>-45.8</v>
       </c>
       <c r="K15" t="n">
-        <v>-24.18</v>
+        <v>24.2</v>
       </c>
       <c r="L15" t="n">
-        <v>127.94</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:17:05</t>
+          <t>07:16:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.21</v>
+        <v>4.67</v>
       </c>
       <c r="F16" t="n">
-        <v>12.09</v>
+        <v>13.04</v>
       </c>
       <c r="G16" t="n">
-        <v>78.90000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="H16" t="n">
-        <v>79.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-208.55</v>
+        <v>98.84</v>
       </c>
       <c r="K16" t="n">
-        <v>57.94</v>
+        <v>-34.23</v>
       </c>
       <c r="L16" t="n">
-        <v>216.45</v>
+        <v>104.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:20:28</t>
+          <t>07:22:06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.06</v>
+        <v>4.5</v>
       </c>
       <c r="F17" t="n">
-        <v>12.79</v>
+        <v>12.72</v>
       </c>
       <c r="G17" t="n">
-        <v>76</v>
+        <v>87.8</v>
       </c>
       <c r="H17" t="n">
-        <v>79.3</v>
+        <v>85.5</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>122.73</v>
+        <v>-32.16</v>
       </c>
       <c r="K17" t="n">
-        <v>165.4</v>
+        <v>-97.38</v>
       </c>
       <c r="L17" t="n">
-        <v>205.96</v>
+        <v>102.56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:21:47</t>
+          <t>07:24:04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.81</v>
+        <v>4.61</v>
       </c>
       <c r="F18" t="n">
-        <v>13.07</v>
+        <v>12.32</v>
       </c>
       <c r="G18" t="n">
-        <v>96.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>81.7</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-284.09</v>
+        <v>-92.72</v>
       </c>
       <c r="K18" t="n">
-        <v>-147.55</v>
+        <v>-43.88</v>
       </c>
       <c r="L18" t="n">
-        <v>320.12</v>
+        <v>102.57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:22:26</t>
+          <t>07:25:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.6</v>
+        <v>4.13</v>
       </c>
       <c r="F19" t="n">
-        <v>12.39</v>
+        <v>14.33</v>
       </c>
       <c r="G19" t="n">
-        <v>94.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>239.07</v>
+        <v>147.86</v>
       </c>
       <c r="K19" t="n">
-        <v>204.05</v>
+        <v>54.46</v>
       </c>
       <c r="L19" t="n">
-        <v>314.31</v>
+        <v>157.57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:27:25</t>
+          <t>07:30:39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.16</v>
+        <v>4.35</v>
       </c>
       <c r="F20" t="n">
-        <v>12.6</v>
+        <v>12.41</v>
       </c>
       <c r="G20" t="n">
-        <v>85.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="H20" t="n">
-        <v>85.5</v>
+        <v>81</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>-181.52</v>
+        <v>31.66</v>
       </c>
       <c r="K20" t="n">
-        <v>-163.56</v>
+        <v>-108.02</v>
       </c>
       <c r="L20" t="n">
-        <v>244.34</v>
+        <v>112.56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:28:57</t>
+          <t>07:31:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.87</v>
+        <v>4.57</v>
       </c>
       <c r="F21" t="n">
-        <v>12.65</v>
+        <v>13.14</v>
       </c>
       <c r="G21" t="n">
-        <v>67.8</v>
+        <v>89.5</v>
       </c>
       <c r="H21" t="n">
         <v>80.8</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>74.70999999999999</v>
+        <v>106.48</v>
       </c>
       <c r="K21" t="n">
-        <v>-173.76</v>
+        <v>119.23</v>
       </c>
       <c r="L21" t="n">
-        <v>189.14</v>
+        <v>159.85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:30:21</t>
+          <t>07:33:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.9</v>
+        <v>4.94</v>
       </c>
       <c r="F22" t="n">
-        <v>12.1</v>
+        <v>12.62</v>
       </c>
       <c r="G22" t="n">
-        <v>80</v>
+        <v>92.5</v>
       </c>
       <c r="H22" t="n">
-        <v>83.90000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-176.46</v>
+        <v>-71.05</v>
       </c>
       <c r="K22" t="n">
-        <v>87.76000000000001</v>
+        <v>-84.76000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>197.08</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:34:23</t>
+          <t>07:37:39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.48</v>
+        <v>4.15</v>
       </c>
       <c r="F23" t="n">
-        <v>12.43</v>
+        <v>12.27</v>
       </c>
       <c r="G23" t="n">
-        <v>86.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>90.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-241.02</v>
+        <v>16.59</v>
       </c>
       <c r="K23" t="n">
-        <v>149.06</v>
+        <v>192.23</v>
       </c>
       <c r="L23" t="n">
-        <v>283.39</v>
+        <v>192.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:35:47</t>
+          <t>07:39:43</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.48</v>
+        <v>4.17</v>
       </c>
       <c r="F24" t="n">
-        <v>11.96</v>
+        <v>12.44</v>
       </c>
       <c r="G24" t="n">
-        <v>97.2</v>
+        <v>78.5</v>
       </c>
       <c r="H24" t="n">
-        <v>86.59999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>444.76</v>
+        <v>156.4</v>
       </c>
       <c r="K24" t="n">
-        <v>-437.44</v>
+        <v>-39.79</v>
       </c>
       <c r="L24" t="n">
-        <v>623.83</v>
+        <v>161.38</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:36:42</t>
+          <t>07:42:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.24</v>
+        <v>5.22</v>
       </c>
       <c r="F25" t="n">
-        <v>12.87</v>
+        <v>12.67</v>
       </c>
       <c r="G25" t="n">
-        <v>81.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>80.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>43.19</v>
+        <v>97.53</v>
       </c>
       <c r="K25" t="n">
-        <v>-207.57</v>
+        <v>139.66</v>
       </c>
       <c r="L25" t="n">
-        <v>212.02</v>
+        <v>170.34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:42:00</t>
+          <t>07:45:35</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.35</v>
+        <v>3.75</v>
       </c>
       <c r="F26" t="n">
-        <v>12.32</v>
+        <v>12.08</v>
       </c>
       <c r="G26" t="n">
-        <v>85.3</v>
+        <v>82</v>
       </c>
       <c r="H26" t="n">
-        <v>77.2</v>
+        <v>75.8</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-523.87</v>
+        <v>-4.02</v>
       </c>
       <c r="K26" t="n">
-        <v>-150.52</v>
+        <v>157.54</v>
       </c>
       <c r="L26" t="n">
-        <v>545.0599999999999</v>
+        <v>157.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:43:57</t>
+          <t>07:46:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.91</v>
+        <v>4.29</v>
       </c>
       <c r="F27" t="n">
-        <v>12.84</v>
+        <v>12.93</v>
       </c>
       <c r="G27" t="n">
-        <v>76.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>79.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>578.39</v>
+        <v>-234.55</v>
       </c>
       <c r="K27" t="n">
-        <v>112.94</v>
+        <v>158.5</v>
       </c>
       <c r="L27" t="n">
-        <v>589.3099999999999</v>
+        <v>283.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:44:32</t>
+          <t>07:48:58</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.45</v>
+        <v>4.35</v>
       </c>
       <c r="F28" t="n">
-        <v>13.15</v>
+        <v>12.49</v>
       </c>
       <c r="G28" t="n">
-        <v>83.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="H28" t="n">
-        <v>92.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-203.67</v>
+        <v>175.68</v>
       </c>
       <c r="K28" t="n">
-        <v>596.34</v>
+        <v>-165.01</v>
       </c>
       <c r="L28" t="n">
-        <v>630.16</v>
+        <v>241.02</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:52:57</t>
+          <t>08:02:13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.53</v>
+        <v>4.79</v>
       </c>
       <c r="F29" t="n">
-        <v>12.44</v>
+        <v>12.43</v>
       </c>
       <c r="G29" t="n">
-        <v>81.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="H29" t="n">
-        <v>78.90000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="I29" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>78.78</v>
+        <v>33.79</v>
       </c>
       <c r="K29" t="n">
-        <v>-117.41</v>
+        <v>32.59</v>
       </c>
       <c r="L29" t="n">
-        <v>141.39</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:54:56</t>
+          <t>08:04:41</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>5.37</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>12.35</v>
+        <v>12.84</v>
       </c>
       <c r="G30" t="n">
-        <v>96.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="H30" t="n">
-        <v>82.90000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>54.59</v>
+        <v>60.88</v>
       </c>
       <c r="K30" t="n">
-        <v>-248.63</v>
+        <v>-58.02</v>
       </c>
       <c r="L30" t="n">
-        <v>254.55</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:57:03</t>
+          <t>08:05:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.46</v>
+        <v>4.98</v>
       </c>
       <c r="F31" t="n">
-        <v>12.9</v>
+        <v>12.16</v>
       </c>
       <c r="G31" t="n">
-        <v>94.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="H31" t="n">
-        <v>86.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>207</v>
+        <v>22.01</v>
       </c>
       <c r="K31" t="n">
-        <v>-117.51</v>
+        <v>-37.86</v>
       </c>
       <c r="L31" t="n">
-        <v>238.03</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:03:32</t>
+          <t>08:10:51</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.99</v>
+        <v>4.44</v>
       </c>
       <c r="F32" t="n">
-        <v>13.51</v>
+        <v>12.85</v>
       </c>
       <c r="G32" t="n">
-        <v>89.7</v>
+        <v>77.7</v>
       </c>
       <c r="H32" t="n">
-        <v>80.7</v>
+        <v>83.8</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>135.26</v>
+        <v>-23.32</v>
       </c>
       <c r="K32" t="n">
-        <v>21.36</v>
+        <v>77.5</v>
       </c>
       <c r="L32" t="n">
-        <v>136.93</v>
+        <v>80.93000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:05:59</t>
+          <t>08:11:56</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.93</v>
+        <v>5.03</v>
       </c>
       <c r="F33" t="n">
-        <v>12.61</v>
+        <v>13.28</v>
       </c>
       <c r="G33" t="n">
-        <v>77</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>82</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-280.24</v>
+        <v>-63.82</v>
       </c>
       <c r="K33" t="n">
-        <v>-209.44</v>
+        <v>3.4</v>
       </c>
       <c r="L33" t="n">
-        <v>349.85</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:07:06</t>
+          <t>08:13:38</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.39</v>
+        <v>5.21</v>
       </c>
       <c r="F34" t="n">
-        <v>12.86</v>
+        <v>12.57</v>
       </c>
       <c r="G34" t="n">
-        <v>78.5</v>
+        <v>95</v>
       </c>
       <c r="H34" t="n">
-        <v>79.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>237.42</v>
+        <v>19.39</v>
       </c>
       <c r="K34" t="n">
-        <v>127.89</v>
+        <v>70.45</v>
       </c>
       <c r="L34" t="n">
-        <v>269.67</v>
+        <v>73.06999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:12:12</t>
+          <t>08:18:34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.23</v>
+        <v>4.38</v>
       </c>
       <c r="F35" t="n">
-        <v>12.02</v>
+        <v>12.41</v>
       </c>
       <c r="G35" t="n">
-        <v>82.8</v>
+        <v>106.8</v>
       </c>
       <c r="H35" t="n">
-        <v>79</v>
+        <v>85.2</v>
       </c>
       <c r="I35" t="n">
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>263.36</v>
+        <v>-81.5</v>
       </c>
       <c r="K35" t="n">
-        <v>34.83</v>
+        <v>-64.44</v>
       </c>
       <c r="L35" t="n">
-        <v>265.65</v>
+        <v>103.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:12:56</t>
+          <t>08:20:57</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="F36" t="n">
-        <v>12.89</v>
+        <v>12.74</v>
       </c>
       <c r="G36" t="n">
-        <v>80.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="H36" t="n">
-        <v>89.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>285.74</v>
+        <v>3.17</v>
       </c>
       <c r="K36" t="n">
-        <v>-153.33</v>
+        <v>-122.63</v>
       </c>
       <c r="L36" t="n">
-        <v>324.28</v>
+        <v>122.67</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:14:07</t>
+          <t>08:21:32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.09</v>
+        <v>4.69</v>
       </c>
       <c r="F37" t="n">
-        <v>12.44</v>
+        <v>13.03</v>
       </c>
       <c r="G37" t="n">
-        <v>91.5</v>
+        <v>81.5</v>
       </c>
       <c r="H37" t="n">
-        <v>90.5</v>
+        <v>79.5</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-89.69</v>
+        <v>-141.57</v>
       </c>
       <c r="K37" t="n">
-        <v>-203.1</v>
+        <v>70.23</v>
       </c>
       <c r="L37" t="n">
-        <v>222.02</v>
+        <v>158.03</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:17:34</t>
+          <t>08:25:01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.54</v>
+        <v>4.94</v>
       </c>
       <c r="F38" t="n">
-        <v>12.49</v>
+        <v>12.87</v>
       </c>
       <c r="G38" t="n">
-        <v>95.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>79.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>217.11</v>
+        <v>146.34</v>
       </c>
       <c r="K38" t="n">
-        <v>-279.7</v>
+        <v>-28.86</v>
       </c>
       <c r="L38" t="n">
-        <v>354.08</v>
+        <v>149.16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:19:08</t>
+          <t>08:26:25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.31</v>
+        <v>4.46</v>
       </c>
       <c r="F39" t="n">
-        <v>12.59</v>
+        <v>12.04</v>
       </c>
       <c r="G39" t="n">
-        <v>85.7</v>
+        <v>88.7</v>
       </c>
       <c r="H39" t="n">
-        <v>80.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-501.92</v>
+        <v>26.43</v>
       </c>
       <c r="K39" t="n">
-        <v>-36.98</v>
+        <v>164.33</v>
       </c>
       <c r="L39" t="n">
-        <v>503.28</v>
+        <v>166.44</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:20:00</t>
+          <t>08:27:45</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.34</v>
+        <v>5.16</v>
       </c>
       <c r="F40" t="n">
-        <v>12.95</v>
+        <v>12.55</v>
       </c>
       <c r="G40" t="n">
-        <v>89.2</v>
+        <v>78.8</v>
       </c>
       <c r="H40" t="n">
-        <v>81</v>
+        <v>74.2</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>509.35</v>
+        <v>47.81</v>
       </c>
       <c r="K40" t="n">
-        <v>58.08</v>
+        <v>205.04</v>
       </c>
       <c r="L40" t="n">
-        <v>512.65</v>
+        <v>210.54</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:26:06</t>
+          <t>08:32:31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.6</v>
+        <v>5.08</v>
       </c>
       <c r="F41" t="n">
-        <v>12.97</v>
+        <v>13.02</v>
       </c>
       <c r="G41" t="n">
-        <v>90.5</v>
+        <v>84.5</v>
       </c>
       <c r="H41" t="n">
-        <v>77.8</v>
+        <v>78.8</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-619.28</v>
+        <v>-53.88</v>
       </c>
       <c r="K41" t="n">
-        <v>261.41</v>
+        <v>-2.61</v>
       </c>
       <c r="L41" t="n">
-        <v>672.1900000000001</v>
+        <v>53.94</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:28:07</t>
+          <t>08:33:17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.63</v>
+        <v>5.44</v>
       </c>
       <c r="F42" t="n">
-        <v>13.1</v>
+        <v>12.58</v>
       </c>
       <c r="G42" t="n">
-        <v>83.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>85.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>139.55</v>
+        <v>211.33</v>
       </c>
       <c r="K42" t="n">
-        <v>210.33</v>
+        <v>-92.33</v>
       </c>
       <c r="L42" t="n">
-        <v>252.42</v>
+        <v>230.61</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:29:52</t>
+          <t>08:35:25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>5.43</v>
+        <v>4.52</v>
       </c>
       <c r="F43" t="n">
-        <v>12.85</v>
+        <v>13.01</v>
       </c>
       <c r="G43" t="n">
-        <v>94.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="H43" t="n">
-        <v>85.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>450.16</v>
+        <v>77.48</v>
       </c>
       <c r="K43" t="n">
-        <v>-23.69</v>
+        <v>154.47</v>
       </c>
       <c r="L43" t="n">
-        <v>450.78</v>
+        <v>172.81</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:37:59</t>
+          <t>08:46:37</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.64</v>
+        <v>4.49</v>
       </c>
       <c r="F44" t="n">
-        <v>12.32</v>
+        <v>12.47</v>
       </c>
       <c r="G44" t="n">
-        <v>89.5</v>
+        <v>99.2</v>
       </c>
       <c r="H44" t="n">
-        <v>84.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>248.07</v>
+        <v>-66.84999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>110.9</v>
+        <v>69.11</v>
       </c>
       <c r="L44" t="n">
-        <v>271.73</v>
+        <v>96.15000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:38:57</t>
+          <t>08:48:34</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.83</v>
+        <v>4.72</v>
       </c>
       <c r="F45" t="n">
-        <v>13.09</v>
+        <v>12.64</v>
       </c>
       <c r="G45" t="n">
-        <v>85.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>81.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-146.24</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>-181.48</v>
+        <v>-35.23</v>
       </c>
       <c r="L45" t="n">
-        <v>233.07</v>
+        <v>78.75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:39:56</t>
+          <t>08:51:08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>5.15</v>
+        <v>4.51</v>
       </c>
       <c r="F46" t="n">
-        <v>12.45</v>
+        <v>12.09</v>
       </c>
       <c r="G46" t="n">
-        <v>83.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>78.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>202.86</v>
+        <v>-54.43</v>
       </c>
       <c r="K46" t="n">
-        <v>-22.68</v>
+        <v>24.71</v>
       </c>
       <c r="L46" t="n">
-        <v>204.13</v>
+        <v>59.77</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:43:54</t>
+          <t>08:54:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.34</v>
+        <v>4.72</v>
       </c>
       <c r="F47" t="n">
-        <v>12.01</v>
+        <v>12.68</v>
       </c>
       <c r="G47" t="n">
-        <v>105</v>
+        <v>84.7</v>
       </c>
       <c r="H47" t="n">
-        <v>76.7</v>
+        <v>84.2</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>25.87</v>
+        <v>-106.67</v>
       </c>
       <c r="K47" t="n">
-        <v>-118.36</v>
+        <v>16.15</v>
       </c>
       <c r="L47" t="n">
-        <v>121.15</v>
+        <v>107.89</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:45:03</t>
+          <t>08:56:23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.07</v>
+        <v>4.77</v>
       </c>
       <c r="F48" t="n">
-        <v>12.7</v>
+        <v>12.72</v>
       </c>
       <c r="G48" t="n">
-        <v>92.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="I48" t="n">
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>292.47</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>95.23999999999999</v>
+        <v>-96.15000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>307.59</v>
+        <v>96.55</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:46:33</t>
+          <t>08:57:49</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.52</v>
+        <v>4.62</v>
       </c>
       <c r="F49" t="n">
-        <v>12.3</v>
+        <v>12.44</v>
       </c>
       <c r="G49" t="n">
-        <v>89.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>79.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>102.26</v>
+        <v>-28.43</v>
       </c>
       <c r="K49" t="n">
-        <v>267.82</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>286.68</v>
+        <v>95.06</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:51:05</t>
+          <t>09:02:23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.12</v>
+        <v>4.81</v>
       </c>
       <c r="F50" t="n">
-        <v>12.45</v>
+        <v>12.27</v>
       </c>
       <c r="G50" t="n">
-        <v>99.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>77.2</v>
+        <v>78.8</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-213.08</v>
+        <v>-48.57</v>
       </c>
       <c r="K50" t="n">
-        <v>187.33</v>
+        <v>-71.44</v>
       </c>
       <c r="L50" t="n">
-        <v>283.71</v>
+        <v>86.39</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:52:40</t>
+          <t>09:03:41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2182,31 +2182,31 @@
         <v>4.91</v>
       </c>
       <c r="F51" t="n">
-        <v>12.37</v>
+        <v>12.22</v>
       </c>
       <c r="G51" t="n">
-        <v>71.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="H51" t="n">
-        <v>78.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-222.31</v>
+        <v>-7.18</v>
       </c>
       <c r="K51" t="n">
-        <v>212.51</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>307.54</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:53:46</t>
+          <t>09:05:58</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.47</v>
+        <v>5.27</v>
       </c>
       <c r="F52" t="n">
-        <v>13.3</v>
+        <v>12.68</v>
       </c>
       <c r="G52" t="n">
-        <v>91.5</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>82.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>302.04</v>
+        <v>35.66</v>
       </c>
       <c r="K52" t="n">
-        <v>35.93</v>
+        <v>-80.16</v>
       </c>
       <c r="L52" t="n">
-        <v>304.17</v>
+        <v>87.73</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:57:15</t>
+          <t>09:11:28</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.64</v>
+        <v>5.04</v>
       </c>
       <c r="F53" t="n">
-        <v>12.48</v>
+        <v>12.78</v>
       </c>
       <c r="G53" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H53" t="n">
-        <v>75.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>448.29</v>
+        <v>62.53</v>
       </c>
       <c r="K53" t="n">
-        <v>26.75</v>
+        <v>96.28</v>
       </c>
       <c r="L53" t="n">
-        <v>449.09</v>
+        <v>114.81</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:58:20</t>
+          <t>09:13:47</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.78</v>
+        <v>5.72</v>
       </c>
       <c r="F54" t="n">
-        <v>12.91</v>
+        <v>13.06</v>
       </c>
       <c r="G54" t="n">
-        <v>68</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>81.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>352.3</v>
+        <v>107.58</v>
       </c>
       <c r="K54" t="n">
-        <v>-310.32</v>
+        <v>-304.73</v>
       </c>
       <c r="L54" t="n">
-        <v>469.48</v>
+        <v>323.17</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:59:44</t>
+          <t>09:15:25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.15</v>
+        <v>4.19</v>
       </c>
       <c r="F55" t="n">
-        <v>12.3</v>
+        <v>12.53</v>
       </c>
       <c r="G55" t="n">
-        <v>93.3</v>
+        <v>75.5</v>
       </c>
       <c r="H55" t="n">
-        <v>84.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>332.27</v>
+        <v>-151.11</v>
       </c>
       <c r="K55" t="n">
-        <v>-577.74</v>
+        <v>-81.66</v>
       </c>
       <c r="L55" t="n">
-        <v>666.48</v>
+        <v>171.76</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:04:16</t>
+          <t>09:19:17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.99</v>
+        <v>5.15</v>
       </c>
       <c r="F56" t="n">
-        <v>12.68</v>
+        <v>13.08</v>
       </c>
       <c r="G56" t="n">
-        <v>91</v>
+        <v>93.3</v>
       </c>
       <c r="H56" t="n">
-        <v>85.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I56" t="n">
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>720.91</v>
+        <v>342.13</v>
       </c>
       <c r="K56" t="n">
-        <v>369.21</v>
+        <v>208.81</v>
       </c>
       <c r="L56" t="n">
-        <v>809.96</v>
+        <v>400.82</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:05:58</t>
+          <t>09:20:41</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.28</v>
+        <v>5.09</v>
       </c>
       <c r="F57" t="n">
-        <v>12.73</v>
+        <v>13.34</v>
       </c>
       <c r="G57" t="n">
-        <v>82.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="H57" t="n">
-        <v>86.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>178.98</v>
+        <v>-133.33</v>
       </c>
       <c r="K57" t="n">
-        <v>618.41</v>
+        <v>152.76</v>
       </c>
       <c r="L57" t="n">
-        <v>643.79</v>
+        <v>202.76</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:07:12</t>
+          <t>09:21:41</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.4</v>
+        <v>4.99</v>
       </c>
       <c r="F58" t="n">
-        <v>12.62</v>
+        <v>13.16</v>
       </c>
       <c r="G58" t="n">
-        <v>92.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>91.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>59.78</v>
+        <v>1.16</v>
       </c>
       <c r="K58" t="n">
-        <v>516.28</v>
+        <v>-163.32</v>
       </c>
       <c r="L58" t="n">
-        <v>519.73</v>
+        <v>163.33</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:18:13</t>
+          <t>09:32:08</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="F59" t="n">
-        <v>12.83</v>
+        <v>12.63</v>
       </c>
       <c r="G59" t="n">
-        <v>89.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>84.2</v>
+        <v>81.3</v>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>100.09</v>
+        <v>88.67</v>
       </c>
       <c r="K59" t="n">
-        <v>-157.35</v>
+        <v>-71.13</v>
       </c>
       <c r="L59" t="n">
-        <v>186.49</v>
+        <v>113.67</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:19:02</t>
+          <t>09:34:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.81</v>
+        <v>5.2</v>
       </c>
       <c r="F60" t="n">
-        <v>13.14</v>
+        <v>12.19</v>
       </c>
       <c r="G60" t="n">
-        <v>83.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>82.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="I60" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-213.6</v>
+        <v>-91.83</v>
       </c>
       <c r="K60" t="n">
-        <v>247.74</v>
+        <v>-40.76</v>
       </c>
       <c r="L60" t="n">
-        <v>327.11</v>
+        <v>100.47</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:21:01</t>
+          <t>09:35:02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.67</v>
+        <v>5.32</v>
       </c>
       <c r="F61" t="n">
-        <v>12.59</v>
+        <v>13.02</v>
       </c>
       <c r="G61" t="n">
-        <v>84.3</v>
+        <v>90</v>
       </c>
       <c r="H61" t="n">
-        <v>79.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I61" t="n">
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-133.89</v>
+        <v>-35.27</v>
       </c>
       <c r="K61" t="n">
-        <v>-31.61</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>137.57</v>
+        <v>100.67</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:27:02</t>
+          <t>09:39:29</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>5.02</v>
+        <v>4.65</v>
       </c>
       <c r="F62" t="n">
-        <v>12.48</v>
+        <v>12.59</v>
       </c>
       <c r="G62" t="n">
-        <v>77.59999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>80.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="I62" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-265.47</v>
+        <v>32.38</v>
       </c>
       <c r="K62" t="n">
-        <v>187.8</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>325.19</v>
+        <v>89.08</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:27:43</t>
+          <t>09:41:19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>5.05</v>
+        <v>4.24</v>
       </c>
       <c r="F63" t="n">
-        <v>12.42</v>
+        <v>12.63</v>
       </c>
       <c r="G63" t="n">
-        <v>76.7</v>
+        <v>96.8</v>
       </c>
       <c r="H63" t="n">
-        <v>79.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>141.88</v>
+        <v>-88.39</v>
       </c>
       <c r="K63" t="n">
-        <v>-51.53</v>
+        <v>109.83</v>
       </c>
       <c r="L63" t="n">
-        <v>150.94</v>
+        <v>140.98</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:29:31</t>
+          <t>09:43:09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.42</v>
+        <v>5.64</v>
       </c>
       <c r="F64" t="n">
-        <v>12.19</v>
+        <v>12.5</v>
       </c>
       <c r="G64" t="n">
-        <v>95.7</v>
+        <v>76.5</v>
       </c>
       <c r="H64" t="n">
         <v>85.09999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-126.69</v>
+        <v>-152.62</v>
       </c>
       <c r="K64" t="n">
-        <v>-239.34</v>
+        <v>-2.32</v>
       </c>
       <c r="L64" t="n">
-        <v>270.8</v>
+        <v>152.64</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:34:44</t>
+          <t>09:47:11</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.78</v>
+        <v>5.89</v>
       </c>
       <c r="F65" t="n">
-        <v>12.18</v>
+        <v>13.5</v>
       </c>
       <c r="G65" t="n">
-        <v>83.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="H65" t="n">
-        <v>79.8</v>
+        <v>86.7</v>
       </c>
       <c r="I65" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>98</v>
+        <v>214.76</v>
       </c>
       <c r="K65" t="n">
-        <v>337.72</v>
+        <v>-126.69</v>
       </c>
       <c r="L65" t="n">
-        <v>351.66</v>
+        <v>249.35</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:35:56</t>
+          <t>09:48:14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.81</v>
+        <v>5.43</v>
       </c>
       <c r="F66" t="n">
-        <v>13.25</v>
+        <v>12.19</v>
       </c>
       <c r="G66" t="n">
-        <v>81.59999999999999</v>
+        <v>57.5</v>
       </c>
       <c r="H66" t="n">
-        <v>85.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-86.13</v>
+        <v>94.92</v>
       </c>
       <c r="K66" t="n">
-        <v>-335.15</v>
+        <v>-69.67</v>
       </c>
       <c r="L66" t="n">
-        <v>346.04</v>
+        <v>117.74</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:37:18</t>
+          <t>09:49:46</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.55</v>
+        <v>5.13</v>
       </c>
       <c r="F67" t="n">
-        <v>12.04</v>
+        <v>13.03</v>
       </c>
       <c r="G67" t="n">
-        <v>80.90000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="H67" t="n">
-        <v>85.8</v>
+        <v>82.2</v>
       </c>
       <c r="I67" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>402.46</v>
+        <v>-130.14</v>
       </c>
       <c r="K67" t="n">
-        <v>-177.41</v>
+        <v>30.31</v>
       </c>
       <c r="L67" t="n">
-        <v>439.83</v>
+        <v>133.62</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:42:00</t>
+          <t>09:55:22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.09</v>
+        <v>4.57</v>
       </c>
       <c r="F68" t="n">
-        <v>12.83</v>
+        <v>12.57</v>
       </c>
       <c r="G68" t="n">
-        <v>82.09999999999999</v>
+        <v>101.5</v>
       </c>
       <c r="H68" t="n">
-        <v>80.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-432.48</v>
+        <v>-103.82</v>
       </c>
       <c r="K68" t="n">
-        <v>-207.11</v>
+        <v>-57.65</v>
       </c>
       <c r="L68" t="n">
-        <v>479.52</v>
+        <v>118.75</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:42:33</t>
+          <t>09:56:51</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.02</v>
+        <v>5.84</v>
       </c>
       <c r="F69" t="n">
-        <v>12.88</v>
+        <v>12.5</v>
       </c>
       <c r="G69" t="n">
-        <v>80.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>86.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-364.95</v>
+        <v>233.02</v>
       </c>
       <c r="K69" t="n">
-        <v>-105.27</v>
+        <v>41.95</v>
       </c>
       <c r="L69" t="n">
-        <v>379.83</v>
+        <v>236.76</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:44:45</t>
+          <t>09:59:16</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.23</v>
+        <v>5.11</v>
       </c>
       <c r="F70" t="n">
-        <v>13.06</v>
+        <v>12.59</v>
       </c>
       <c r="G70" t="n">
-        <v>84.7</v>
+        <v>92.5</v>
       </c>
       <c r="H70" t="n">
-        <v>79.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-251.84</v>
+        <v>112.32</v>
       </c>
       <c r="K70" t="n">
-        <v>-76.08</v>
+        <v>-24.62</v>
       </c>
       <c r="L70" t="n">
-        <v>263.08</v>
+        <v>114.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:48:40</t>
+          <t>10:04:41</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.58</v>
+        <v>5.56</v>
       </c>
       <c r="F71" t="n">
-        <v>12.76</v>
+        <v>12.61</v>
       </c>
       <c r="G71" t="n">
-        <v>89.8</v>
+        <v>85.7</v>
       </c>
       <c r="H71" t="n">
-        <v>87.2</v>
+        <v>82.3</v>
       </c>
       <c r="I71" t="n">
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>9.42</v>
+        <v>241.65</v>
       </c>
       <c r="K71" t="n">
-        <v>-288.13</v>
+        <v>-31.04</v>
       </c>
       <c r="L71" t="n">
-        <v>288.28</v>
+        <v>243.63</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:50:15</t>
+          <t>10:05:44</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.62</v>
+        <v>5.19</v>
       </c>
       <c r="F72" t="n">
-        <v>13.18</v>
+        <v>12.64</v>
       </c>
       <c r="G72" t="n">
-        <v>77.40000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="H72" t="n">
-        <v>83.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-18.73</v>
+        <v>-167.03</v>
       </c>
       <c r="K72" t="n">
-        <v>626.9400000000001</v>
+        <v>107.12</v>
       </c>
       <c r="L72" t="n">
-        <v>627.21</v>
+        <v>198.43</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:51:19</t>
+          <t>10:07:33</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.5</v>
+        <v>5.28</v>
       </c>
       <c r="F73" t="n">
-        <v>12.11</v>
+        <v>12.8</v>
       </c>
       <c r="G73" t="n">
-        <v>80.8</v>
+        <v>96.3</v>
       </c>
       <c r="H73" t="n">
-        <v>81.7</v>
+        <v>78.8</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-851.13</v>
+        <v>54.17</v>
       </c>
       <c r="K73" t="n">
-        <v>321.2</v>
+        <v>-194.84</v>
       </c>
       <c r="L73" t="n">
-        <v>909.72</v>
+        <v>202.24</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:02:24</t>
+          <t>10:17:29</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.52</v>
+        <v>5.06</v>
       </c>
       <c r="F74" t="n">
-        <v>13.11</v>
+        <v>12.76</v>
       </c>
       <c r="G74" t="n">
-        <v>81.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>83.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-224.82</v>
+        <v>34.42</v>
       </c>
       <c r="K74" t="n">
-        <v>-24.72</v>
+        <v>-47.13</v>
       </c>
       <c r="L74" t="n">
-        <v>226.17</v>
+        <v>58.36</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:03:32</t>
+          <t>10:19:16</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.35</v>
+        <v>5.12</v>
       </c>
       <c r="F75" t="n">
-        <v>12.64</v>
+        <v>12.4</v>
       </c>
       <c r="G75" t="n">
-        <v>88.7</v>
+        <v>63.1</v>
       </c>
       <c r="H75" t="n">
-        <v>80.8</v>
+        <v>86.2</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-21.49</v>
+        <v>-69.06999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>167.25</v>
+        <v>-73.19</v>
       </c>
       <c r="L75" t="n">
-        <v>168.63</v>
+        <v>100.64</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:05:53</t>
+          <t>10:20:09</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.61</v>
+        <v>5.08</v>
       </c>
       <c r="F76" t="n">
-        <v>13.37</v>
+        <v>12.52</v>
       </c>
       <c r="G76" t="n">
-        <v>85.3</v>
+        <v>82.5</v>
       </c>
       <c r="H76" t="n">
-        <v>80.7</v>
+        <v>85</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-162.41</v>
+        <v>45.23</v>
       </c>
       <c r="K76" t="n">
-        <v>-146.51</v>
+        <v>36.96</v>
       </c>
       <c r="L76" t="n">
-        <v>218.73</v>
+        <v>58.41</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:11:48</t>
+          <t>10:24:36</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.29</v>
+        <v>5.63</v>
       </c>
       <c r="F77" t="n">
-        <v>13.29</v>
+        <v>12.01</v>
       </c>
       <c r="G77" t="n">
-        <v>101.6</v>
+        <v>92.3</v>
       </c>
       <c r="H77" t="n">
-        <v>77.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-237.81</v>
+        <v>24.97</v>
       </c>
       <c r="K77" t="n">
-        <v>256.41</v>
+        <v>140.97</v>
       </c>
       <c r="L77" t="n">
-        <v>349.71</v>
+        <v>143.17</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:13:59</t>
+          <t>10:26:42</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.69</v>
+        <v>5.02</v>
       </c>
       <c r="F78" t="n">
-        <v>12.32</v>
+        <v>13.13</v>
       </c>
       <c r="G78" t="n">
-        <v>81.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="H78" t="n">
-        <v>87.3</v>
+        <v>89.3</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-297.54</v>
+        <v>-19.88</v>
       </c>
       <c r="K78" t="n">
-        <v>-220.55</v>
+        <v>57.34</v>
       </c>
       <c r="L78" t="n">
-        <v>370.37</v>
+        <v>60.69</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:16:18</t>
+          <t>10:27:30</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.45</v>
+        <v>5.21</v>
       </c>
       <c r="F79" t="n">
-        <v>12.5</v>
+        <v>12.65</v>
       </c>
       <c r="G79" t="n">
-        <v>74.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="H79" t="n">
-        <v>80.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>242.47</v>
+        <v>-44.65</v>
       </c>
       <c r="K79" t="n">
-        <v>-31.91</v>
+        <v>58.17</v>
       </c>
       <c r="L79" t="n">
-        <v>244.56</v>
+        <v>73.33</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:20:30</t>
+          <t>10:32:06</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.15</v>
+        <v>5.38</v>
       </c>
       <c r="F80" t="n">
-        <v>12.89</v>
+        <v>12.65</v>
       </c>
       <c r="G80" t="n">
-        <v>84.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="H80" t="n">
-        <v>75.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>216.47</v>
+        <v>189.97</v>
       </c>
       <c r="K80" t="n">
-        <v>199.12</v>
+        <v>-83.12</v>
       </c>
       <c r="L80" t="n">
-        <v>294.12</v>
+        <v>207.36</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:21:50</t>
+          <t>10:33:27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>6.14</v>
+        <v>5.09</v>
       </c>
       <c r="F81" t="n">
-        <v>12.45</v>
+        <v>12.91</v>
       </c>
       <c r="G81" t="n">
-        <v>82.8</v>
+        <v>97.5</v>
       </c>
       <c r="H81" t="n">
-        <v>83.90000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>175.01</v>
+        <v>-108.12</v>
       </c>
       <c r="K81" t="n">
-        <v>-327.44</v>
+        <v>-17.49</v>
       </c>
       <c r="L81" t="n">
-        <v>371.27</v>
+        <v>109.52</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:23:55</t>
+          <t>10:35:27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.53</v>
+        <v>6.3</v>
       </c>
       <c r="F82" t="n">
-        <v>12.33</v>
+        <v>12.62</v>
       </c>
       <c r="G82" t="n">
-        <v>90.2</v>
+        <v>103.3</v>
       </c>
       <c r="H82" t="n">
-        <v>79.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-302.95</v>
+        <v>-136.81</v>
       </c>
       <c r="K82" t="n">
-        <v>-294.69</v>
+        <v>-56.22</v>
       </c>
       <c r="L82" t="n">
-        <v>422.64</v>
+        <v>147.91</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:28:45</t>
+          <t>10:40:01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.96</v>
+        <v>6.1</v>
       </c>
       <c r="F83" t="n">
-        <v>12.61</v>
+        <v>12.96</v>
       </c>
       <c r="G83" t="n">
-        <v>71.8</v>
+        <v>92.7</v>
       </c>
       <c r="H83" t="n">
-        <v>83.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-437.8</v>
+        <v>-178.54</v>
       </c>
       <c r="K83" t="n">
-        <v>98.15000000000001</v>
+        <v>-154.64</v>
       </c>
       <c r="L83" t="n">
-        <v>448.67</v>
+        <v>236.2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:30:19</t>
+          <t>10:42:05</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
       <c r="F84" t="n">
-        <v>12.97</v>
+        <v>12.81</v>
       </c>
       <c r="G84" t="n">
-        <v>67.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="H84" t="n">
-        <v>85.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-124.06</v>
+        <v>-38.29</v>
       </c>
       <c r="K84" t="n">
-        <v>413.82</v>
+        <v>-103.56</v>
       </c>
       <c r="L84" t="n">
-        <v>432.02</v>
+        <v>110.41</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:32:34</t>
+          <t>10:44:05</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.03</v>
+        <v>5.31</v>
       </c>
       <c r="F85" t="n">
-        <v>12.92</v>
+        <v>12.87</v>
       </c>
       <c r="G85" t="n">
-        <v>92.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="H85" t="n">
-        <v>82.2</v>
+        <v>84.3</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-84.77</v>
+        <v>113.04</v>
       </c>
       <c r="K85" t="n">
-        <v>-475.47</v>
+        <v>-82.56</v>
       </c>
       <c r="L85" t="n">
-        <v>482.97</v>
+        <v>139.98</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:37:32</t>
+          <t>10:48:02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.69</v>
+        <v>5.51</v>
       </c>
       <c r="F86" t="n">
-        <v>11.99</v>
+        <v>12.95</v>
       </c>
       <c r="G86" t="n">
-        <v>86.40000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="H86" t="n">
-        <v>89.3</v>
+        <v>80.5</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-310.74</v>
+        <v>-167.17</v>
       </c>
       <c r="K86" t="n">
-        <v>-284.38</v>
+        <v>162.36</v>
       </c>
       <c r="L86" t="n">
-        <v>421.23</v>
+        <v>233.04</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:39:21</t>
+          <t>10:50:16</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.95</v>
+        <v>5.16</v>
       </c>
       <c r="F87" t="n">
-        <v>12.78</v>
+        <v>12.7</v>
       </c>
       <c r="G87" t="n">
-        <v>82.3</v>
+        <v>78.8</v>
       </c>
       <c r="H87" t="n">
-        <v>88.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>450.77</v>
+        <v>158.84</v>
       </c>
       <c r="K87" t="n">
-        <v>-429.03</v>
+        <v>164.99</v>
       </c>
       <c r="L87" t="n">
-        <v>622.3099999999999</v>
+        <v>229.02</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:40:10</t>
+          <t>10:51:53</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.47</v>
+        <v>5.12</v>
       </c>
       <c r="F88" t="n">
-        <v>13.39</v>
+        <v>12.72</v>
       </c>
       <c r="G88" t="n">
-        <v>85.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="H88" t="n">
-        <v>83.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>-365.97</v>
+        <v>-16.19</v>
       </c>
       <c r="K88" t="n">
-        <v>-419.48</v>
+        <v>-235.99</v>
       </c>
       <c r="L88" t="n">
-        <v>556.6799999999999</v>
+        <v>236.55</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-29.xlsx
+++ b/output/2025-09-29.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-82.48999999999999</v>
+        <v>-76.48</v>
       </c>
       <c r="K14" t="n">
-        <v>57.69</v>
+        <v>53.49</v>
       </c>
       <c r="L14" t="n">
-        <v>100.66</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-45.8</v>
+        <v>-43.03</v>
       </c>
       <c r="K15" t="n">
-        <v>24.2</v>
+        <v>22.73</v>
       </c>
       <c r="L15" t="n">
-        <v>51.8</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>98.84</v>
+        <v>91.77</v>
       </c>
       <c r="K16" t="n">
-        <v>-34.23</v>
+        <v>-31.78</v>
       </c>
       <c r="L16" t="n">
-        <v>104.6</v>
+        <v>97.12</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-32.16</v>
+        <v>-30.42</v>
       </c>
       <c r="K17" t="n">
-        <v>-97.38</v>
+        <v>-92.13</v>
       </c>
       <c r="L17" t="n">
-        <v>102.56</v>
+        <v>97.02</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-92.72</v>
+        <v>-87.73</v>
       </c>
       <c r="K18" t="n">
-        <v>-43.88</v>
+        <v>-41.52</v>
       </c>
       <c r="L18" t="n">
-        <v>102.57</v>
+        <v>97.06</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>147.86</v>
+        <v>135.54</v>
       </c>
       <c r="K19" t="n">
-        <v>54.46</v>
+        <v>49.92</v>
       </c>
       <c r="L19" t="n">
-        <v>157.57</v>
+        <v>144.44</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>31.66</v>
+        <v>31.72</v>
       </c>
       <c r="K20" t="n">
-        <v>-108.02</v>
+        <v>-108.25</v>
       </c>
       <c r="L20" t="n">
-        <v>112.56</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>106.48</v>
+        <v>103.42</v>
       </c>
       <c r="K21" t="n">
-        <v>119.23</v>
+        <v>115.8</v>
       </c>
       <c r="L21" t="n">
-        <v>159.85</v>
+        <v>155.26</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-71.05</v>
+        <v>-71.8</v>
       </c>
       <c r="K22" t="n">
-        <v>-84.76000000000001</v>
+        <v>-85.66</v>
       </c>
       <c r="L22" t="n">
-        <v>110.6</v>
+        <v>111.77</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>16.59</v>
+        <v>16.28</v>
       </c>
       <c r="K23" t="n">
-        <v>192.23</v>
+        <v>188.71</v>
       </c>
       <c r="L23" t="n">
-        <v>192.95</v>
+        <v>189.41</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>156.4</v>
+        <v>158.44</v>
       </c>
       <c r="K24" t="n">
-        <v>-39.79</v>
+        <v>-40.31</v>
       </c>
       <c r="L24" t="n">
-        <v>161.38</v>
+        <v>163.49</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>97.53</v>
+        <v>105.31</v>
       </c>
       <c r="K25" t="n">
-        <v>139.66</v>
+        <v>150.79</v>
       </c>
       <c r="L25" t="n">
-        <v>170.34</v>
+        <v>183.93</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.02</v>
+        <v>-4.33</v>
       </c>
       <c r="K26" t="n">
-        <v>157.54</v>
+        <v>169.63</v>
       </c>
       <c r="L26" t="n">
-        <v>157.6</v>
+        <v>169.68</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-234.55</v>
+        <v>-241.11</v>
       </c>
       <c r="K27" t="n">
-        <v>158.5</v>
+        <v>162.93</v>
       </c>
       <c r="L27" t="n">
-        <v>283.08</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>175.68</v>
+        <v>187.14</v>
       </c>
       <c r="K28" t="n">
-        <v>-165.01</v>
+        <v>-175.77</v>
       </c>
       <c r="L28" t="n">
-        <v>241.02</v>
+        <v>256.74</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>33.79</v>
+        <v>34.36</v>
       </c>
       <c r="K29" t="n">
-        <v>32.59</v>
+        <v>33.14</v>
       </c>
       <c r="L29" t="n">
-        <v>46.95</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>60.88</v>
+        <v>54.96</v>
       </c>
       <c r="K30" t="n">
-        <v>-58.02</v>
+        <v>-52.37</v>
       </c>
       <c r="L30" t="n">
-        <v>84.09999999999999</v>
+        <v>75.92</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>22.01</v>
+        <v>21.84</v>
       </c>
       <c r="K31" t="n">
-        <v>-37.86</v>
+        <v>-37.56</v>
       </c>
       <c r="L31" t="n">
-        <v>43.8</v>
+        <v>43.45</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-23.32</v>
+        <v>-22.45</v>
       </c>
       <c r="K32" t="n">
-        <v>77.5</v>
+        <v>74.62</v>
       </c>
       <c r="L32" t="n">
-        <v>80.93000000000001</v>
+        <v>77.92</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-63.82</v>
+        <v>-61.55</v>
       </c>
       <c r="K33" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="L33" t="n">
-        <v>63.92</v>
+        <v>61.64</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>19.39</v>
+        <v>17.69</v>
       </c>
       <c r="K34" t="n">
-        <v>70.45</v>
+        <v>64.3</v>
       </c>
       <c r="L34" t="n">
-        <v>73.06999999999999</v>
+        <v>66.69</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-81.5</v>
+        <v>-82.81999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>-64.44</v>
+        <v>-65.48999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>103.9</v>
+        <v>105.58</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="K36" t="n">
-        <v>-122.63</v>
+        <v>-122</v>
       </c>
       <c r="L36" t="n">
-        <v>122.67</v>
+        <v>122.04</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-141.57</v>
+        <v>-136.78</v>
       </c>
       <c r="K37" t="n">
-        <v>70.23</v>
+        <v>67.86</v>
       </c>
       <c r="L37" t="n">
-        <v>158.03</v>
+        <v>152.69</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>146.34</v>
+        <v>157.26</v>
       </c>
       <c r="K38" t="n">
-        <v>-28.86</v>
+        <v>-31.01</v>
       </c>
       <c r="L38" t="n">
-        <v>149.16</v>
+        <v>160.29</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>26.43</v>
+        <v>26.68</v>
       </c>
       <c r="K39" t="n">
-        <v>164.33</v>
+        <v>165.9</v>
       </c>
       <c r="L39" t="n">
-        <v>166.44</v>
+        <v>168.03</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>47.81</v>
+        <v>50.31</v>
       </c>
       <c r="K40" t="n">
-        <v>205.04</v>
+        <v>215.76</v>
       </c>
       <c r="L40" t="n">
-        <v>210.54</v>
+        <v>221.55</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-53.88</v>
+        <v>-60.54</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.61</v>
+        <v>-2.94</v>
       </c>
       <c r="L41" t="n">
-        <v>53.94</v>
+        <v>60.61</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>211.33</v>
+        <v>255.1</v>
       </c>
       <c r="K42" t="n">
-        <v>-92.33</v>
+        <v>-111.45</v>
       </c>
       <c r="L42" t="n">
-        <v>230.61</v>
+        <v>278.39</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>77.48</v>
+        <v>89.08</v>
       </c>
       <c r="K43" t="n">
-        <v>154.47</v>
+        <v>177.59</v>
       </c>
       <c r="L43" t="n">
-        <v>172.81</v>
+        <v>198.68</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-66.84999999999999</v>
+        <v>-62.64</v>
       </c>
       <c r="K44" t="n">
-        <v>69.11</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>96.15000000000001</v>
+        <v>90.09</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>70.43000000000001</v>
+        <v>66.37</v>
       </c>
       <c r="K45" t="n">
-        <v>-35.23</v>
+        <v>-33.2</v>
       </c>
       <c r="L45" t="n">
-        <v>78.75</v>
+        <v>74.20999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-54.43</v>
+        <v>-53.69</v>
       </c>
       <c r="K46" t="n">
-        <v>24.71</v>
+        <v>24.37</v>
       </c>
       <c r="L46" t="n">
-        <v>59.77</v>
+        <v>58.96</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-106.67</v>
+        <v>-99.16</v>
       </c>
       <c r="K47" t="n">
-        <v>16.15</v>
+        <v>15.01</v>
       </c>
       <c r="L47" t="n">
-        <v>107.89</v>
+        <v>100.29</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-8.779999999999999</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-96.15000000000001</v>
+        <v>-90.89</v>
       </c>
       <c r="L48" t="n">
-        <v>96.55</v>
+        <v>91.27</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-28.43</v>
+        <v>-26.88</v>
       </c>
       <c r="K49" t="n">
-        <v>90.70999999999999</v>
+        <v>85.75</v>
       </c>
       <c r="L49" t="n">
-        <v>95.06</v>
+        <v>89.86</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-48.57</v>
+        <v>-50.72</v>
       </c>
       <c r="K50" t="n">
-        <v>-71.44</v>
+        <v>-74.61</v>
       </c>
       <c r="L50" t="n">
-        <v>86.39</v>
+        <v>90.22</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.18</v>
+        <v>-7.45</v>
       </c>
       <c r="K51" t="n">
-        <v>86.09999999999999</v>
+        <v>89.38</v>
       </c>
       <c r="L51" t="n">
-        <v>86.40000000000001</v>
+        <v>89.69</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>35.66</v>
+        <v>37.73</v>
       </c>
       <c r="K52" t="n">
-        <v>-80.16</v>
+        <v>-84.8</v>
       </c>
       <c r="L52" t="n">
-        <v>87.73</v>
+        <v>92.81</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>62.53</v>
+        <v>71.84</v>
       </c>
       <c r="K53" t="n">
-        <v>96.28</v>
+        <v>110.62</v>
       </c>
       <c r="L53" t="n">
-        <v>114.81</v>
+        <v>131.9</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>107.58</v>
+        <v>110.27</v>
       </c>
       <c r="K54" t="n">
-        <v>-304.73</v>
+        <v>-312.37</v>
       </c>
       <c r="L54" t="n">
-        <v>323.17</v>
+        <v>331.26</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>-151.11</v>
+        <v>-151.03</v>
       </c>
       <c r="K55" t="n">
-        <v>-81.66</v>
+        <v>-81.62</v>
       </c>
       <c r="L55" t="n">
-        <v>171.76</v>
+        <v>171.67</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>342.13</v>
+        <v>378.52</v>
       </c>
       <c r="K56" t="n">
-        <v>208.81</v>
+        <v>231.02</v>
       </c>
       <c r="L56" t="n">
-        <v>400.82</v>
+        <v>443.45</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-133.33</v>
+        <v>-160.18</v>
       </c>
       <c r="K57" t="n">
-        <v>152.76</v>
+        <v>183.53</v>
       </c>
       <c r="L57" t="n">
-        <v>202.76</v>
+        <v>243.6</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="K58" t="n">
-        <v>-163.32</v>
+        <v>-198.23</v>
       </c>
       <c r="L58" t="n">
-        <v>163.33</v>
+        <v>198.23</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>88.67</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-71.13</v>
+        <v>-60.24</v>
       </c>
       <c r="L59" t="n">
-        <v>113.67</v>
+        <v>96.28</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-91.83</v>
+        <v>-78.87</v>
       </c>
       <c r="K60" t="n">
-        <v>-40.76</v>
+        <v>-35.01</v>
       </c>
       <c r="L60" t="n">
-        <v>100.47</v>
+        <v>86.29000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-35.27</v>
+        <v>-29.55</v>
       </c>
       <c r="K61" t="n">
-        <v>94.29000000000001</v>
+        <v>78.98</v>
       </c>
       <c r="L61" t="n">
-        <v>100.67</v>
+        <v>84.33</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>32.38</v>
+        <v>30.92</v>
       </c>
       <c r="K62" t="n">
-        <v>82.98999999999999</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>89.08</v>
+        <v>85.06999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-88.39</v>
+        <v>-81.92</v>
       </c>
       <c r="K63" t="n">
-        <v>109.83</v>
+        <v>101.79</v>
       </c>
       <c r="L63" t="n">
-        <v>140.98</v>
+        <v>130.65</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-152.62</v>
+        <v>-125.26</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.32</v>
+        <v>-1.9</v>
       </c>
       <c r="L64" t="n">
-        <v>152.64</v>
+        <v>125.27</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>214.76</v>
+        <v>200.53</v>
       </c>
       <c r="K65" t="n">
-        <v>-126.69</v>
+        <v>-118.29</v>
       </c>
       <c r="L65" t="n">
-        <v>249.35</v>
+        <v>232.82</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>94.92</v>
+        <v>95.16</v>
       </c>
       <c r="K66" t="n">
-        <v>-69.67</v>
+        <v>-69.84</v>
       </c>
       <c r="L66" t="n">
-        <v>117.74</v>
+        <v>118.04</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-130.14</v>
+        <v>-128.69</v>
       </c>
       <c r="K67" t="n">
-        <v>30.31</v>
+        <v>29.97</v>
       </c>
       <c r="L67" t="n">
-        <v>133.62</v>
+        <v>132.14</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-103.82</v>
+        <v>-111.69</v>
       </c>
       <c r="K68" t="n">
-        <v>-57.65</v>
+        <v>-62.02</v>
       </c>
       <c r="L68" t="n">
-        <v>118.75</v>
+        <v>127.75</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>233.02</v>
+        <v>248.72</v>
       </c>
       <c r="K69" t="n">
-        <v>41.95</v>
+        <v>44.78</v>
       </c>
       <c r="L69" t="n">
-        <v>236.76</v>
+        <v>252.72</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>112.32</v>
+        <v>127.94</v>
       </c>
       <c r="K70" t="n">
-        <v>-24.62</v>
+        <v>-28.04</v>
       </c>
       <c r="L70" t="n">
-        <v>114.99</v>
+        <v>130.98</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>241.65</v>
+        <v>292.34</v>
       </c>
       <c r="K71" t="n">
-        <v>-31.04</v>
+        <v>-37.55</v>
       </c>
       <c r="L71" t="n">
-        <v>243.63</v>
+        <v>294.75</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-167.03</v>
+        <v>-203.45</v>
       </c>
       <c r="K72" t="n">
-        <v>107.12</v>
+        <v>130.48</v>
       </c>
       <c r="L72" t="n">
-        <v>198.43</v>
+        <v>241.7</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>54.17</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="K73" t="n">
-        <v>-194.84</v>
+        <v>-234.91</v>
       </c>
       <c r="L73" t="n">
-        <v>202.24</v>
+        <v>243.83</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>34.42</v>
+        <v>32.26</v>
       </c>
       <c r="K74" t="n">
-        <v>-47.13</v>
+        <v>-44.18</v>
       </c>
       <c r="L74" t="n">
-        <v>58.36</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-69.06999999999999</v>
+        <v>-60.26</v>
       </c>
       <c r="K75" t="n">
-        <v>-73.19</v>
+        <v>-63.85</v>
       </c>
       <c r="L75" t="n">
-        <v>100.64</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>45.23</v>
+        <v>42.01</v>
       </c>
       <c r="K76" t="n">
-        <v>36.96</v>
+        <v>34.33</v>
       </c>
       <c r="L76" t="n">
-        <v>58.41</v>
+        <v>54.25</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>24.97</v>
+        <v>20.44</v>
       </c>
       <c r="K77" t="n">
-        <v>140.97</v>
+        <v>115.38</v>
       </c>
       <c r="L77" t="n">
-        <v>143.17</v>
+        <v>117.17</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-19.88</v>
+        <v>-19.28</v>
       </c>
       <c r="K78" t="n">
-        <v>57.34</v>
+        <v>55.6</v>
       </c>
       <c r="L78" t="n">
-        <v>60.69</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-44.65</v>
+        <v>-41.25</v>
       </c>
       <c r="K79" t="n">
-        <v>58.17</v>
+        <v>53.74</v>
       </c>
       <c r="L79" t="n">
-        <v>73.33</v>
+        <v>67.75</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>189.97</v>
+        <v>180.08</v>
       </c>
       <c r="K80" t="n">
-        <v>-83.12</v>
+        <v>-78.79000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>207.36</v>
+        <v>196.57</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>-108.12</v>
+        <v>-109.06</v>
       </c>
       <c r="K81" t="n">
-        <v>-17.49</v>
+        <v>-17.64</v>
       </c>
       <c r="L81" t="n">
-        <v>109.52</v>
+        <v>110.48</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-136.81</v>
+        <v>-134.67</v>
       </c>
       <c r="K82" t="n">
-        <v>-56.22</v>
+        <v>-55.34</v>
       </c>
       <c r="L82" t="n">
-        <v>147.91</v>
+        <v>145.6</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-178.54</v>
+        <v>-194.65</v>
       </c>
       <c r="K83" t="n">
-        <v>-154.64</v>
+        <v>-168.59</v>
       </c>
       <c r="L83" t="n">
-        <v>236.2</v>
+        <v>257.51</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-38.29</v>
+        <v>-42.44</v>
       </c>
       <c r="K84" t="n">
-        <v>-103.56</v>
+        <v>-114.78</v>
       </c>
       <c r="L84" t="n">
-        <v>110.41</v>
+        <v>122.38</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>113.04</v>
+        <v>126.22</v>
       </c>
       <c r="K85" t="n">
-        <v>-82.56</v>
+        <v>-92.18000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>139.98</v>
+        <v>156.3</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-167.17</v>
+        <v>-203.77</v>
       </c>
       <c r="K86" t="n">
-        <v>162.36</v>
+        <v>197.9</v>
       </c>
       <c r="L86" t="n">
-        <v>233.04</v>
+        <v>284.06</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>158.84</v>
+        <v>188.19</v>
       </c>
       <c r="K87" t="n">
-        <v>164.99</v>
+        <v>195.48</v>
       </c>
       <c r="L87" t="n">
-        <v>229.02</v>
+        <v>271.34</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>-16.19</v>
+        <v>-18.96</v>
       </c>
       <c r="K88" t="n">
-        <v>-235.99</v>
+        <v>-276.44</v>
       </c>
       <c r="L88" t="n">
-        <v>236.55</v>
+        <v>277.09</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-29.xlsx
+++ b/output/2025-09-29.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-76.48</v>
+        <v>-72.61</v>
       </c>
       <c r="K14" t="n">
-        <v>53.49</v>
+        <v>50.78</v>
       </c>
       <c r="L14" t="n">
-        <v>93.33</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-43.03</v>
+        <v>-46.21</v>
       </c>
       <c r="K15" t="n">
-        <v>22.73</v>
+        <v>24.41</v>
       </c>
       <c r="L15" t="n">
-        <v>48.66</v>
+        <v>52.26</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>91.77</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-31.78</v>
+        <v>-30.5</v>
       </c>
       <c r="L16" t="n">
-        <v>97.12</v>
+        <v>93.20999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-30.42</v>
+        <v>-29.69</v>
       </c>
       <c r="K17" t="n">
-        <v>-92.13</v>
+        <v>-89.92</v>
       </c>
       <c r="L17" t="n">
-        <v>97.02</v>
+        <v>94.69</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-87.73</v>
+        <v>-85.92</v>
       </c>
       <c r="K18" t="n">
-        <v>-41.52</v>
+        <v>-40.66</v>
       </c>
       <c r="L18" t="n">
-        <v>97.06</v>
+        <v>95.06</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>135.54</v>
+        <v>125.7</v>
       </c>
       <c r="K19" t="n">
-        <v>49.92</v>
+        <v>46.3</v>
       </c>
       <c r="L19" t="n">
-        <v>144.44</v>
+        <v>133.95</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>31.72</v>
+        <v>32.19</v>
       </c>
       <c r="K20" t="n">
-        <v>-108.25</v>
+        <v>-109.83</v>
       </c>
       <c r="L20" t="n">
-        <v>112.8</v>
+        <v>114.45</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>103.42</v>
+        <v>101.44</v>
       </c>
       <c r="K21" t="n">
-        <v>115.8</v>
+        <v>113.59</v>
       </c>
       <c r="L21" t="n">
-        <v>155.26</v>
+        <v>152.29</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-71.8</v>
+        <v>-74.23999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-85.66</v>
+        <v>-88.56999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>111.77</v>
+        <v>115.57</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>16.28</v>
+        <v>15.81</v>
       </c>
       <c r="K23" t="n">
-        <v>188.71</v>
+        <v>183.28</v>
       </c>
       <c r="L23" t="n">
-        <v>189.41</v>
+        <v>183.96</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>158.44</v>
+        <v>159.61</v>
       </c>
       <c r="K24" t="n">
-        <v>-40.31</v>
+        <v>-40.6</v>
       </c>
       <c r="L24" t="n">
-        <v>163.49</v>
+        <v>164.69</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>105.31</v>
+        <v>107.15</v>
       </c>
       <c r="K25" t="n">
-        <v>150.79</v>
+        <v>153.42</v>
       </c>
       <c r="L25" t="n">
-        <v>183.93</v>
+        <v>187.13</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.33</v>
+        <v>-4.57</v>
       </c>
       <c r="K26" t="n">
-        <v>169.63</v>
+        <v>178.88</v>
       </c>
       <c r="L26" t="n">
-        <v>169.68</v>
+        <v>178.94</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-241.11</v>
+        <v>-235.3</v>
       </c>
       <c r="K27" t="n">
-        <v>162.93</v>
+        <v>159.01</v>
       </c>
       <c r="L27" t="n">
-        <v>291</v>
+        <v>283.99</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>187.14</v>
+        <v>189.81</v>
       </c>
       <c r="K28" t="n">
-        <v>-175.77</v>
+        <v>-178.28</v>
       </c>
       <c r="L28" t="n">
-        <v>256.74</v>
+        <v>260.4</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>34.36</v>
+        <v>36.87</v>
       </c>
       <c r="K29" t="n">
-        <v>33.14</v>
+        <v>35.55</v>
       </c>
       <c r="L29" t="n">
-        <v>47.73</v>
+        <v>51.22</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>54.96</v>
+        <v>54.39</v>
       </c>
       <c r="K30" t="n">
-        <v>-52.37</v>
+        <v>-51.83</v>
       </c>
       <c r="L30" t="n">
-        <v>75.92</v>
+        <v>75.13</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>21.84</v>
+        <v>23.76</v>
       </c>
       <c r="K31" t="n">
-        <v>-37.56</v>
+        <v>-40.87</v>
       </c>
       <c r="L31" t="n">
-        <v>43.45</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-22.45</v>
+        <v>-22.33</v>
       </c>
       <c r="K32" t="n">
-        <v>74.62</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>77.92</v>
+        <v>77.48999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-61.55</v>
+        <v>-65.28</v>
       </c>
       <c r="K33" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="L33" t="n">
-        <v>61.64</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>17.69</v>
+        <v>18.29</v>
       </c>
       <c r="K34" t="n">
-        <v>64.3</v>
+        <v>66.47</v>
       </c>
       <c r="L34" t="n">
-        <v>66.69</v>
+        <v>68.94</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-82.81999999999999</v>
+        <v>-85.34</v>
       </c>
       <c r="K35" t="n">
-        <v>-65.48999999999999</v>
+        <v>-67.48</v>
       </c>
       <c r="L35" t="n">
-        <v>105.58</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="K36" t="n">
-        <v>-122</v>
+        <v>-122.67</v>
       </c>
       <c r="L36" t="n">
-        <v>122.04</v>
+        <v>122.71</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-136.78</v>
+        <v>-133.49</v>
       </c>
       <c r="K37" t="n">
-        <v>67.86</v>
+        <v>66.22</v>
       </c>
       <c r="L37" t="n">
-        <v>152.69</v>
+        <v>149.01</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>157.26</v>
+        <v>160.08</v>
       </c>
       <c r="K38" t="n">
-        <v>-31.01</v>
+        <v>-31.57</v>
       </c>
       <c r="L38" t="n">
-        <v>160.29</v>
+        <v>163.16</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>26.68</v>
+        <v>26.71</v>
       </c>
       <c r="K39" t="n">
-        <v>165.9</v>
+        <v>166.09</v>
       </c>
       <c r="L39" t="n">
-        <v>168.03</v>
+        <v>168.23</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>50.31</v>
+        <v>49.75</v>
       </c>
       <c r="K40" t="n">
-        <v>215.76</v>
+        <v>213.38</v>
       </c>
       <c r="L40" t="n">
-        <v>221.55</v>
+        <v>219.1</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-60.54</v>
+        <v>-66.06999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.94</v>
+        <v>-3.21</v>
       </c>
       <c r="L41" t="n">
-        <v>60.61</v>
+        <v>66.15000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>255.1</v>
+        <v>269.56</v>
       </c>
       <c r="K42" t="n">
-        <v>-111.45</v>
+        <v>-117.77</v>
       </c>
       <c r="L42" t="n">
-        <v>278.39</v>
+        <v>294.16</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>89.08</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>177.59</v>
+        <v>190.05</v>
       </c>
       <c r="L43" t="n">
-        <v>198.68</v>
+        <v>212.61</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-62.64</v>
+        <v>-60.45</v>
       </c>
       <c r="K44" t="n">
-        <v>64.76000000000001</v>
+        <v>62.49</v>
       </c>
       <c r="L44" t="n">
-        <v>90.09</v>
+        <v>86.94</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>66.37</v>
+        <v>64.94</v>
       </c>
       <c r="K45" t="n">
-        <v>-33.2</v>
+        <v>-32.48</v>
       </c>
       <c r="L45" t="n">
-        <v>74.20999999999999</v>
+        <v>72.61</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-53.69</v>
+        <v>-54.99</v>
       </c>
       <c r="K46" t="n">
-        <v>24.37</v>
+        <v>24.96</v>
       </c>
       <c r="L46" t="n">
-        <v>58.96</v>
+        <v>60.39</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-99.16</v>
+        <v>-95.38</v>
       </c>
       <c r="K47" t="n">
-        <v>15.01</v>
+        <v>14.44</v>
       </c>
       <c r="L47" t="n">
-        <v>100.29</v>
+        <v>96.47</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.19</v>
       </c>
       <c r="K48" t="n">
-        <v>-90.89</v>
+        <v>-89.66</v>
       </c>
       <c r="L48" t="n">
-        <v>91.27</v>
+        <v>90.03</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-26.88</v>
+        <v>-26.3</v>
       </c>
       <c r="K49" t="n">
-        <v>85.75</v>
+        <v>83.92</v>
       </c>
       <c r="L49" t="n">
-        <v>89.86</v>
+        <v>87.94</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-50.72</v>
+        <v>-54.11</v>
       </c>
       <c r="K50" t="n">
-        <v>-74.61</v>
+        <v>-79.59</v>
       </c>
       <c r="L50" t="n">
-        <v>90.22</v>
+        <v>96.23999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.45</v>
+        <v>-7.92</v>
       </c>
       <c r="K51" t="n">
-        <v>89.38</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>89.69</v>
+        <v>95.34</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>37.73</v>
+        <v>40.97</v>
       </c>
       <c r="K52" t="n">
-        <v>-84.8</v>
+        <v>-92.09999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>92.81</v>
+        <v>100.8</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>71.84</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>110.62</v>
+        <v>120.51</v>
       </c>
       <c r="L53" t="n">
-        <v>131.9</v>
+        <v>143.69</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>110.27</v>
+        <v>104.44</v>
       </c>
       <c r="K54" t="n">
-        <v>-312.37</v>
+        <v>-295.83</v>
       </c>
       <c r="L54" t="n">
-        <v>331.26</v>
+        <v>313.72</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>-151.03</v>
+        <v>-149.78</v>
       </c>
       <c r="K55" t="n">
-        <v>-81.62</v>
+        <v>-80.95</v>
       </c>
       <c r="L55" t="n">
-        <v>171.67</v>
+        <v>170.26</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>378.52</v>
+        <v>366.47</v>
       </c>
       <c r="K56" t="n">
-        <v>231.02</v>
+        <v>223.67</v>
       </c>
       <c r="L56" t="n">
-        <v>443.45</v>
+        <v>429.34</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-160.18</v>
+        <v>-170.75</v>
       </c>
       <c r="K57" t="n">
-        <v>183.53</v>
+        <v>195.64</v>
       </c>
       <c r="L57" t="n">
-        <v>243.6</v>
+        <v>259.67</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="K58" t="n">
-        <v>-198.23</v>
+        <v>-214.4</v>
       </c>
       <c r="L58" t="n">
-        <v>198.23</v>
+        <v>214.41</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>75.09999999999999</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>-60.24</v>
+        <v>-57.88</v>
       </c>
       <c r="L59" t="n">
-        <v>96.28</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-78.87</v>
+        <v>-77.06</v>
       </c>
       <c r="K60" t="n">
-        <v>-35.01</v>
+        <v>-34.21</v>
       </c>
       <c r="L60" t="n">
-        <v>86.29000000000001</v>
+        <v>84.31</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-29.55</v>
+        <v>-28.78</v>
       </c>
       <c r="K61" t="n">
-        <v>78.98</v>
+        <v>76.92</v>
       </c>
       <c r="L61" t="n">
-        <v>84.33</v>
+        <v>82.13</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>30.92</v>
+        <v>30.64</v>
       </c>
       <c r="K62" t="n">
-        <v>79.26000000000001</v>
+        <v>78.55</v>
       </c>
       <c r="L62" t="n">
-        <v>85.06999999999999</v>
+        <v>84.31999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-81.92</v>
+        <v>-77.33</v>
       </c>
       <c r="K63" t="n">
-        <v>101.79</v>
+        <v>96.09</v>
       </c>
       <c r="L63" t="n">
-        <v>130.65</v>
+        <v>123.35</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-125.26</v>
+        <v>-118.77</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="L64" t="n">
-        <v>125.27</v>
+        <v>118.78</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>200.53</v>
+        <v>190.75</v>
       </c>
       <c r="K65" t="n">
-        <v>-118.29</v>
+        <v>-112.52</v>
       </c>
       <c r="L65" t="n">
-        <v>232.82</v>
+        <v>221.46</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>95.16</v>
+        <v>97.94</v>
       </c>
       <c r="K66" t="n">
-        <v>-69.84</v>
+        <v>-71.89</v>
       </c>
       <c r="L66" t="n">
-        <v>118.04</v>
+        <v>121.49</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-128.69</v>
+        <v>-130.18</v>
       </c>
       <c r="K67" t="n">
-        <v>29.97</v>
+        <v>30.32</v>
       </c>
       <c r="L67" t="n">
-        <v>132.14</v>
+        <v>133.67</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-111.69</v>
+        <v>-119.24</v>
       </c>
       <c r="K68" t="n">
-        <v>-62.02</v>
+        <v>-66.20999999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>127.75</v>
+        <v>136.39</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>248.72</v>
+        <v>247.03</v>
       </c>
       <c r="K69" t="n">
-        <v>44.78</v>
+        <v>44.47</v>
       </c>
       <c r="L69" t="n">
-        <v>252.72</v>
+        <v>251</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>127.94</v>
+        <v>138.03</v>
       </c>
       <c r="K70" t="n">
-        <v>-28.04</v>
+        <v>-30.25</v>
       </c>
       <c r="L70" t="n">
-        <v>130.98</v>
+        <v>141.31</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>292.34</v>
+        <v>308.29</v>
       </c>
       <c r="K71" t="n">
-        <v>-37.55</v>
+        <v>-39.6</v>
       </c>
       <c r="L71" t="n">
-        <v>294.75</v>
+        <v>310.82</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-203.45</v>
+        <v>-219.06</v>
       </c>
       <c r="K72" t="n">
-        <v>130.48</v>
+        <v>140.49</v>
       </c>
       <c r="L72" t="n">
-        <v>241.7</v>
+        <v>260.24</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>65.31999999999999</v>
+        <v>69.34</v>
       </c>
       <c r="K73" t="n">
-        <v>-234.91</v>
+        <v>-249.41</v>
       </c>
       <c r="L73" t="n">
-        <v>243.83</v>
+        <v>258.87</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>32.26</v>
+        <v>33.71</v>
       </c>
       <c r="K74" t="n">
-        <v>-44.18</v>
+        <v>-46.16</v>
       </c>
       <c r="L74" t="n">
-        <v>54.71</v>
+        <v>57.16</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-60.26</v>
+        <v>-58.9</v>
       </c>
       <c r="K75" t="n">
-        <v>-63.85</v>
+        <v>-62.41</v>
       </c>
       <c r="L75" t="n">
-        <v>87.8</v>
+        <v>85.81</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>42.01</v>
+        <v>43.66</v>
       </c>
       <c r="K76" t="n">
-        <v>34.33</v>
+        <v>35.68</v>
       </c>
       <c r="L76" t="n">
-        <v>54.25</v>
+        <v>56.38</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>20.44</v>
+        <v>19.3</v>
       </c>
       <c r="K77" t="n">
-        <v>115.38</v>
+        <v>108.98</v>
       </c>
       <c r="L77" t="n">
-        <v>117.17</v>
+        <v>110.67</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-19.28</v>
+        <v>-20.52</v>
       </c>
       <c r="K78" t="n">
-        <v>55.6</v>
+        <v>59.19</v>
       </c>
       <c r="L78" t="n">
-        <v>58.85</v>
+        <v>62.65</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-41.25</v>
+        <v>-43.18</v>
       </c>
       <c r="K79" t="n">
-        <v>53.74</v>
+        <v>56.26</v>
       </c>
       <c r="L79" t="n">
-        <v>67.75</v>
+        <v>70.92</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>180.08</v>
+        <v>173.8</v>
       </c>
       <c r="K80" t="n">
-        <v>-78.79000000000001</v>
+        <v>-76.04000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>196.57</v>
+        <v>189.71</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>-109.06</v>
+        <v>-112.69</v>
       </c>
       <c r="K81" t="n">
-        <v>-17.64</v>
+        <v>-18.23</v>
       </c>
       <c r="L81" t="n">
-        <v>110.48</v>
+        <v>114.16</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-134.67</v>
+        <v>-136.66</v>
       </c>
       <c r="K82" t="n">
-        <v>-55.34</v>
+        <v>-56.16</v>
       </c>
       <c r="L82" t="n">
-        <v>145.6</v>
+        <v>147.75</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-194.65</v>
+        <v>-197.34</v>
       </c>
       <c r="K83" t="n">
-        <v>-168.59</v>
+        <v>-170.92</v>
       </c>
       <c r="L83" t="n">
-        <v>257.51</v>
+        <v>261.07</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-42.44</v>
+        <v>-45.66</v>
       </c>
       <c r="K84" t="n">
-        <v>-114.78</v>
+        <v>-123.48</v>
       </c>
       <c r="L84" t="n">
-        <v>122.38</v>
+        <v>131.65</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>126.22</v>
+        <v>132.95</v>
       </c>
       <c r="K85" t="n">
-        <v>-92.18000000000001</v>
+        <v>-97.09999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>156.3</v>
+        <v>164.63</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-203.77</v>
+        <v>-216.98</v>
       </c>
       <c r="K86" t="n">
-        <v>197.9</v>
+        <v>210.72</v>
       </c>
       <c r="L86" t="n">
-        <v>284.06</v>
+        <v>302.46</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>188.19</v>
+        <v>197.09</v>
       </c>
       <c r="K87" t="n">
-        <v>195.48</v>
+        <v>204.73</v>
       </c>
       <c r="L87" t="n">
-        <v>271.34</v>
+        <v>284.18</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>-18.96</v>
+        <v>-19.65</v>
       </c>
       <c r="K88" t="n">
-        <v>-276.44</v>
+        <v>-286.46</v>
       </c>
       <c r="L88" t="n">
-        <v>277.09</v>
+        <v>287.14</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-29.xlsx
+++ b/output/2025-09-29.xlsx
@@ -628,25 +628,25 @@
         <v>4.38</v>
       </c>
       <c r="F14" t="n">
-        <v>12.54</v>
+        <v>10.63</v>
       </c>
       <c r="G14" t="n">
-        <v>80.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>81.7</v>
+        <v>79.8</v>
       </c>
       <c r="I14" t="n">
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-72.61</v>
+        <v>-76</v>
       </c>
       <c r="K14" t="n">
-        <v>50.78</v>
+        <v>53.93</v>
       </c>
       <c r="L14" t="n">
-        <v>88.59999999999999</v>
+        <v>93.19</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>5.19</v>
       </c>
       <c r="F15" t="n">
-        <v>12.49</v>
+        <v>11.67</v>
       </c>
       <c r="G15" t="n">
-        <v>87.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="H15" t="n">
-        <v>87.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-46.21</v>
+        <v>-52.78</v>
       </c>
       <c r="K15" t="n">
-        <v>24.41</v>
+        <v>31.49</v>
       </c>
       <c r="L15" t="n">
-        <v>52.26</v>
+        <v>61.46</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>4.67</v>
       </c>
       <c r="F16" t="n">
-        <v>13.04</v>
+        <v>12.44</v>
       </c>
       <c r="G16" t="n">
-        <v>82.7</v>
+        <v>92.2</v>
       </c>
       <c r="H16" t="n">
-        <v>84.3</v>
+        <v>81.2</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>88.06999999999999</v>
+        <v>87.37</v>
       </c>
       <c r="K16" t="n">
-        <v>-30.5</v>
+        <v>-30.15</v>
       </c>
       <c r="L16" t="n">
-        <v>93.20999999999999</v>
+        <v>92.43000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>4.5</v>
       </c>
       <c r="F17" t="n">
-        <v>12.72</v>
+        <v>13.01</v>
       </c>
       <c r="G17" t="n">
-        <v>87.8</v>
+        <v>85.8</v>
       </c>
       <c r="H17" t="n">
-        <v>85.5</v>
+        <v>83.7</v>
       </c>
       <c r="I17" t="n">
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-29.69</v>
+        <v>-29.81</v>
       </c>
       <c r="K17" t="n">
-        <v>-89.92</v>
+        <v>-101.28</v>
       </c>
       <c r="L17" t="n">
-        <v>94.69</v>
+        <v>105.58</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>4.61</v>
       </c>
       <c r="F18" t="n">
-        <v>12.32</v>
+        <v>12.69</v>
       </c>
       <c r="G18" t="n">
-        <v>82.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="H18" t="n">
-        <v>85.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-85.92</v>
+        <v>-91.63</v>
       </c>
       <c r="K18" t="n">
-        <v>-40.66</v>
+        <v>-44</v>
       </c>
       <c r="L18" t="n">
-        <v>95.06</v>
+        <v>101.65</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>4.13</v>
       </c>
       <c r="F19" t="n">
-        <v>14.33</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>74.40000000000001</v>
+        <v>118.1</v>
       </c>
       <c r="H19" t="n">
-        <v>88.3</v>
+        <v>77</v>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>125.7</v>
+        <v>126.23</v>
       </c>
       <c r="K19" t="n">
-        <v>46.3</v>
+        <v>43.27</v>
       </c>
       <c r="L19" t="n">
-        <v>133.95</v>
+        <v>133.44</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>4.35</v>
       </c>
       <c r="F20" t="n">
-        <v>12.41</v>
+        <v>10.44</v>
       </c>
       <c r="G20" t="n">
-        <v>88.2</v>
+        <v>79.5</v>
       </c>
       <c r="H20" t="n">
-        <v>81</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>32.19</v>
+        <v>58.66</v>
       </c>
       <c r="K20" t="n">
-        <v>-109.83</v>
+        <v>-123.96</v>
       </c>
       <c r="L20" t="n">
-        <v>114.45</v>
+        <v>137.14</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>4.57</v>
       </c>
       <c r="F21" t="n">
-        <v>13.14</v>
+        <v>10.47</v>
       </c>
       <c r="G21" t="n">
-        <v>89.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>80.8</v>
+        <v>84.5</v>
       </c>
       <c r="I21" t="n">
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>101.44</v>
+        <v>121.83</v>
       </c>
       <c r="K21" t="n">
-        <v>113.59</v>
+        <v>115.37</v>
       </c>
       <c r="L21" t="n">
-        <v>152.29</v>
+        <v>167.79</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>4.94</v>
       </c>
       <c r="F22" t="n">
-        <v>12.62</v>
+        <v>11.14</v>
       </c>
       <c r="G22" t="n">
-        <v>92.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>78.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-74.23999999999999</v>
+        <v>-59.81</v>
       </c>
       <c r="K22" t="n">
-        <v>-88.56999999999999</v>
+        <v>-103.95</v>
       </c>
       <c r="L22" t="n">
-        <v>115.57</v>
+        <v>119.92</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>4.15</v>
       </c>
       <c r="F23" t="n">
-        <v>12.27</v>
+        <v>9.67</v>
       </c>
       <c r="G23" t="n">
-        <v>89.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>78.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>15.81</v>
+        <v>41.93</v>
       </c>
       <c r="K23" t="n">
-        <v>183.28</v>
+        <v>203.16</v>
       </c>
       <c r="L23" t="n">
-        <v>183.96</v>
+        <v>207.44</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>4.17</v>
       </c>
       <c r="F24" t="n">
-        <v>12.44</v>
+        <v>8.58</v>
       </c>
       <c r="G24" t="n">
-        <v>78.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>77.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>159.61</v>
+        <v>170.61</v>
       </c>
       <c r="K24" t="n">
-        <v>-40.6</v>
+        <v>-30.87</v>
       </c>
       <c r="L24" t="n">
-        <v>164.69</v>
+        <v>173.38</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>5.22</v>
       </c>
       <c r="F25" t="n">
-        <v>12.67</v>
+        <v>12.74</v>
       </c>
       <c r="G25" t="n">
-        <v>93.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="H25" t="n">
-        <v>80.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>107.15</v>
+        <v>153.01</v>
       </c>
       <c r="K25" t="n">
-        <v>153.42</v>
+        <v>173.76</v>
       </c>
       <c r="L25" t="n">
-        <v>187.13</v>
+        <v>231.53</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>3.75</v>
       </c>
       <c r="F26" t="n">
-        <v>12.08</v>
+        <v>6.98</v>
       </c>
       <c r="G26" t="n">
-        <v>82</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>75.8</v>
+        <v>80.8</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.57</v>
+        <v>46.85</v>
       </c>
       <c r="K26" t="n">
-        <v>178.88</v>
+        <v>186.74</v>
       </c>
       <c r="L26" t="n">
-        <v>178.94</v>
+        <v>192.52</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>4.29</v>
       </c>
       <c r="F27" t="n">
-        <v>12.93</v>
+        <v>7.9</v>
       </c>
       <c r="G27" t="n">
-        <v>89.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>82.3</v>
+        <v>84.5</v>
       </c>
       <c r="I27" t="n">
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-235.3</v>
+        <v>-219.93</v>
       </c>
       <c r="K27" t="n">
-        <v>159.01</v>
+        <v>169.53</v>
       </c>
       <c r="L27" t="n">
-        <v>283.99</v>
+        <v>277.69</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>4.35</v>
       </c>
       <c r="F28" t="n">
-        <v>12.49</v>
+        <v>14.6</v>
       </c>
       <c r="G28" t="n">
-        <v>86.2</v>
+        <v>81.2</v>
       </c>
       <c r="H28" t="n">
-        <v>91.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>189.81</v>
+        <v>260.35</v>
       </c>
       <c r="K28" t="n">
-        <v>-178.28</v>
+        <v>-190.09</v>
       </c>
       <c r="L28" t="n">
-        <v>260.4</v>
+        <v>322.36</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>4.79</v>
       </c>
       <c r="F29" t="n">
-        <v>12.43</v>
+        <v>12.37</v>
       </c>
       <c r="G29" t="n">
-        <v>84.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>86.5</v>
+        <v>82.2</v>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>36.87</v>
+        <v>44.79</v>
       </c>
       <c r="K29" t="n">
-        <v>35.55</v>
+        <v>40.94</v>
       </c>
       <c r="L29" t="n">
-        <v>51.22</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>12.84</v>
+        <v>14.6</v>
       </c>
       <c r="G30" t="n">
-        <v>80.8</v>
+        <v>88.2</v>
       </c>
       <c r="H30" t="n">
-        <v>90.8</v>
+        <v>80.2</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>54.39</v>
+        <v>57.46</v>
       </c>
       <c r="K30" t="n">
-        <v>-51.83</v>
+        <v>-53.45</v>
       </c>
       <c r="L30" t="n">
-        <v>75.13</v>
+        <v>78.48</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>4.98</v>
       </c>
       <c r="F31" t="n">
-        <v>12.16</v>
+        <v>14.28</v>
       </c>
       <c r="G31" t="n">
-        <v>73</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>87.3</v>
+        <v>76.3</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>23.76</v>
+        <v>30.58</v>
       </c>
       <c r="K31" t="n">
-        <v>-40.87</v>
+        <v>-44.23</v>
       </c>
       <c r="L31" t="n">
-        <v>47.28</v>
+        <v>53.77</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>4.44</v>
       </c>
       <c r="F32" t="n">
-        <v>12.85</v>
+        <v>12.21</v>
       </c>
       <c r="G32" t="n">
-        <v>77.7</v>
+        <v>88.3</v>
       </c>
       <c r="H32" t="n">
-        <v>83.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-22.33</v>
+        <v>-22.17</v>
       </c>
       <c r="K32" t="n">
-        <v>74.20999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="L32" t="n">
-        <v>77.48999999999999</v>
+        <v>89.45999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>5.03</v>
       </c>
       <c r="F33" t="n">
-        <v>13.28</v>
+        <v>11.85</v>
       </c>
       <c r="G33" t="n">
-        <v>73.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="H33" t="n">
-        <v>85.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-65.28</v>
+        <v>-69.68000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>3.48</v>
+        <v>-0.74</v>
       </c>
       <c r="L33" t="n">
-        <v>65.37</v>
+        <v>69.68000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>5.21</v>
       </c>
       <c r="F34" t="n">
-        <v>12.57</v>
+        <v>14.6</v>
       </c>
       <c r="G34" t="n">
-        <v>95</v>
+        <v>82.8</v>
       </c>
       <c r="H34" t="n">
-        <v>86.59999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="I34" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>18.29</v>
+        <v>29.79</v>
       </c>
       <c r="K34" t="n">
-        <v>66.47</v>
+        <v>84.11</v>
       </c>
       <c r="L34" t="n">
-        <v>68.94</v>
+        <v>89.23</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>4.38</v>
       </c>
       <c r="F35" t="n">
-        <v>12.41</v>
+        <v>11.44</v>
       </c>
       <c r="G35" t="n">
-        <v>106.8</v>
+        <v>79.5</v>
       </c>
       <c r="H35" t="n">
-        <v>85.2</v>
+        <v>93.2</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-85.34</v>
+        <v>-85.98</v>
       </c>
       <c r="K35" t="n">
-        <v>-67.48</v>
+        <v>-76.25</v>
       </c>
       <c r="L35" t="n">
-        <v>108.8</v>
+        <v>114.92</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>4.26</v>
       </c>
       <c r="F36" t="n">
-        <v>12.74</v>
+        <v>13.2</v>
       </c>
       <c r="G36" t="n">
-        <v>88.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>87.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>3.18</v>
+        <v>22.14</v>
       </c>
       <c r="K36" t="n">
-        <v>-122.67</v>
+        <v>-135.13</v>
       </c>
       <c r="L36" t="n">
-        <v>122.71</v>
+        <v>136.93</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>4.69</v>
       </c>
       <c r="F37" t="n">
-        <v>13.03</v>
+        <v>11.58</v>
       </c>
       <c r="G37" t="n">
-        <v>81.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>79.5</v>
+        <v>80.5</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-133.49</v>
+        <v>-127.79</v>
       </c>
       <c r="K37" t="n">
-        <v>66.22</v>
+        <v>69.19</v>
       </c>
       <c r="L37" t="n">
-        <v>149.01</v>
+        <v>145.32</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>4.94</v>
       </c>
       <c r="F38" t="n">
-        <v>12.87</v>
+        <v>14.6</v>
       </c>
       <c r="G38" t="n">
-        <v>85.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="H38" t="n">
-        <v>89.09999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>160.08</v>
+        <v>212.8</v>
       </c>
       <c r="K38" t="n">
-        <v>-31.57</v>
+        <v>-35.73</v>
       </c>
       <c r="L38" t="n">
-        <v>163.16</v>
+        <v>215.78</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>4.46</v>
       </c>
       <c r="F39" t="n">
-        <v>12.04</v>
+        <v>13.36</v>
       </c>
       <c r="G39" t="n">
-        <v>88.7</v>
+        <v>72.2</v>
       </c>
       <c r="H39" t="n">
-        <v>87.59999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>26.71</v>
+        <v>60.32</v>
       </c>
       <c r="K39" t="n">
-        <v>166.09</v>
+        <v>196.7</v>
       </c>
       <c r="L39" t="n">
-        <v>168.23</v>
+        <v>205.74</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>5.16</v>
       </c>
       <c r="F40" t="n">
-        <v>12.55</v>
+        <v>10.44</v>
       </c>
       <c r="G40" t="n">
-        <v>78.8</v>
+        <v>82.5</v>
       </c>
       <c r="H40" t="n">
-        <v>74.2</v>
+        <v>79.2</v>
       </c>
       <c r="I40" t="n">
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>49.75</v>
+        <v>80.83</v>
       </c>
       <c r="K40" t="n">
-        <v>213.38</v>
+        <v>219.82</v>
       </c>
       <c r="L40" t="n">
-        <v>219.1</v>
+        <v>234.21</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>5.08</v>
       </c>
       <c r="F41" t="n">
-        <v>13.02</v>
+        <v>12.27</v>
       </c>
       <c r="G41" t="n">
-        <v>84.5</v>
+        <v>91.8</v>
       </c>
       <c r="H41" t="n">
-        <v>78.8</v>
+        <v>82</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-66.06999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.21</v>
+        <v>-17.57</v>
       </c>
       <c r="L41" t="n">
-        <v>66.15000000000001</v>
+        <v>20.07</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>5.44</v>
       </c>
       <c r="F42" t="n">
-        <v>12.58</v>
+        <v>14.6</v>
       </c>
       <c r="G42" t="n">
-        <v>89.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="H42" t="n">
-        <v>85.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>269.56</v>
+        <v>324.06</v>
       </c>
       <c r="K42" t="n">
-        <v>-117.77</v>
+        <v>-97.47</v>
       </c>
       <c r="L42" t="n">
-        <v>294.16</v>
+        <v>338.4</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>4.52</v>
       </c>
       <c r="F43" t="n">
-        <v>13.01</v>
+        <v>14.6</v>
       </c>
       <c r="G43" t="n">
-        <v>87</v>
+        <v>91.7</v>
       </c>
       <c r="H43" t="n">
-        <v>80.7</v>
+        <v>83.3</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>95.31999999999999</v>
+        <v>157.38</v>
       </c>
       <c r="K43" t="n">
-        <v>190.05</v>
+        <v>177.35</v>
       </c>
       <c r="L43" t="n">
-        <v>212.61</v>
+        <v>237.11</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>4.49</v>
       </c>
       <c r="F44" t="n">
-        <v>12.47</v>
+        <v>10.98</v>
       </c>
       <c r="G44" t="n">
-        <v>99.2</v>
+        <v>80.8</v>
       </c>
       <c r="H44" t="n">
-        <v>79.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I44" t="n">
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-60.45</v>
+        <v>-64.56999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>62.49</v>
+        <v>68.77</v>
       </c>
       <c r="L44" t="n">
-        <v>86.94</v>
+        <v>94.33</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>4.72</v>
       </c>
       <c r="F45" t="n">
-        <v>12.64</v>
+        <v>12.57</v>
       </c>
       <c r="G45" t="n">
-        <v>88.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>92.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>64.94</v>
+        <v>77.66</v>
       </c>
       <c r="K45" t="n">
-        <v>-32.48</v>
+        <v>-37.84</v>
       </c>
       <c r="L45" t="n">
-        <v>72.61</v>
+        <v>86.39</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>4.51</v>
       </c>
       <c r="F46" t="n">
-        <v>12.09</v>
+        <v>14.59</v>
       </c>
       <c r="G46" t="n">
-        <v>85.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="H46" t="n">
-        <v>88.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-54.99</v>
+        <v>-67.8</v>
       </c>
       <c r="K46" t="n">
-        <v>24.96</v>
+        <v>32.88</v>
       </c>
       <c r="L46" t="n">
-        <v>60.39</v>
+        <v>75.34999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>4.72</v>
       </c>
       <c r="F47" t="n">
-        <v>12.68</v>
+        <v>12.71</v>
       </c>
       <c r="G47" t="n">
-        <v>84.7</v>
+        <v>69.7</v>
       </c>
       <c r="H47" t="n">
-        <v>84.2</v>
+        <v>77.5</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-95.38</v>
+        <v>-39</v>
       </c>
       <c r="K47" t="n">
-        <v>14.44</v>
+        <v>-39.97</v>
       </c>
       <c r="L47" t="n">
-        <v>96.47</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="48">
@@ -2053,28 +2053,28 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.77</v>
+        <v>5.19</v>
       </c>
       <c r="F48" t="n">
-        <v>12.72</v>
+        <v>14.24</v>
       </c>
       <c r="G48" t="n">
-        <v>69.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>85.5</v>
+        <v>85.2</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-8.19</v>
+        <v>-60.07</v>
       </c>
       <c r="K48" t="n">
-        <v>-89.66</v>
+        <v>-49.44</v>
       </c>
       <c r="L48" t="n">
-        <v>90.03</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="49">
@@ -2095,28 +2095,28 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.62</v>
+        <v>4.25</v>
       </c>
       <c r="F49" t="n">
-        <v>12.44</v>
+        <v>11.6</v>
       </c>
       <c r="G49" t="n">
-        <v>85.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="H49" t="n">
-        <v>84</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-26.3</v>
+        <v>-14.6</v>
       </c>
       <c r="K49" t="n">
-        <v>83.92</v>
+        <v>-83.56</v>
       </c>
       <c r="L49" t="n">
-        <v>87.94</v>
+        <v>84.83</v>
       </c>
     </row>
     <row r="50">
@@ -2137,28 +2137,28 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.81</v>
+        <v>4.54</v>
       </c>
       <c r="F50" t="n">
-        <v>12.27</v>
+        <v>10.7</v>
       </c>
       <c r="G50" t="n">
-        <v>86.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="H50" t="n">
-        <v>78.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-54.11</v>
+        <v>29.86</v>
       </c>
       <c r="K50" t="n">
-        <v>-79.59</v>
+        <v>132.38</v>
       </c>
       <c r="L50" t="n">
-        <v>96.23999999999999</v>
+        <v>135.7</v>
       </c>
     </row>
     <row r="51">
@@ -2179,28 +2179,28 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.91</v>
+        <v>4.7</v>
       </c>
       <c r="F51" t="n">
-        <v>12.22</v>
+        <v>13.58</v>
       </c>
       <c r="G51" t="n">
-        <v>89</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>83.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.92</v>
+        <v>-98.97</v>
       </c>
       <c r="K51" t="n">
-        <v>95.01000000000001</v>
+        <v>-126.6</v>
       </c>
       <c r="L51" t="n">
-        <v>95.34</v>
+        <v>160.7</v>
       </c>
     </row>
     <row r="52">
@@ -2221,28 +2221,28 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.27</v>
+        <v>4.91</v>
       </c>
       <c r="F52" t="n">
-        <v>12.68</v>
+        <v>13.5</v>
       </c>
       <c r="G52" t="n">
-        <v>77.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>78.09999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I52" t="n">
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>40.97</v>
+        <v>95.69</v>
       </c>
       <c r="K52" t="n">
-        <v>-92.09999999999999</v>
+        <v>148.37</v>
       </c>
       <c r="L52" t="n">
-        <v>100.8</v>
+        <v>176.55</v>
       </c>
     </row>
     <row r="53">
@@ -2263,28 +2263,28 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.04</v>
+        <v>5.49</v>
       </c>
       <c r="F53" t="n">
-        <v>12.78</v>
+        <v>14.6</v>
       </c>
       <c r="G53" t="n">
-        <v>81</v>
+        <v>101.7</v>
       </c>
       <c r="H53" t="n">
-        <v>88.40000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I53" t="n">
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>78.26000000000001</v>
+        <v>-5.35</v>
       </c>
       <c r="K53" t="n">
-        <v>120.51</v>
+        <v>219.45</v>
       </c>
       <c r="L53" t="n">
-        <v>143.69</v>
+        <v>219.51</v>
       </c>
     </row>
     <row r="54">
@@ -2305,28 +2305,28 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5.72</v>
+        <v>5.17</v>
       </c>
       <c r="F54" t="n">
-        <v>13.06</v>
+        <v>10.05</v>
       </c>
       <c r="G54" t="n">
-        <v>82.09999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="H54" t="n">
-        <v>78.3</v>
+        <v>74.7</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>104.44</v>
+        <v>103.36</v>
       </c>
       <c r="K54" t="n">
-        <v>-295.83</v>
+        <v>-181</v>
       </c>
       <c r="L54" t="n">
-        <v>313.72</v>
+        <v>208.43</v>
       </c>
     </row>
     <row r="55">
@@ -2347,28 +2347,28 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.19</v>
+        <v>4.81</v>
       </c>
       <c r="F55" t="n">
-        <v>12.53</v>
+        <v>11.06</v>
       </c>
       <c r="G55" t="n">
-        <v>75.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>83.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>-149.78</v>
+        <v>174.31</v>
       </c>
       <c r="K55" t="n">
-        <v>-80.95</v>
+        <v>119.68</v>
       </c>
       <c r="L55" t="n">
-        <v>170.26</v>
+        <v>211.44</v>
       </c>
     </row>
     <row r="56">
@@ -2389,28 +2389,28 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.15</v>
+        <v>4.27</v>
       </c>
       <c r="F56" t="n">
-        <v>13.08</v>
+        <v>13.69</v>
       </c>
       <c r="G56" t="n">
-        <v>93.3</v>
+        <v>84.3</v>
       </c>
       <c r="H56" t="n">
-        <v>80.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>366.47</v>
+        <v>237.33</v>
       </c>
       <c r="K56" t="n">
-        <v>223.67</v>
+        <v>-59.05</v>
       </c>
       <c r="L56" t="n">
-        <v>429.34</v>
+        <v>244.57</v>
       </c>
     </row>
     <row r="57">
@@ -2431,28 +2431,28 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.09</v>
+        <v>5.66</v>
       </c>
       <c r="F57" t="n">
-        <v>13.34</v>
+        <v>14.6</v>
       </c>
       <c r="G57" t="n">
-        <v>83.2</v>
+        <v>91</v>
       </c>
       <c r="H57" t="n">
-        <v>84.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="I57" t="n">
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-170.75</v>
+        <v>51.17</v>
       </c>
       <c r="K57" t="n">
-        <v>195.64</v>
+        <v>402.1</v>
       </c>
       <c r="L57" t="n">
-        <v>259.67</v>
+        <v>405.34</v>
       </c>
     </row>
     <row r="58">
@@ -2473,28 +2473,28 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.99</v>
+        <v>4.4</v>
       </c>
       <c r="F58" t="n">
-        <v>13.16</v>
+        <v>11.34</v>
       </c>
       <c r="G58" t="n">
-        <v>83.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="H58" t="n">
-        <v>76.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="I58" t="n">
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>1.52</v>
+        <v>52.7</v>
       </c>
       <c r="K58" t="n">
-        <v>-214.4</v>
+        <v>35.33</v>
       </c>
       <c r="L58" t="n">
-        <v>214.41</v>
+        <v>63.45</v>
       </c>
     </row>
     <row r="59">
@@ -2515,28 +2515,28 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.2</v>
+        <v>4.99</v>
       </c>
       <c r="F59" t="n">
-        <v>12.63</v>
+        <v>14.6</v>
       </c>
       <c r="G59" t="n">
-        <v>85.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>81.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>72.15000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="K59" t="n">
-        <v>-57.88</v>
+        <v>-79.28</v>
       </c>
       <c r="L59" t="n">
-        <v>92.5</v>
+        <v>79.86</v>
       </c>
     </row>
     <row r="60">
@@ -2557,28 +2557,28 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.2</v>
+        <v>4.97</v>
       </c>
       <c r="F60" t="n">
-        <v>12.19</v>
+        <v>12.86</v>
       </c>
       <c r="G60" t="n">
-        <v>86.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="H60" t="n">
-        <v>90.3</v>
+        <v>85</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-77.06</v>
+        <v>-4.69</v>
       </c>
       <c r="K60" t="n">
-        <v>-34.21</v>
+        <v>63.88</v>
       </c>
       <c r="L60" t="n">
-        <v>84.31</v>
+        <v>64.05</v>
       </c>
     </row>
     <row r="61">
@@ -2599,28 +2599,28 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>5.32</v>
+        <v>5.4</v>
       </c>
       <c r="F61" t="n">
-        <v>13.02</v>
+        <v>14.12</v>
       </c>
       <c r="G61" t="n">
-        <v>90</v>
+        <v>94.8</v>
       </c>
       <c r="H61" t="n">
-        <v>82.09999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-28.78</v>
+        <v>-63.43</v>
       </c>
       <c r="K61" t="n">
-        <v>76.92</v>
+        <v>-29.98</v>
       </c>
       <c r="L61" t="n">
-        <v>82.13</v>
+        <v>70.16</v>
       </c>
     </row>
     <row r="62">
@@ -2641,28 +2641,28 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.65</v>
+        <v>5.74</v>
       </c>
       <c r="F62" t="n">
-        <v>12.59</v>
+        <v>12.69</v>
       </c>
       <c r="G62" t="n">
-        <v>79.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="H62" t="n">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="I62" t="n">
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>30.64</v>
+        <v>105.67</v>
       </c>
       <c r="K62" t="n">
-        <v>78.55</v>
+        <v>-9.59</v>
       </c>
       <c r="L62" t="n">
-        <v>84.31999999999999</v>
+        <v>106.11</v>
       </c>
     </row>
     <row r="63">
@@ -2683,28 +2683,28 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.24</v>
+        <v>4.81</v>
       </c>
       <c r="F63" t="n">
-        <v>12.63</v>
+        <v>14.6</v>
       </c>
       <c r="G63" t="n">
-        <v>96.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>86.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I63" t="n">
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-77.33</v>
+        <v>-31.02</v>
       </c>
       <c r="K63" t="n">
-        <v>96.09</v>
+        <v>-99.81999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>123.35</v>
+        <v>104.53</v>
       </c>
     </row>
     <row r="64">
@@ -2725,28 +2725,28 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>5.64</v>
+        <v>4.29</v>
       </c>
       <c r="F64" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="G64" t="n">
-        <v>76.5</v>
+        <v>92.5</v>
       </c>
       <c r="H64" t="n">
-        <v>85.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-118.77</v>
+        <v>49.24</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.8</v>
+        <v>118.32</v>
       </c>
       <c r="L64" t="n">
-        <v>118.78</v>
+        <v>128.15</v>
       </c>
     </row>
     <row r="65">
@@ -2767,28 +2767,28 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.89</v>
+        <v>5.51</v>
       </c>
       <c r="F65" t="n">
-        <v>13.5</v>
+        <v>13.66</v>
       </c>
       <c r="G65" t="n">
-        <v>91.2</v>
+        <v>79.2</v>
       </c>
       <c r="H65" t="n">
-        <v>86.7</v>
+        <v>88.5</v>
       </c>
       <c r="I65" t="n">
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>190.75</v>
+        <v>-135.83</v>
       </c>
       <c r="K65" t="n">
-        <v>-112.52</v>
+        <v>-96.13</v>
       </c>
       <c r="L65" t="n">
-        <v>221.46</v>
+        <v>166.4</v>
       </c>
     </row>
     <row r="66">
@@ -2809,28 +2809,28 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.43</v>
+        <v>5.35</v>
       </c>
       <c r="F66" t="n">
-        <v>12.19</v>
+        <v>14.6</v>
       </c>
       <c r="G66" t="n">
-        <v>57.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="H66" t="n">
-        <v>79.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>97.94</v>
+        <v>-54.07</v>
       </c>
       <c r="K66" t="n">
-        <v>-71.89</v>
+        <v>151.42</v>
       </c>
       <c r="L66" t="n">
-        <v>121.49</v>
+        <v>160.79</v>
       </c>
     </row>
     <row r="67">
@@ -2851,28 +2851,28 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.13</v>
+        <v>5.69</v>
       </c>
       <c r="F67" t="n">
-        <v>13.03</v>
+        <v>14.6</v>
       </c>
       <c r="G67" t="n">
-        <v>80.3</v>
+        <v>93.7</v>
       </c>
       <c r="H67" t="n">
-        <v>82.2</v>
+        <v>75.5</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-130.18</v>
+        <v>2.28</v>
       </c>
       <c r="K67" t="n">
-        <v>30.32</v>
+        <v>196.17</v>
       </c>
       <c r="L67" t="n">
-        <v>133.67</v>
+        <v>196.19</v>
       </c>
     </row>
     <row r="68">
@@ -2893,28 +2893,28 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.57</v>
+        <v>4.89</v>
       </c>
       <c r="F68" t="n">
-        <v>12.57</v>
+        <v>14.6</v>
       </c>
       <c r="G68" t="n">
-        <v>101.5</v>
+        <v>92.7</v>
       </c>
       <c r="H68" t="n">
-        <v>86.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-119.24</v>
+        <v>-83.38</v>
       </c>
       <c r="K68" t="n">
-        <v>-66.20999999999999</v>
+        <v>-137</v>
       </c>
       <c r="L68" t="n">
-        <v>136.39</v>
+        <v>160.38</v>
       </c>
     </row>
     <row r="69">
@@ -2935,28 +2935,28 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.84</v>
+        <v>4.28</v>
       </c>
       <c r="F69" t="n">
-        <v>12.5</v>
+        <v>12.47</v>
       </c>
       <c r="G69" t="n">
-        <v>79.59999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>81.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>247.03</v>
+        <v>22.8</v>
       </c>
       <c r="K69" t="n">
-        <v>44.47</v>
+        <v>178.18</v>
       </c>
       <c r="L69" t="n">
-        <v>251</v>
+        <v>179.63</v>
       </c>
     </row>
     <row r="70">
@@ -2977,28 +2977,28 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.11</v>
+        <v>6.22</v>
       </c>
       <c r="F70" t="n">
-        <v>12.59</v>
+        <v>14.6</v>
       </c>
       <c r="G70" t="n">
-        <v>92.5</v>
+        <v>85</v>
       </c>
       <c r="H70" t="n">
-        <v>83.7</v>
+        <v>77.5</v>
       </c>
       <c r="I70" t="n">
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>138.03</v>
+        <v>37.81</v>
       </c>
       <c r="K70" t="n">
-        <v>-30.25</v>
+        <v>262.85</v>
       </c>
       <c r="L70" t="n">
-        <v>141.31</v>
+        <v>265.55</v>
       </c>
     </row>
     <row r="71">
@@ -3019,28 +3019,28 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.56</v>
+        <v>5.39</v>
       </c>
       <c r="F71" t="n">
-        <v>12.61</v>
+        <v>14.6</v>
       </c>
       <c r="G71" t="n">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="H71" t="n">
-        <v>82.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>308.29</v>
+        <v>-292.54</v>
       </c>
       <c r="K71" t="n">
-        <v>-39.6</v>
+        <v>-212.85</v>
       </c>
       <c r="L71" t="n">
-        <v>310.82</v>
+        <v>361.77</v>
       </c>
     </row>
     <row r="72">
@@ -3061,28 +3061,28 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.19</v>
+        <v>5.31</v>
       </c>
       <c r="F72" t="n">
-        <v>12.64</v>
+        <v>12.7</v>
       </c>
       <c r="G72" t="n">
-        <v>85.8</v>
+        <v>78</v>
       </c>
       <c r="H72" t="n">
-        <v>84.59999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-219.06</v>
+        <v>240.39</v>
       </c>
       <c r="K72" t="n">
-        <v>140.49</v>
+        <v>192.16</v>
       </c>
       <c r="L72" t="n">
-        <v>260.24</v>
+        <v>307.75</v>
       </c>
     </row>
     <row r="73">
@@ -3103,28 +3103,28 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.28</v>
+        <v>5.17</v>
       </c>
       <c r="F73" t="n">
-        <v>12.8</v>
+        <v>13.98</v>
       </c>
       <c r="G73" t="n">
-        <v>96.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>78.8</v>
+        <v>81.5</v>
       </c>
       <c r="I73" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>69.34</v>
+        <v>285.19</v>
       </c>
       <c r="K73" t="n">
-        <v>-249.41</v>
+        <v>143.82</v>
       </c>
       <c r="L73" t="n">
-        <v>258.87</v>
+        <v>319.4</v>
       </c>
     </row>
     <row r="74">
@@ -3145,28 +3145,28 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
       <c r="F74" t="n">
-        <v>12.76</v>
+        <v>14.6</v>
       </c>
       <c r="G74" t="n">
-        <v>89.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="H74" t="n">
-        <v>81.5</v>
+        <v>89.8</v>
       </c>
       <c r="I74" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>33.71</v>
+        <v>-70.90000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-46.16</v>
+        <v>11.42</v>
       </c>
       <c r="L74" t="n">
-        <v>57.16</v>
+        <v>71.81</v>
       </c>
     </row>
     <row r="75">
@@ -3187,28 +3187,28 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.12</v>
+        <v>4.8</v>
       </c>
       <c r="F75" t="n">
-        <v>12.4</v>
+        <v>13.05</v>
       </c>
       <c r="G75" t="n">
-        <v>63.1</v>
+        <v>82.5</v>
       </c>
       <c r="H75" t="n">
-        <v>86.2</v>
+        <v>85</v>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-58.9</v>
+        <v>-64.06</v>
       </c>
       <c r="K75" t="n">
-        <v>-62.41</v>
+        <v>42.18</v>
       </c>
       <c r="L75" t="n">
-        <v>85.81</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="76">
@@ -3229,28 +3229,28 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.08</v>
+        <v>5.42</v>
       </c>
       <c r="F76" t="n">
-        <v>12.52</v>
+        <v>14.6</v>
       </c>
       <c r="G76" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>85</v>
+        <v>77.3</v>
       </c>
       <c r="I76" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>43.66</v>
+        <v>-96.20999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>35.68</v>
+        <v>-4.38</v>
       </c>
       <c r="L76" t="n">
-        <v>56.38</v>
+        <v>96.31</v>
       </c>
     </row>
     <row r="77">
@@ -3271,28 +3271,28 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.63</v>
+        <v>5.38</v>
       </c>
       <c r="F77" t="n">
-        <v>12.01</v>
+        <v>14.45</v>
       </c>
       <c r="G77" t="n">
-        <v>92.3</v>
+        <v>80.7</v>
       </c>
       <c r="H77" t="n">
-        <v>81.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="I77" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>19.3</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>108.98</v>
+        <v>-30.63</v>
       </c>
       <c r="L77" t="n">
-        <v>110.67</v>
+        <v>86.34999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3313,28 +3313,28 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.02</v>
+        <v>5.45</v>
       </c>
       <c r="F78" t="n">
-        <v>13.13</v>
+        <v>14.6</v>
       </c>
       <c r="G78" t="n">
-        <v>80.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>89.3</v>
+        <v>74.2</v>
       </c>
       <c r="I78" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-20.52</v>
+        <v>0.11</v>
       </c>
       <c r="K78" t="n">
-        <v>59.19</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>62.65</v>
+        <v>96.15000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3355,28 +3355,28 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.21</v>
+        <v>5.09</v>
       </c>
       <c r="F79" t="n">
-        <v>12.65</v>
+        <v>14.6</v>
       </c>
       <c r="G79" t="n">
-        <v>83.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="H79" t="n">
-        <v>81.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-43.18</v>
+        <v>-53.59</v>
       </c>
       <c r="K79" t="n">
-        <v>56.26</v>
+        <v>100.05</v>
       </c>
       <c r="L79" t="n">
-        <v>70.92</v>
+        <v>113.5</v>
       </c>
     </row>
     <row r="80">
@@ -3397,28 +3397,28 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.38</v>
+        <v>4.97</v>
       </c>
       <c r="F80" t="n">
-        <v>12.65</v>
+        <v>12.91</v>
       </c>
       <c r="G80" t="n">
-        <v>88</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>82</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I80" t="n">
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>173.8</v>
+        <v>138.93</v>
       </c>
       <c r="K80" t="n">
-        <v>-76.04000000000001</v>
+        <v>-38.56</v>
       </c>
       <c r="L80" t="n">
-        <v>189.71</v>
+        <v>144.18</v>
       </c>
     </row>
     <row r="81">
@@ -3439,28 +3439,28 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>5.09</v>
+        <v>4.92</v>
       </c>
       <c r="F81" t="n">
-        <v>12.91</v>
+        <v>14.6</v>
       </c>
       <c r="G81" t="n">
-        <v>97.5</v>
+        <v>77.2</v>
       </c>
       <c r="H81" t="n">
-        <v>80.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-112.69</v>
+        <v>11.22</v>
       </c>
       <c r="K81" t="n">
-        <v>-18.23</v>
+        <v>-155.85</v>
       </c>
       <c r="L81" t="n">
-        <v>114.16</v>
+        <v>156.25</v>
       </c>
     </row>
     <row r="82">
@@ -3481,28 +3481,28 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>6.3</v>
+        <v>4.86</v>
       </c>
       <c r="F82" t="n">
-        <v>12.62</v>
+        <v>14.6</v>
       </c>
       <c r="G82" t="n">
-        <v>103.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>78.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="I82" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-136.66</v>
+        <v>152.14</v>
       </c>
       <c r="K82" t="n">
-        <v>-56.16</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>147.75</v>
+        <v>175.53</v>
       </c>
     </row>
     <row r="83">
@@ -3523,28 +3523,28 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>6.1</v>
+        <v>5.39</v>
       </c>
       <c r="F83" t="n">
-        <v>12.96</v>
+        <v>14.34</v>
       </c>
       <c r="G83" t="n">
-        <v>92.7</v>
+        <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>85.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-197.34</v>
+        <v>154.19</v>
       </c>
       <c r="K83" t="n">
-        <v>-170.92</v>
+        <v>-137.33</v>
       </c>
       <c r="L83" t="n">
-        <v>261.07</v>
+        <v>206.47</v>
       </c>
     </row>
     <row r="84">
@@ -3565,28 +3565,28 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.67</v>
+        <v>5.18</v>
       </c>
       <c r="F84" t="n">
-        <v>12.81</v>
+        <v>14.6</v>
       </c>
       <c r="G84" t="n">
-        <v>81.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>80.8</v>
+        <v>84</v>
       </c>
       <c r="I84" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>-45.66</v>
+        <v>154.57</v>
       </c>
       <c r="K84" t="n">
-        <v>-123.48</v>
+        <v>124.83</v>
       </c>
       <c r="L84" t="n">
-        <v>131.65</v>
+        <v>198.68</v>
       </c>
     </row>
     <row r="85">
@@ -3607,28 +3607,28 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.31</v>
+        <v>6.09</v>
       </c>
       <c r="F85" t="n">
-        <v>12.87</v>
+        <v>14.6</v>
       </c>
       <c r="G85" t="n">
-        <v>87.5</v>
+        <v>81.7</v>
       </c>
       <c r="H85" t="n">
-        <v>84.3</v>
+        <v>80.5</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>132.95</v>
+        <v>-49.92</v>
       </c>
       <c r="K85" t="n">
-        <v>-97.09999999999999</v>
+        <v>-208.72</v>
       </c>
       <c r="L85" t="n">
-        <v>164.63</v>
+        <v>214.61</v>
       </c>
     </row>
     <row r="86">
@@ -3649,28 +3649,28 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5.51</v>
+        <v>5.5</v>
       </c>
       <c r="F86" t="n">
-        <v>12.95</v>
+        <v>14.6</v>
       </c>
       <c r="G86" t="n">
-        <v>81.7</v>
+        <v>78.8</v>
       </c>
       <c r="H86" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-216.98</v>
+        <v>375.44</v>
       </c>
       <c r="K86" t="n">
-        <v>210.72</v>
+        <v>180.51</v>
       </c>
       <c r="L86" t="n">
-        <v>302.46</v>
+        <v>416.59</v>
       </c>
     </row>
     <row r="87">
@@ -3691,28 +3691,28 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.16</v>
+        <v>5.56</v>
       </c>
       <c r="F87" t="n">
-        <v>12.7</v>
+        <v>14.6</v>
       </c>
       <c r="G87" t="n">
-        <v>78.8</v>
+        <v>85.7</v>
       </c>
       <c r="H87" t="n">
-        <v>80.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>197.09</v>
+        <v>34.15</v>
       </c>
       <c r="K87" t="n">
-        <v>204.73</v>
+        <v>-364.48</v>
       </c>
       <c r="L87" t="n">
-        <v>284.18</v>
+        <v>366.08</v>
       </c>
     </row>
     <row r="88">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.12</v>
+        <v>5.26</v>
       </c>
       <c r="F88" t="n">
-        <v>12.72</v>
+        <v>14.37</v>
       </c>
       <c r="G88" t="n">
-        <v>79.2</v>
+        <v>81.7</v>
       </c>
       <c r="H88" t="n">
-        <v>75.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="I88" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-19.65</v>
+        <v>370.15</v>
       </c>
       <c r="K88" t="n">
-        <v>-286.46</v>
+        <v>-104.33</v>
       </c>
       <c r="L88" t="n">
-        <v>287.14</v>
+        <v>384.57</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-29.xlsx
+++ b/output/2025-09-29.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-76</v>
+        <v>-72.45</v>
       </c>
       <c r="K14" t="n">
-        <v>53.93</v>
+        <v>51.4</v>
       </c>
       <c r="L14" t="n">
-        <v>93.19</v>
+        <v>88.83</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-52.78</v>
+        <v>-56.18</v>
       </c>
       <c r="K15" t="n">
-        <v>31.49</v>
+        <v>33.52</v>
       </c>
       <c r="L15" t="n">
-        <v>61.46</v>
+        <v>65.42</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>87.37</v>
+        <v>85.02</v>
       </c>
       <c r="K16" t="n">
-        <v>-30.15</v>
+        <v>-29.34</v>
       </c>
       <c r="L16" t="n">
-        <v>92.43000000000001</v>
+        <v>89.94</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-29.81</v>
+        <v>-30.22</v>
       </c>
       <c r="K17" t="n">
-        <v>-101.28</v>
+        <v>-102.66</v>
       </c>
       <c r="L17" t="n">
-        <v>105.58</v>
+        <v>107.02</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-91.63</v>
+        <v>-92.84</v>
       </c>
       <c r="K18" t="n">
-        <v>-44</v>
+        <v>-44.58</v>
       </c>
       <c r="L18" t="n">
-        <v>101.65</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>126.23</v>
+        <v>123.13</v>
       </c>
       <c r="K19" t="n">
-        <v>43.27</v>
+        <v>42.21</v>
       </c>
       <c r="L19" t="n">
-        <v>133.44</v>
+        <v>130.16</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>58.66</v>
+        <v>62.9</v>
       </c>
       <c r="K20" t="n">
-        <v>-123.96</v>
+        <v>-132.9</v>
       </c>
       <c r="L20" t="n">
-        <v>137.14</v>
+        <v>147.03</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>121.83</v>
+        <v>130.58</v>
       </c>
       <c r="K21" t="n">
-        <v>115.37</v>
+        <v>123.66</v>
       </c>
       <c r="L21" t="n">
-        <v>167.79</v>
+        <v>179.84</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-59.81</v>
+        <v>-59.61</v>
       </c>
       <c r="K22" t="n">
-        <v>-103.95</v>
+        <v>-103.6</v>
       </c>
       <c r="L22" t="n">
-        <v>119.92</v>
+        <v>119.53</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>41.93</v>
+        <v>41.97</v>
       </c>
       <c r="K23" t="n">
-        <v>203.16</v>
+        <v>203.37</v>
       </c>
       <c r="L23" t="n">
-        <v>207.44</v>
+        <v>207.66</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>170.61</v>
+        <v>170.79</v>
       </c>
       <c r="K24" t="n">
-        <v>-30.87</v>
+        <v>-30.91</v>
       </c>
       <c r="L24" t="n">
-        <v>173.38</v>
+        <v>173.56</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>153.01</v>
+        <v>163.24</v>
       </c>
       <c r="K25" t="n">
-        <v>173.76</v>
+        <v>185.37</v>
       </c>
       <c r="L25" t="n">
-        <v>231.53</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>46.85</v>
+        <v>47.04</v>
       </c>
       <c r="K26" t="n">
-        <v>186.74</v>
+        <v>187.5</v>
       </c>
       <c r="L26" t="n">
-        <v>192.52</v>
+        <v>193.31</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-219.93</v>
+        <v>-218.26</v>
       </c>
       <c r="K27" t="n">
-        <v>169.53</v>
+        <v>168.25</v>
       </c>
       <c r="L27" t="n">
-        <v>277.69</v>
+        <v>275.58</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>260.35</v>
+        <v>283.49</v>
       </c>
       <c r="K28" t="n">
-        <v>-190.09</v>
+        <v>-206.99</v>
       </c>
       <c r="L28" t="n">
-        <v>322.36</v>
+        <v>351.02</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>44.79</v>
+        <v>46.99</v>
       </c>
       <c r="K29" t="n">
-        <v>40.94</v>
+        <v>42.95</v>
       </c>
       <c r="L29" t="n">
-        <v>60.68</v>
+        <v>63.66</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>57.46</v>
+        <v>55.84</v>
       </c>
       <c r="K30" t="n">
-        <v>-53.45</v>
+        <v>-51.94</v>
       </c>
       <c r="L30" t="n">
-        <v>78.48</v>
+        <v>76.26000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>30.58</v>
+        <v>29.07</v>
       </c>
       <c r="K31" t="n">
-        <v>-44.23</v>
+        <v>-42.04</v>
       </c>
       <c r="L31" t="n">
-        <v>53.77</v>
+        <v>51.11</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-22.17</v>
+        <v>-22.04</v>
       </c>
       <c r="K32" t="n">
-        <v>86.67</v>
+        <v>86.19</v>
       </c>
       <c r="L32" t="n">
-        <v>89.45999999999999</v>
+        <v>88.95999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-69.68000000000001</v>
+        <v>-70.47</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.74</v>
+        <v>-0.75</v>
       </c>
       <c r="L33" t="n">
-        <v>69.68000000000001</v>
+        <v>70.48</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>29.79</v>
+        <v>31.72</v>
       </c>
       <c r="K34" t="n">
-        <v>84.11</v>
+        <v>89.55</v>
       </c>
       <c r="L34" t="n">
-        <v>89.23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-85.98</v>
+        <v>-87.5</v>
       </c>
       <c r="K35" t="n">
-        <v>-76.25</v>
+        <v>-77.61</v>
       </c>
       <c r="L35" t="n">
-        <v>114.92</v>
+        <v>116.96</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>22.14</v>
+        <v>22.54</v>
       </c>
       <c r="K36" t="n">
-        <v>-135.13</v>
+        <v>-137.55</v>
       </c>
       <c r="L36" t="n">
-        <v>136.93</v>
+        <v>139.38</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-127.79</v>
+        <v>-124.9</v>
       </c>
       <c r="K37" t="n">
-        <v>69.19</v>
+        <v>67.63</v>
       </c>
       <c r="L37" t="n">
-        <v>145.32</v>
+        <v>142.03</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>212.8</v>
+        <v>222.95</v>
       </c>
       <c r="K38" t="n">
-        <v>-35.73</v>
+        <v>-37.44</v>
       </c>
       <c r="L38" t="n">
-        <v>215.78</v>
+        <v>226.08</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>60.32</v>
+        <v>64.88</v>
       </c>
       <c r="K39" t="n">
-        <v>196.7</v>
+        <v>211.56</v>
       </c>
       <c r="L39" t="n">
-        <v>205.74</v>
+        <v>221.29</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>80.83</v>
+        <v>86.22</v>
       </c>
       <c r="K40" t="n">
-        <v>219.82</v>
+        <v>234.48</v>
       </c>
       <c r="L40" t="n">
-        <v>234.21</v>
+        <v>249.83</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>9.699999999999999</v>
+        <v>10.44</v>
       </c>
       <c r="K41" t="n">
-        <v>-17.57</v>
+        <v>-18.91</v>
       </c>
       <c r="L41" t="n">
-        <v>20.07</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>324.06</v>
+        <v>343.49</v>
       </c>
       <c r="K42" t="n">
-        <v>-97.47</v>
+        <v>-103.31</v>
       </c>
       <c r="L42" t="n">
-        <v>338.4</v>
+        <v>358.69</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>157.38</v>
+        <v>153.11</v>
       </c>
       <c r="K43" t="n">
-        <v>177.35</v>
+        <v>172.54</v>
       </c>
       <c r="L43" t="n">
-        <v>237.11</v>
+        <v>230.68</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-64.56999999999999</v>
+        <v>-68.94</v>
       </c>
       <c r="K44" t="n">
-        <v>68.77</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>94.33</v>
+        <v>100.72</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>77.66</v>
+        <v>80.09</v>
       </c>
       <c r="K45" t="n">
-        <v>-37.84</v>
+        <v>-39.02</v>
       </c>
       <c r="L45" t="n">
-        <v>86.39</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-67.8</v>
+        <v>-72.38</v>
       </c>
       <c r="K46" t="n">
-        <v>32.88</v>
+        <v>35.1</v>
       </c>
       <c r="L46" t="n">
-        <v>75.34999999999999</v>
+        <v>80.45</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-39</v>
+        <v>-40.22</v>
       </c>
       <c r="K47" t="n">
-        <v>-39.97</v>
+        <v>-41.23</v>
       </c>
       <c r="L47" t="n">
-        <v>55.84</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-60.07</v>
+        <v>-58.34</v>
       </c>
       <c r="K48" t="n">
-        <v>-49.44</v>
+        <v>-48.01</v>
       </c>
       <c r="L48" t="n">
-        <v>77.8</v>
+        <v>75.55</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-14.6</v>
+        <v>-15.09</v>
       </c>
       <c r="K49" t="n">
-        <v>-83.56</v>
+        <v>-86.37</v>
       </c>
       <c r="L49" t="n">
-        <v>84.83</v>
+        <v>87.68000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>29.86</v>
+        <v>31.49</v>
       </c>
       <c r="K50" t="n">
-        <v>132.38</v>
+        <v>139.59</v>
       </c>
       <c r="L50" t="n">
-        <v>135.7</v>
+        <v>143.09</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-98.97</v>
+        <v>-106.07</v>
       </c>
       <c r="K51" t="n">
-        <v>-126.6</v>
+        <v>-135.67</v>
       </c>
       <c r="L51" t="n">
-        <v>160.7</v>
+        <v>172.21</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>95.69</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>148.37</v>
+        <v>153.58</v>
       </c>
       <c r="L52" t="n">
-        <v>176.55</v>
+        <v>182.74</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>-5.35</v>
+        <v>-5.8</v>
       </c>
       <c r="K53" t="n">
-        <v>219.45</v>
+        <v>238.14</v>
       </c>
       <c r="L53" t="n">
-        <v>219.51</v>
+        <v>238.21</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>103.36</v>
+        <v>102.22</v>
       </c>
       <c r="K54" t="n">
-        <v>-181</v>
+        <v>-179</v>
       </c>
       <c r="L54" t="n">
-        <v>208.43</v>
+        <v>206.13</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>174.31</v>
+        <v>175.79</v>
       </c>
       <c r="K55" t="n">
-        <v>119.68</v>
+        <v>120.7</v>
       </c>
       <c r="L55" t="n">
-        <v>211.44</v>
+        <v>213.24</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>237.33</v>
+        <v>229.78</v>
       </c>
       <c r="K56" t="n">
-        <v>-59.05</v>
+        <v>-57.17</v>
       </c>
       <c r="L56" t="n">
-        <v>244.57</v>
+        <v>236.78</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>51.17</v>
+        <v>56.15</v>
       </c>
       <c r="K57" t="n">
-        <v>402.1</v>
+        <v>441.25</v>
       </c>
       <c r="L57" t="n">
-        <v>405.34</v>
+        <v>444.81</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>52.7</v>
+        <v>52.36</v>
       </c>
       <c r="K58" t="n">
-        <v>35.33</v>
+        <v>35.1</v>
       </c>
       <c r="L58" t="n">
-        <v>63.45</v>
+        <v>63.04</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>9.6</v>
+        <v>9.52</v>
       </c>
       <c r="K59" t="n">
-        <v>-79.28</v>
+        <v>-78.64</v>
       </c>
       <c r="L59" t="n">
-        <v>79.86</v>
+        <v>79.20999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.69</v>
+        <v>-4.83</v>
       </c>
       <c r="K60" t="n">
-        <v>63.88</v>
+        <v>65.81</v>
       </c>
       <c r="L60" t="n">
-        <v>64.05</v>
+        <v>65.98</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-63.43</v>
+        <v>-67.47</v>
       </c>
       <c r="K61" t="n">
-        <v>-29.98</v>
+        <v>-31.89</v>
       </c>
       <c r="L61" t="n">
-        <v>70.16</v>
+        <v>74.62</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>105.67</v>
+        <v>102.64</v>
       </c>
       <c r="K62" t="n">
-        <v>-9.59</v>
+        <v>-9.32</v>
       </c>
       <c r="L62" t="n">
-        <v>106.11</v>
+        <v>103.07</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-31.02</v>
+        <v>-33.08</v>
       </c>
       <c r="K63" t="n">
-        <v>-99.81999999999999</v>
+        <v>-106.45</v>
       </c>
       <c r="L63" t="n">
-        <v>104.53</v>
+        <v>111.47</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>49.24</v>
+        <v>51.77</v>
       </c>
       <c r="K64" t="n">
-        <v>118.32</v>
+        <v>124.4</v>
       </c>
       <c r="L64" t="n">
-        <v>128.15</v>
+        <v>134.74</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-135.83</v>
+        <v>-142.94</v>
       </c>
       <c r="K65" t="n">
-        <v>-96.13</v>
+        <v>-101.16</v>
       </c>
       <c r="L65" t="n">
-        <v>166.4</v>
+        <v>175.11</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-54.07</v>
+        <v>-53.86</v>
       </c>
       <c r="K66" t="n">
-        <v>151.42</v>
+        <v>150.84</v>
       </c>
       <c r="L66" t="n">
-        <v>160.79</v>
+        <v>160.17</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="K67" t="n">
-        <v>196.17</v>
+        <v>199.17</v>
       </c>
       <c r="L67" t="n">
-        <v>196.19</v>
+        <v>199.18</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-83.38</v>
+        <v>-80.61</v>
       </c>
       <c r="K68" t="n">
-        <v>-137</v>
+        <v>-132.44</v>
       </c>
       <c r="L68" t="n">
-        <v>160.38</v>
+        <v>155.04</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>22.8</v>
+        <v>24.52</v>
       </c>
       <c r="K69" t="n">
-        <v>178.18</v>
+        <v>191.6</v>
       </c>
       <c r="L69" t="n">
-        <v>179.63</v>
+        <v>193.16</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>37.81</v>
+        <v>38.25</v>
       </c>
       <c r="K70" t="n">
-        <v>262.85</v>
+        <v>265.95</v>
       </c>
       <c r="L70" t="n">
-        <v>265.55</v>
+        <v>268.69</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-292.54</v>
+        <v>-298.52</v>
       </c>
       <c r="K71" t="n">
-        <v>-212.85</v>
+        <v>-217.2</v>
       </c>
       <c r="L71" t="n">
-        <v>361.77</v>
+        <v>369.18</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>240.39</v>
+        <v>245.21</v>
       </c>
       <c r="K72" t="n">
-        <v>192.16</v>
+        <v>196.01</v>
       </c>
       <c r="L72" t="n">
-        <v>307.75</v>
+        <v>313.93</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>285.19</v>
+        <v>307.16</v>
       </c>
       <c r="K73" t="n">
-        <v>143.82</v>
+        <v>154.9</v>
       </c>
       <c r="L73" t="n">
-        <v>319.4</v>
+        <v>344</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-70.90000000000001</v>
+        <v>-73.03</v>
       </c>
       <c r="K74" t="n">
-        <v>11.42</v>
+        <v>11.76</v>
       </c>
       <c r="L74" t="n">
-        <v>71.81</v>
+        <v>73.97</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-64.06</v>
+        <v>-67.2</v>
       </c>
       <c r="K75" t="n">
-        <v>42.18</v>
+        <v>44.24</v>
       </c>
       <c r="L75" t="n">
-        <v>76.7</v>
+        <v>80.45</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-96.20999999999999</v>
+        <v>-100.65</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.38</v>
+        <v>-4.58</v>
       </c>
       <c r="L76" t="n">
-        <v>96.31</v>
+        <v>100.76</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>80.73999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-30.63</v>
+        <v>-32.59</v>
       </c>
       <c r="L77" t="n">
-        <v>86.34999999999999</v>
+        <v>91.88</v>
       </c>
     </row>
     <row r="78">
@@ -3331,10 +3331,10 @@
         <v>0.11</v>
       </c>
       <c r="K78" t="n">
-        <v>96.15000000000001</v>
+        <v>97.09</v>
       </c>
       <c r="L78" t="n">
-        <v>96.15000000000001</v>
+        <v>97.09</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-53.59</v>
+        <v>-52.07</v>
       </c>
       <c r="K79" t="n">
-        <v>100.05</v>
+        <v>97.2</v>
       </c>
       <c r="L79" t="n">
-        <v>113.5</v>
+        <v>110.27</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>138.93</v>
+        <v>146.3</v>
       </c>
       <c r="K80" t="n">
-        <v>-38.56</v>
+        <v>-40.6</v>
       </c>
       <c r="L80" t="n">
-        <v>144.18</v>
+        <v>151.83</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>11.22</v>
+        <v>10.96</v>
       </c>
       <c r="K81" t="n">
-        <v>-155.85</v>
+        <v>-152.16</v>
       </c>
       <c r="L81" t="n">
-        <v>156.25</v>
+        <v>152.56</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>152.14</v>
+        <v>163.01</v>
       </c>
       <c r="K82" t="n">
-        <v>87.54000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="L82" t="n">
-        <v>175.53</v>
+        <v>188.07</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>154.19</v>
+        <v>152.57</v>
       </c>
       <c r="K83" t="n">
-        <v>-137.33</v>
+        <v>-135.88</v>
       </c>
       <c r="L83" t="n">
-        <v>206.47</v>
+        <v>204.31</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>154.57</v>
+        <v>156.05</v>
       </c>
       <c r="K84" t="n">
-        <v>124.83</v>
+        <v>126.02</v>
       </c>
       <c r="L84" t="n">
-        <v>198.68</v>
+        <v>200.58</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-49.92</v>
+        <v>-48.39</v>
       </c>
       <c r="K85" t="n">
-        <v>-208.72</v>
+        <v>-202.35</v>
       </c>
       <c r="L85" t="n">
-        <v>214.61</v>
+        <v>208.05</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>375.44</v>
+        <v>405.02</v>
       </c>
       <c r="K86" t="n">
-        <v>180.51</v>
+        <v>194.73</v>
       </c>
       <c r="L86" t="n">
-        <v>416.59</v>
+        <v>449.4</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>34.15</v>
+        <v>35.56</v>
       </c>
       <c r="K87" t="n">
-        <v>-364.48</v>
+        <v>-379.53</v>
       </c>
       <c r="L87" t="n">
-        <v>366.08</v>
+        <v>381.19</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>370.15</v>
+        <v>361.76</v>
       </c>
       <c r="K88" t="n">
-        <v>-104.33</v>
+        <v>-101.97</v>
       </c>
       <c r="L88" t="n">
-        <v>384.57</v>
+        <v>375.85</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-29.xlsx
+++ b/output/2025-09-29.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.38</v>
+        <v>4.74</v>
       </c>
       <c r="F14" t="n">
-        <v>10.63</v>
+        <v>13.59</v>
       </c>
       <c r="G14" t="n">
-        <v>82.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>79.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-72.45</v>
+        <v>119.13</v>
       </c>
       <c r="K14" t="n">
-        <v>51.4</v>
+        <v>-40.65</v>
       </c>
       <c r="L14" t="n">
-        <v>88.83</v>
+        <v>125.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:15:20</t>
+          <t>07:16:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>5.19</v>
+        <v>4.41</v>
       </c>
       <c r="F15" t="n">
-        <v>11.67</v>
+        <v>10.25</v>
       </c>
       <c r="G15" t="n">
-        <v>81.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>83.59999999999999</v>
+        <v>33.9</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-56.18</v>
+        <v>114.34</v>
       </c>
       <c r="K15" t="n">
-        <v>33.52</v>
+        <v>64.09</v>
       </c>
       <c r="L15" t="n">
-        <v>65.42</v>
+        <v>131.08</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:16:40</t>
+          <t>07:17:01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>12.44</v>
+        <v>7.88</v>
       </c>
       <c r="G16" t="n">
-        <v>92.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>81.2</v>
+        <v>73</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>85.02</v>
+        <v>-18.7</v>
       </c>
       <c r="K16" t="n">
-        <v>-29.34</v>
+        <v>47.4</v>
       </c>
       <c r="L16" t="n">
-        <v>89.94</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:22:06</t>
+          <t>07:21:48</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.5</v>
+        <v>3.53</v>
       </c>
       <c r="F17" t="n">
-        <v>13.01</v>
+        <v>7.65</v>
       </c>
       <c r="G17" t="n">
-        <v>85.8</v>
+        <v>88.8</v>
       </c>
       <c r="H17" t="n">
-        <v>83.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-30.22</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-102.66</v>
+        <v>-26.62</v>
       </c>
       <c r="L17" t="n">
-        <v>107.02</v>
+        <v>78.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:24:04</t>
+          <t>07:22:58</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.61</v>
+        <v>3.65</v>
       </c>
       <c r="F18" t="n">
-        <v>12.69</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>77.8</v>
+        <v>94.3</v>
       </c>
       <c r="H18" t="n">
-        <v>81.3</v>
+        <v>32.4</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-92.84</v>
+        <v>44.14</v>
       </c>
       <c r="K18" t="n">
-        <v>-44.58</v>
+        <v>-50.56</v>
       </c>
       <c r="L18" t="n">
-        <v>102.99</v>
+        <v>67.12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:25:12</t>
+          <t>07:24:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.13</v>
+        <v>3.86</v>
       </c>
       <c r="F19" t="n">
-        <v>9.460000000000001</v>
+        <v>7.62</v>
       </c>
       <c r="G19" t="n">
-        <v>118.1</v>
+        <v>95.7</v>
       </c>
       <c r="H19" t="n">
-        <v>77</v>
+        <v>35.2</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>123.13</v>
+        <v>-23.19</v>
       </c>
       <c r="K19" t="n">
-        <v>42.21</v>
+        <v>-86.29000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>130.16</v>
+        <v>89.34999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:30:39</t>
+          <t>07:30:31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.35</v>
+        <v>5.17</v>
       </c>
       <c r="F20" t="n">
-        <v>10.44</v>
+        <v>11.74</v>
       </c>
       <c r="G20" t="n">
-        <v>79.5</v>
+        <v>85</v>
       </c>
       <c r="H20" t="n">
-        <v>83.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>62.9</v>
+        <v>115.67</v>
       </c>
       <c r="K20" t="n">
-        <v>-132.9</v>
+        <v>186.58</v>
       </c>
       <c r="L20" t="n">
-        <v>147.03</v>
+        <v>219.53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:31:25</t>
+          <t>07:31:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.57</v>
+        <v>4.24</v>
       </c>
       <c r="F21" t="n">
-        <v>10.47</v>
+        <v>10.37</v>
       </c>
       <c r="G21" t="n">
-        <v>94.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="H21" t="n">
-        <v>84.5</v>
+        <v>39.3</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>130.58</v>
+        <v>-67</v>
       </c>
       <c r="K21" t="n">
-        <v>123.66</v>
+        <v>-149.04</v>
       </c>
       <c r="L21" t="n">
-        <v>179.84</v>
+        <v>163.41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:33:33</t>
+          <t>07:33:13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.94</v>
+        <v>3.93</v>
       </c>
       <c r="F22" t="n">
-        <v>11.14</v>
+        <v>11.84</v>
       </c>
       <c r="G22" t="n">
-        <v>83.90000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="H22" t="n">
-        <v>86.09999999999999</v>
+        <v>39</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-59.61</v>
+        <v>34.54</v>
       </c>
       <c r="K22" t="n">
-        <v>-103.6</v>
+        <v>154.73</v>
       </c>
       <c r="L22" t="n">
-        <v>119.53</v>
+        <v>158.54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:37:39</t>
+          <t>07:37:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.15</v>
+        <v>3.68</v>
       </c>
       <c r="F23" t="n">
-        <v>9.67</v>
+        <v>10.86</v>
       </c>
       <c r="G23" t="n">
-        <v>76.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="H23" t="n">
-        <v>84.8</v>
+        <v>29.4</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>41.97</v>
+        <v>94.16</v>
       </c>
       <c r="K23" t="n">
-        <v>203.37</v>
+        <v>-48.67</v>
       </c>
       <c r="L23" t="n">
-        <v>207.66</v>
+        <v>105.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:39:43</t>
+          <t>07:39:37</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.17</v>
+        <v>4.23</v>
       </c>
       <c r="F24" t="n">
-        <v>8.58</v>
+        <v>9.99</v>
       </c>
       <c r="G24" t="n">
-        <v>80.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="H24" t="n">
-        <v>79.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>170.79</v>
+        <v>211.96</v>
       </c>
       <c r="K24" t="n">
-        <v>-30.91</v>
+        <v>54.56</v>
       </c>
       <c r="L24" t="n">
-        <v>173.56</v>
+        <v>218.87</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:42:03</t>
+          <t>07:41:37</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5.22</v>
+        <v>5.34</v>
       </c>
       <c r="F25" t="n">
-        <v>12.74</v>
+        <v>9.6</v>
       </c>
       <c r="G25" t="n">
-        <v>84.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>86.59999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>163.24</v>
+        <v>-104.43</v>
       </c>
       <c r="K25" t="n">
-        <v>185.37</v>
+        <v>369.7</v>
       </c>
       <c r="L25" t="n">
-        <v>247</v>
+        <v>384.17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:45:35</t>
+          <t>07:45:50</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.75</v>
+        <v>4.63</v>
       </c>
       <c r="F26" t="n">
-        <v>6.98</v>
+        <v>12.44</v>
       </c>
       <c r="G26" t="n">
-        <v>73.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>80.8</v>
+        <v>55.8</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>47.04</v>
+        <v>175.42</v>
       </c>
       <c r="K26" t="n">
-        <v>187.5</v>
+        <v>-145.55</v>
       </c>
       <c r="L26" t="n">
-        <v>193.31</v>
+        <v>227.94</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:46:21</t>
+          <t>07:47:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.29</v>
+        <v>4.21</v>
       </c>
       <c r="F27" t="n">
-        <v>7.9</v>
+        <v>8.77</v>
       </c>
       <c r="G27" t="n">
-        <v>90.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>84.5</v>
+        <v>52.8</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-218.26</v>
+        <v>167.88</v>
       </c>
       <c r="K27" t="n">
-        <v>168.25</v>
+        <v>331.42</v>
       </c>
       <c r="L27" t="n">
-        <v>275.58</v>
+        <v>371.51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:48:58</t>
+          <t>07:49:14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.35</v>
+        <v>4.83</v>
       </c>
       <c r="F28" t="n">
-        <v>14.6</v>
+        <v>13.45</v>
       </c>
       <c r="G28" t="n">
-        <v>81.2</v>
+        <v>73</v>
       </c>
       <c r="H28" t="n">
-        <v>82.90000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>283.49</v>
+        <v>300.43</v>
       </c>
       <c r="K28" t="n">
-        <v>-206.99</v>
+        <v>225.66</v>
       </c>
       <c r="L28" t="n">
-        <v>351.02</v>
+        <v>375.74</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:02:13</t>
+          <t>07:57:45</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.79</v>
+        <v>4.1</v>
       </c>
       <c r="F29" t="n">
-        <v>12.37</v>
+        <v>12.73</v>
       </c>
       <c r="G29" t="n">
-        <v>79.90000000000001</v>
+        <v>101.4</v>
       </c>
       <c r="H29" t="n">
-        <v>82.2</v>
+        <v>67.5</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>46.99</v>
+        <v>57.5</v>
       </c>
       <c r="K29" t="n">
-        <v>42.95</v>
+        <v>35.11</v>
       </c>
       <c r="L29" t="n">
-        <v>63.66</v>
+        <v>67.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:04:41</t>
+          <t>07:59:20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>4.57</v>
       </c>
       <c r="F30" t="n">
-        <v>14.6</v>
+        <v>12.11</v>
       </c>
       <c r="G30" t="n">
         <v>88.2</v>
       </c>
       <c r="H30" t="n">
-        <v>80.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>55.84</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>-51.94</v>
+        <v>-82.86</v>
       </c>
       <c r="L30" t="n">
-        <v>76.26000000000001</v>
+        <v>124.86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:05:59</t>
+          <t>08:00:21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.98</v>
+        <v>4.4</v>
       </c>
       <c r="F31" t="n">
-        <v>14.28</v>
+        <v>12.78</v>
       </c>
       <c r="G31" t="n">
-        <v>74.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>76.3</v>
+        <v>26.2</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>29.07</v>
+        <v>3.06</v>
       </c>
       <c r="K31" t="n">
-        <v>-42.04</v>
+        <v>59.2</v>
       </c>
       <c r="L31" t="n">
-        <v>51.11</v>
+        <v>59.28</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:10:51</t>
+          <t>08:03:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.44</v>
+        <v>5.06</v>
       </c>
       <c r="F32" t="n">
-        <v>12.21</v>
+        <v>14.01</v>
       </c>
       <c r="G32" t="n">
-        <v>88.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>78.59999999999999</v>
+        <v>53.1</v>
       </c>
       <c r="I32" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>-22.04</v>
+        <v>192.96</v>
       </c>
       <c r="K32" t="n">
-        <v>86.19</v>
+        <v>-17.44</v>
       </c>
       <c r="L32" t="n">
-        <v>88.95999999999999</v>
+        <v>193.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:11:56</t>
+          <t>08:04:50</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>5.03</v>
+        <v>4.56</v>
       </c>
       <c r="F33" t="n">
-        <v>11.85</v>
+        <v>12.18</v>
       </c>
       <c r="G33" t="n">
-        <v>97</v>
+        <v>90.7</v>
       </c>
       <c r="H33" t="n">
-        <v>76.8</v>
+        <v>61.2</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-70.47</v>
+        <v>342.54</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.75</v>
+        <v>156.68</v>
       </c>
       <c r="L33" t="n">
-        <v>70.48</v>
+        <v>376.67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:13:38</t>
+          <t>08:07:11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5.21</v>
+        <v>4.68</v>
       </c>
       <c r="F34" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="G34" t="n">
-        <v>82.8</v>
+        <v>79</v>
       </c>
       <c r="H34" t="n">
-        <v>87.3</v>
+        <v>38.9</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>31.72</v>
+        <v>28.12</v>
       </c>
       <c r="K34" t="n">
-        <v>89.55</v>
+        <v>-120.94</v>
       </c>
       <c r="L34" t="n">
-        <v>95</v>
+        <v>124.17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:18:34</t>
+          <t>08:11:35</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.38</v>
+        <v>5.2</v>
       </c>
       <c r="F35" t="n">
-        <v>11.44</v>
+        <v>12.95</v>
       </c>
       <c r="G35" t="n">
-        <v>79.5</v>
+        <v>94.2</v>
       </c>
       <c r="H35" t="n">
-        <v>93.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-87.5</v>
+        <v>64.89</v>
       </c>
       <c r="K35" t="n">
-        <v>-77.61</v>
+        <v>236.56</v>
       </c>
       <c r="L35" t="n">
-        <v>116.96</v>
+        <v>245.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:20:57</t>
+          <t>08:13:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.26</v>
+        <v>5.72</v>
       </c>
       <c r="F36" t="n">
-        <v>13.2</v>
+        <v>13.49</v>
       </c>
       <c r="G36" t="n">
-        <v>86.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="H36" t="n">
-        <v>83.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>22.54</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-137.55</v>
+        <v>-243.69</v>
       </c>
       <c r="L36" t="n">
-        <v>139.38</v>
+        <v>260.91</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:21:32</t>
+          <t>08:14:56</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.69</v>
+        <v>4.99</v>
       </c>
       <c r="F37" t="n">
-        <v>11.58</v>
+        <v>13.3</v>
       </c>
       <c r="G37" t="n">
-        <v>91.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="H37" t="n">
-        <v>80.5</v>
+        <v>88.2</v>
       </c>
       <c r="I37" t="n">
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-124.9</v>
+        <v>137.2</v>
       </c>
       <c r="K37" t="n">
-        <v>67.63</v>
+        <v>165.99</v>
       </c>
       <c r="L37" t="n">
-        <v>142.03</v>
+        <v>215.35</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:25:01</t>
+          <t>08:19:04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.94</v>
+        <v>4.25</v>
       </c>
       <c r="F38" t="n">
-        <v>14.6</v>
+        <v>10.67</v>
       </c>
       <c r="G38" t="n">
-        <v>88.8</v>
+        <v>72.8</v>
       </c>
       <c r="H38" t="n">
-        <v>82.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>222.95</v>
+        <v>243.14</v>
       </c>
       <c r="K38" t="n">
-        <v>-37.44</v>
+        <v>-87.64</v>
       </c>
       <c r="L38" t="n">
-        <v>226.08</v>
+        <v>258.45</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:26:25</t>
+          <t>08:21:39</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.46</v>
+        <v>3.97</v>
       </c>
       <c r="F39" t="n">
-        <v>13.36</v>
+        <v>10.79</v>
       </c>
       <c r="G39" t="n">
-        <v>72.2</v>
+        <v>85.8</v>
       </c>
       <c r="H39" t="n">
-        <v>84.2</v>
+        <v>57.1</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>64.88</v>
+        <v>106.61</v>
       </c>
       <c r="K39" t="n">
-        <v>211.56</v>
+        <v>-310.14</v>
       </c>
       <c r="L39" t="n">
-        <v>221.29</v>
+        <v>327.95</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:27:45</t>
+          <t>08:24:06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.16</v>
+        <v>5.79</v>
       </c>
       <c r="F40" t="n">
-        <v>10.44</v>
+        <v>14.6</v>
       </c>
       <c r="G40" t="n">
-        <v>82.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>79.2</v>
+        <v>59.5</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>86.22</v>
+        <v>385.3</v>
       </c>
       <c r="K40" t="n">
-        <v>234.48</v>
+        <v>-174.74</v>
       </c>
       <c r="L40" t="n">
-        <v>249.83</v>
+        <v>423.07</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:32:31</t>
+          <t>08:28:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.08</v>
+        <v>4.56</v>
       </c>
       <c r="F41" t="n">
-        <v>12.27</v>
+        <v>14.55</v>
       </c>
       <c r="G41" t="n">
-        <v>91.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>82</v>
+        <v>51.9</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>10.44</v>
+        <v>-312.04</v>
       </c>
       <c r="K41" t="n">
-        <v>-18.91</v>
+        <v>196.45</v>
       </c>
       <c r="L41" t="n">
-        <v>21.6</v>
+        <v>368.73</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:33:17</t>
+          <t>08:30:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.44</v>
+        <v>5.19</v>
       </c>
       <c r="F42" t="n">
-        <v>14.6</v>
+        <v>10.99</v>
       </c>
       <c r="G42" t="n">
-        <v>83</v>
+        <v>99.2</v>
       </c>
       <c r="H42" t="n">
-        <v>84.59999999999999</v>
+        <v>36.1</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>343.49</v>
+        <v>204.51</v>
       </c>
       <c r="K42" t="n">
-        <v>-103.31</v>
+        <v>-234.93</v>
       </c>
       <c r="L42" t="n">
-        <v>358.69</v>
+        <v>311.48</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:35:25</t>
+          <t>08:32:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.52</v>
+        <v>5.86</v>
       </c>
       <c r="F43" t="n">
         <v>14.6</v>
       </c>
       <c r="G43" t="n">
-        <v>91.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>83.3</v>
+        <v>49.4</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>153.11</v>
+        <v>215.2</v>
       </c>
       <c r="K43" t="n">
-        <v>172.54</v>
+        <v>337.03</v>
       </c>
       <c r="L43" t="n">
-        <v>230.68</v>
+        <v>399.88</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:46:37</t>
+          <t>08:40:27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.49</v>
+        <v>5.17</v>
       </c>
       <c r="F44" t="n">
-        <v>10.98</v>
+        <v>14.6</v>
       </c>
       <c r="G44" t="n">
-        <v>80.8</v>
+        <v>96.3</v>
       </c>
       <c r="H44" t="n">
-        <v>89.40000000000001</v>
+        <v>29.8</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-68.94</v>
+        <v>101.01</v>
       </c>
       <c r="K44" t="n">
-        <v>73.43000000000001</v>
+        <v>-33.08</v>
       </c>
       <c r="L44" t="n">
-        <v>100.72</v>
+        <v>106.29</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:48:34</t>
+          <t>08:42:03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.72</v>
+        <v>5.22</v>
       </c>
       <c r="F45" t="n">
-        <v>12.57</v>
+        <v>14.6</v>
       </c>
       <c r="G45" t="n">
-        <v>84.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="H45" t="n">
-        <v>84.3</v>
+        <v>71.7</v>
       </c>
       <c r="I45" t="n">
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>80.09</v>
+        <v>70.34</v>
       </c>
       <c r="K45" t="n">
-        <v>-39.02</v>
+        <v>-58.75</v>
       </c>
       <c r="L45" t="n">
-        <v>89.09999999999999</v>
+        <v>91.65000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:51:08</t>
+          <t>08:43:46</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.51</v>
+        <v>5.27</v>
       </c>
       <c r="F46" t="n">
-        <v>14.59</v>
+        <v>13.79</v>
       </c>
       <c r="G46" t="n">
-        <v>73.2</v>
+        <v>95.2</v>
       </c>
       <c r="H46" t="n">
-        <v>82.3</v>
+        <v>27.1</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-72.38</v>
+        <v>-78.84</v>
       </c>
       <c r="K46" t="n">
-        <v>35.1</v>
+        <v>-91.59999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>80.45</v>
+        <v>120.86</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:54:30</t>
+          <t>08:47:56</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.72</v>
+        <v>5.38</v>
       </c>
       <c r="F47" t="n">
-        <v>12.71</v>
+        <v>14.6</v>
       </c>
       <c r="G47" t="n">
-        <v>69.7</v>
+        <v>101</v>
       </c>
       <c r="H47" t="n">
-        <v>77.5</v>
+        <v>60</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-40.22</v>
+        <v>-67.97</v>
       </c>
       <c r="K47" t="n">
-        <v>-41.23</v>
+        <v>-166.41</v>
       </c>
       <c r="L47" t="n">
-        <v>57.6</v>
+        <v>179.76</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:56:23</t>
+          <t>08:48:49</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.19</v>
+        <v>4.92</v>
       </c>
       <c r="F48" t="n">
-        <v>14.24</v>
+        <v>12.46</v>
       </c>
       <c r="G48" t="n">
-        <v>83.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="H48" t="n">
-        <v>85.2</v>
+        <v>41.5</v>
       </c>
       <c r="I48" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-58.34</v>
+        <v>110.83</v>
       </c>
       <c r="K48" t="n">
-        <v>-48.01</v>
+        <v>109.81</v>
       </c>
       <c r="L48" t="n">
-        <v>75.55</v>
+        <v>156.02</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:57:49</t>
+          <t>08:51:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.25</v>
+        <v>4.66</v>
       </c>
       <c r="F49" t="n">
-        <v>11.6</v>
+        <v>9.85</v>
       </c>
       <c r="G49" t="n">
-        <v>81.2</v>
+        <v>88</v>
       </c>
       <c r="H49" t="n">
-        <v>86.40000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-15.09</v>
+        <v>-118.88</v>
       </c>
       <c r="K49" t="n">
-        <v>-86.37</v>
+        <v>154.4</v>
       </c>
       <c r="L49" t="n">
-        <v>87.68000000000001</v>
+        <v>194.87</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:02:23</t>
+          <t>08:55:20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.54</v>
+        <v>4.65</v>
       </c>
       <c r="F50" t="n">
-        <v>10.7</v>
+        <v>12.46</v>
       </c>
       <c r="G50" t="n">
-        <v>82.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>83.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="I50" t="n">
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>31.49</v>
+        <v>190.03</v>
       </c>
       <c r="K50" t="n">
-        <v>139.59</v>
+        <v>-113.78</v>
       </c>
       <c r="L50" t="n">
-        <v>143.09</v>
+        <v>221.49</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:03:41</t>
+          <t>08:56:33</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.7</v>
+        <v>4.87</v>
       </c>
       <c r="F51" t="n">
-        <v>13.58</v>
+        <v>10.25</v>
       </c>
       <c r="G51" t="n">
-        <v>91.90000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="H51" t="n">
-        <v>84.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I51" t="n">
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-106.07</v>
+        <v>199.25</v>
       </c>
       <c r="K51" t="n">
-        <v>-135.67</v>
+        <v>28.81</v>
       </c>
       <c r="L51" t="n">
-        <v>172.21</v>
+        <v>201.32</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:05:58</t>
+          <t>08:58:31</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.91</v>
+        <v>5.22</v>
       </c>
       <c r="F52" t="n">
-        <v>13.5</v>
+        <v>14.6</v>
       </c>
       <c r="G52" t="n">
-        <v>86.90000000000001</v>
+        <v>100.7</v>
       </c>
       <c r="H52" t="n">
-        <v>81.09999999999999</v>
+        <v>56.9</v>
       </c>
       <c r="I52" t="n">
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>99.04000000000001</v>
+        <v>-3.93</v>
       </c>
       <c r="K52" t="n">
-        <v>153.58</v>
+        <v>-45.16</v>
       </c>
       <c r="L52" t="n">
-        <v>182.74</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:11:28</t>
+          <t>09:03:08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.49</v>
+        <v>5.94</v>
       </c>
       <c r="F53" t="n">
         <v>14.6</v>
       </c>
       <c r="G53" t="n">
-        <v>101.7</v>
+        <v>98.2</v>
       </c>
       <c r="H53" t="n">
-        <v>89.90000000000001</v>
+        <v>41.7</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-5.8</v>
+        <v>-87.81</v>
       </c>
       <c r="K53" t="n">
-        <v>238.14</v>
+        <v>306.97</v>
       </c>
       <c r="L53" t="n">
-        <v>238.21</v>
+        <v>319.29</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:13:47</t>
+          <t>09:05:38</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5.17</v>
+        <v>4.56</v>
       </c>
       <c r="F54" t="n">
-        <v>10.05</v>
+        <v>11.73</v>
       </c>
       <c r="G54" t="n">
-        <v>99.7</v>
+        <v>88.3</v>
       </c>
       <c r="H54" t="n">
-        <v>74.7</v>
+        <v>93</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>102.22</v>
+        <v>131.82</v>
       </c>
       <c r="K54" t="n">
-        <v>-179</v>
+        <v>293.19</v>
       </c>
       <c r="L54" t="n">
-        <v>206.13</v>
+        <v>321.47</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:15:25</t>
+          <t>09:06:53</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.81</v>
+        <v>5.39</v>
       </c>
       <c r="F55" t="n">
-        <v>11.06</v>
+        <v>14.6</v>
       </c>
       <c r="G55" t="n">
-        <v>90.09999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>84</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>175.79</v>
+        <v>352.78</v>
       </c>
       <c r="K55" t="n">
-        <v>120.7</v>
+        <v>133.45</v>
       </c>
       <c r="L55" t="n">
-        <v>213.24</v>
+        <v>377.18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:19:17</t>
+          <t>09:11:55</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.27</v>
+        <v>5.41</v>
       </c>
       <c r="F56" t="n">
-        <v>13.69</v>
+        <v>13.28</v>
       </c>
       <c r="G56" t="n">
-        <v>84.3</v>
+        <v>76.5</v>
       </c>
       <c r="H56" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>229.78</v>
+        <v>-54.31</v>
       </c>
       <c r="K56" t="n">
-        <v>-57.17</v>
+        <v>-330.99</v>
       </c>
       <c r="L56" t="n">
-        <v>236.78</v>
+        <v>335.42</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:20:41</t>
+          <t>09:13:51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.66</v>
+        <v>4.87</v>
       </c>
       <c r="F57" t="n">
-        <v>14.6</v>
+        <v>14.22</v>
       </c>
       <c r="G57" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H57" t="n">
-        <v>82.3</v>
+        <v>65.7</v>
       </c>
       <c r="I57" t="n">
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>56.15</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>441.25</v>
+        <v>-393.21</v>
       </c>
       <c r="L57" t="n">
-        <v>444.81</v>
+        <v>402.22</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:21:41</t>
+          <t>09:15:05</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.4</v>
+        <v>4.82</v>
       </c>
       <c r="F58" t="n">
-        <v>11.34</v>
+        <v>13.76</v>
       </c>
       <c r="G58" t="n">
-        <v>88.5</v>
+        <v>70</v>
       </c>
       <c r="H58" t="n">
-        <v>84</v>
+        <v>58.7</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>52.36</v>
+        <v>-161.95</v>
       </c>
       <c r="K58" t="n">
-        <v>35.1</v>
+        <v>348.53</v>
       </c>
       <c r="L58" t="n">
-        <v>63.04</v>
+        <v>384.32</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:32:08</t>
+          <t>09:25:11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.99</v>
+        <v>4.93</v>
       </c>
       <c r="F59" t="n">
         <v>14.6</v>
       </c>
       <c r="G59" t="n">
-        <v>77.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="H59" t="n">
-        <v>83.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="I59" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>9.52</v>
+        <v>-33.38</v>
       </c>
       <c r="K59" t="n">
-        <v>-78.64</v>
+        <v>88.88</v>
       </c>
       <c r="L59" t="n">
-        <v>79.20999999999999</v>
+        <v>94.94</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:34:00</t>
+          <t>09:26:31</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.97</v>
+        <v>5.06</v>
       </c>
       <c r="F60" t="n">
-        <v>12.86</v>
+        <v>14.6</v>
       </c>
       <c r="G60" t="n">
-        <v>96.3</v>
+        <v>81</v>
       </c>
       <c r="H60" t="n">
-        <v>85</v>
+        <v>41.9</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.83</v>
+        <v>96.38</v>
       </c>
       <c r="K60" t="n">
-        <v>65.81</v>
+        <v>19.45</v>
       </c>
       <c r="L60" t="n">
-        <v>65.98</v>
+        <v>98.33</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:35:02</t>
+          <t>09:27:31</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>5.4</v>
+        <v>4.47</v>
       </c>
       <c r="F61" t="n">
-        <v>14.12</v>
+        <v>14.6</v>
       </c>
       <c r="G61" t="n">
-        <v>94.8</v>
+        <v>103.1</v>
       </c>
       <c r="H61" t="n">
-        <v>78.09999999999999</v>
+        <v>55.3</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-67.47</v>
+        <v>39.54</v>
       </c>
       <c r="K61" t="n">
-        <v>-31.89</v>
+        <v>-44.32</v>
       </c>
       <c r="L61" t="n">
-        <v>74.62</v>
+        <v>59.39</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:39:29</t>
+          <t>09:32:12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>5.74</v>
+        <v>4.78</v>
       </c>
       <c r="F62" t="n">
-        <v>12.69</v>
+        <v>14.6</v>
       </c>
       <c r="G62" t="n">
-        <v>76.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>81.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>102.64</v>
+        <v>59.3</v>
       </c>
       <c r="K62" t="n">
-        <v>-9.32</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>103.07</v>
+        <v>99.59</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:41:19</t>
+          <t>09:33:31</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.81</v>
+        <v>4.92</v>
       </c>
       <c r="F63" t="n">
-        <v>14.6</v>
+        <v>12.3</v>
       </c>
       <c r="G63" t="n">
-        <v>90.59999999999999</v>
+        <v>102.6</v>
       </c>
       <c r="H63" t="n">
-        <v>74.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-33.08</v>
+        <v>-55.36</v>
       </c>
       <c r="K63" t="n">
-        <v>-106.45</v>
+        <v>-133.5</v>
       </c>
       <c r="L63" t="n">
-        <v>111.47</v>
+        <v>144.52</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:43:09</t>
+          <t>09:34:48</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.29</v>
+        <v>5.17</v>
       </c>
       <c r="F64" t="n">
-        <v>14.6</v>
+        <v>13.48</v>
       </c>
       <c r="G64" t="n">
-        <v>92.5</v>
+        <v>70.8</v>
       </c>
       <c r="H64" t="n">
-        <v>78.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>51.77</v>
+        <v>128.25</v>
       </c>
       <c r="K64" t="n">
-        <v>124.4</v>
+        <v>24.8</v>
       </c>
       <c r="L64" t="n">
-        <v>134.74</v>
+        <v>130.62</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:47:11</t>
+          <t>09:39:50</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.51</v>
+        <v>4.61</v>
       </c>
       <c r="F65" t="n">
-        <v>13.66</v>
+        <v>12.22</v>
       </c>
       <c r="G65" t="n">
-        <v>79.2</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H65" t="n">
-        <v>88.5</v>
+        <v>68.2</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-142.94</v>
+        <v>-111.92</v>
       </c>
       <c r="K65" t="n">
-        <v>-101.16</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>175.11</v>
+        <v>145.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:48:14</t>
+          <t>09:42:25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.35</v>
+        <v>4.93</v>
       </c>
       <c r="F66" t="n">
         <v>14.6</v>
       </c>
       <c r="G66" t="n">
-        <v>84.40000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>80.09999999999999</v>
+        <v>48.1</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-53.86</v>
+        <v>186.23</v>
       </c>
       <c r="K66" t="n">
-        <v>150.84</v>
+        <v>-58.08</v>
       </c>
       <c r="L66" t="n">
-        <v>160.17</v>
+        <v>195.08</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:49:46</t>
+          <t>09:44:14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.69</v>
+        <v>4.13</v>
       </c>
       <c r="F67" t="n">
-        <v>14.6</v>
+        <v>11.73</v>
       </c>
       <c r="G67" t="n">
-        <v>93.7</v>
+        <v>88.5</v>
       </c>
       <c r="H67" t="n">
-        <v>75.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>2.32</v>
+        <v>146.36</v>
       </c>
       <c r="K67" t="n">
-        <v>199.17</v>
+        <v>24.09</v>
       </c>
       <c r="L67" t="n">
-        <v>199.18</v>
+        <v>148.33</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:55:22</t>
+          <t>09:48:53</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.89</v>
+        <v>4.82</v>
       </c>
       <c r="F68" t="n">
         <v>14.6</v>
       </c>
       <c r="G68" t="n">
-        <v>92.7</v>
+        <v>92.5</v>
       </c>
       <c r="H68" t="n">
-        <v>78.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-80.61</v>
+        <v>266.44</v>
       </c>
       <c r="K68" t="n">
-        <v>-132.44</v>
+        <v>-98.69</v>
       </c>
       <c r="L68" t="n">
-        <v>155.04</v>
+        <v>284.13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:56:51</t>
+          <t>09:50:05</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.28</v>
+        <v>5.69</v>
       </c>
       <c r="F69" t="n">
-        <v>12.47</v>
+        <v>14.6</v>
       </c>
       <c r="G69" t="n">
-        <v>87.90000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="H69" t="n">
-        <v>79.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>24.52</v>
+        <v>-282.29</v>
       </c>
       <c r="K69" t="n">
-        <v>191.6</v>
+        <v>574.6</v>
       </c>
       <c r="L69" t="n">
-        <v>193.16</v>
+        <v>640.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:59:16</t>
+          <t>09:52:40</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>6.22</v>
+        <v>4.86</v>
       </c>
       <c r="F70" t="n">
         <v>14.6</v>
       </c>
       <c r="G70" t="n">
-        <v>85</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H70" t="n">
-        <v>77.5</v>
+        <v>36.1</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>38.25</v>
+        <v>140.66</v>
       </c>
       <c r="K70" t="n">
-        <v>265.95</v>
+        <v>224.57</v>
       </c>
       <c r="L70" t="n">
-        <v>268.69</v>
+        <v>264.98</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:04:41</t>
+          <t>09:55:40</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.39</v>
+        <v>5.13</v>
       </c>
       <c r="F71" t="n">
         <v>14.6</v>
       </c>
       <c r="G71" t="n">
-        <v>85.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>84.59999999999999</v>
+        <v>47.7</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-298.52</v>
+        <v>-322.63</v>
       </c>
       <c r="K71" t="n">
-        <v>-217.2</v>
+        <v>241.15</v>
       </c>
       <c r="L71" t="n">
-        <v>369.18</v>
+        <v>402.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:05:44</t>
+          <t>09:57:15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.31</v>
+        <v>4.95</v>
       </c>
       <c r="F72" t="n">
-        <v>12.7</v>
+        <v>12.44</v>
       </c>
       <c r="G72" t="n">
-        <v>78</v>
+        <v>81.7</v>
       </c>
       <c r="H72" t="n">
-        <v>80.3</v>
+        <v>95.5</v>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>245.21</v>
+        <v>285.77</v>
       </c>
       <c r="K72" t="n">
-        <v>196.01</v>
+        <v>-90.72</v>
       </c>
       <c r="L72" t="n">
-        <v>313.93</v>
+        <v>299.82</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:07:33</t>
+          <t>09:58:56</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.17</v>
+        <v>5.65</v>
       </c>
       <c r="F73" t="n">
-        <v>13.98</v>
+        <v>14.51</v>
       </c>
       <c r="G73" t="n">
-        <v>89.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="H73" t="n">
-        <v>81.5</v>
+        <v>47.7</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>307.16</v>
+        <v>372.21</v>
       </c>
       <c r="K73" t="n">
-        <v>154.9</v>
+        <v>165.92</v>
       </c>
       <c r="L73" t="n">
-        <v>344</v>
+        <v>407.52</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:17:29</t>
+          <t>10:08:25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.02</v>
+        <v>5.08</v>
       </c>
       <c r="F74" t="n">
-        <v>14.6</v>
+        <v>10.51</v>
       </c>
       <c r="G74" t="n">
-        <v>92.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>89.8</v>
+        <v>52</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>-73.03</v>
+        <v>221.09</v>
       </c>
       <c r="K74" t="n">
-        <v>11.76</v>
+        <v>-67</v>
       </c>
       <c r="L74" t="n">
-        <v>73.97</v>
+        <v>231.02</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:19:16</t>
+          <t>10:10:15</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="F75" t="n">
-        <v>13.05</v>
+        <v>13.36</v>
       </c>
       <c r="G75" t="n">
-        <v>82.5</v>
+        <v>85.5</v>
       </c>
       <c r="H75" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-67.2</v>
+        <v>-6.36</v>
       </c>
       <c r="K75" t="n">
-        <v>44.24</v>
+        <v>-118.9</v>
       </c>
       <c r="L75" t="n">
-        <v>80.45</v>
+        <v>119.07</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:20:09</t>
+          <t>10:12:20</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.42</v>
+        <v>5.28</v>
       </c>
       <c r="F76" t="n">
         <v>14.6</v>
       </c>
       <c r="G76" t="n">
-        <v>82.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>77.3</v>
+        <v>57.7</v>
       </c>
       <c r="I76" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>-100.65</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.58</v>
+        <v>-112.74</v>
       </c>
       <c r="L76" t="n">
-        <v>100.76</v>
+        <v>140.14</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:24:36</t>
+          <t>10:17:41</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.38</v>
+        <v>4.13</v>
       </c>
       <c r="F77" t="n">
-        <v>14.45</v>
+        <v>10.86</v>
       </c>
       <c r="G77" t="n">
-        <v>80.7</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>89.3</v>
+        <v>65.2</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>85.90000000000001</v>
+        <v>-20.85</v>
       </c>
       <c r="K77" t="n">
-        <v>-32.59</v>
+        <v>-54.11</v>
       </c>
       <c r="L77" t="n">
-        <v>91.88</v>
+        <v>57.99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:26:42</t>
+          <t>10:18:43</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.45</v>
+        <v>4.68</v>
       </c>
       <c r="F78" t="n">
         <v>14.6</v>
       </c>
       <c r="G78" t="n">
-        <v>83.09999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="H78" t="n">
-        <v>74.2</v>
+        <v>42.6</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>0.11</v>
+        <v>95</v>
       </c>
       <c r="K78" t="n">
-        <v>97.09</v>
+        <v>-63.73</v>
       </c>
       <c r="L78" t="n">
-        <v>97.09</v>
+        <v>114.39</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:27:30</t>
+          <t>10:20:43</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.09</v>
+        <v>4.64</v>
       </c>
       <c r="F79" t="n">
-        <v>14.6</v>
+        <v>14.17</v>
       </c>
       <c r="G79" t="n">
-        <v>88</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>82</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>-52.07</v>
+        <v>-70.16</v>
       </c>
       <c r="K79" t="n">
-        <v>97.2</v>
+        <v>-97.5</v>
       </c>
       <c r="L79" t="n">
-        <v>110.27</v>
+        <v>120.11</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:32:06</t>
+          <t>10:24:17</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.97</v>
+        <v>4.79</v>
       </c>
       <c r="F80" t="n">
-        <v>12.91</v>
+        <v>11.82</v>
       </c>
       <c r="G80" t="n">
-        <v>81.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="H80" t="n">
-        <v>84.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="I80" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>146.3</v>
+        <v>145.08</v>
       </c>
       <c r="K80" t="n">
-        <v>-40.6</v>
+        <v>-17.78</v>
       </c>
       <c r="L80" t="n">
-        <v>151.83</v>
+        <v>146.17</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:33:27</t>
+          <t>10:25:56</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.92</v>
+        <v>5.7</v>
       </c>
       <c r="F81" t="n">
-        <v>14.6</v>
+        <v>14.45</v>
       </c>
       <c r="G81" t="n">
-        <v>77.2</v>
+        <v>100.8</v>
       </c>
       <c r="H81" t="n">
-        <v>81.90000000000001</v>
+        <v>57</v>
       </c>
       <c r="I81" t="n">
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>10.96</v>
+        <v>171.7</v>
       </c>
       <c r="K81" t="n">
-        <v>-152.16</v>
+        <v>-87.5</v>
       </c>
       <c r="L81" t="n">
-        <v>152.56</v>
+        <v>192.71</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:35:27</t>
+          <t>10:27:49</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.86</v>
+        <v>5.01</v>
       </c>
       <c r="F82" t="n">
-        <v>14.6</v>
+        <v>13.29</v>
       </c>
       <c r="G82" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>81.8</v>
+        <v>71.3</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>163.01</v>
+        <v>213.46</v>
       </c>
       <c r="K82" t="n">
-        <v>93.8</v>
+        <v>-130.89</v>
       </c>
       <c r="L82" t="n">
-        <v>188.07</v>
+        <v>250.4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:40:01</t>
+          <t>10:32:45</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.39</v>
+        <v>5.21</v>
       </c>
       <c r="F83" t="n">
-        <v>14.34</v>
+        <v>12.98</v>
       </c>
       <c r="G83" t="n">
-        <v>82</v>
+        <v>63.1</v>
       </c>
       <c r="H83" t="n">
-        <v>81.59999999999999</v>
+        <v>34.3</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>152.57</v>
+        <v>241.09</v>
       </c>
       <c r="K83" t="n">
-        <v>-135.88</v>
+        <v>162.4</v>
       </c>
       <c r="L83" t="n">
-        <v>204.31</v>
+        <v>290.69</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:42:05</t>
+          <t>10:34:49</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>5.18</v>
+        <v>5.4</v>
       </c>
       <c r="F84" t="n">
         <v>14.6</v>
       </c>
       <c r="G84" t="n">
-        <v>74.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="H84" t="n">
-        <v>84</v>
+        <v>60.3</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>156.05</v>
+        <v>-235.93</v>
       </c>
       <c r="K84" t="n">
-        <v>126.02</v>
+        <v>163.71</v>
       </c>
       <c r="L84" t="n">
-        <v>200.58</v>
+        <v>287.17</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:44:05</t>
+          <t>10:36:30</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>6.09</v>
+        <v>5.43</v>
       </c>
       <c r="F85" t="n">
         <v>14.6</v>
       </c>
       <c r="G85" t="n">
-        <v>81.7</v>
+        <v>96.3</v>
       </c>
       <c r="H85" t="n">
-        <v>80.5</v>
+        <v>43.7</v>
       </c>
       <c r="I85" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-48.39</v>
+        <v>-148.1</v>
       </c>
       <c r="K85" t="n">
-        <v>-202.35</v>
+        <v>-333.36</v>
       </c>
       <c r="L85" t="n">
-        <v>208.05</v>
+        <v>364.78</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:48:02</t>
+          <t>10:42:01</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="F86" t="n">
-        <v>14.6</v>
+        <v>13.68</v>
       </c>
       <c r="G86" t="n">
-        <v>78.8</v>
+        <v>65</v>
       </c>
       <c r="H86" t="n">
-        <v>80.59999999999999</v>
+        <v>50.5</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J86" t="n">
-        <v>405.02</v>
+        <v>-23.78</v>
       </c>
       <c r="K86" t="n">
-        <v>194.73</v>
+        <v>-272.6</v>
       </c>
       <c r="L86" t="n">
-        <v>449.4</v>
+        <v>273.64</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:50:16</t>
+          <t>10:44:07</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.56</v>
+        <v>5.65</v>
       </c>
       <c r="F87" t="n">
         <v>14.6</v>
       </c>
       <c r="G87" t="n">
-        <v>85.7</v>
+        <v>75.7</v>
       </c>
       <c r="H87" t="n">
-        <v>79.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>35.56</v>
+        <v>443.81</v>
       </c>
       <c r="K87" t="n">
-        <v>-379.53</v>
+        <v>-113.42</v>
       </c>
       <c r="L87" t="n">
-        <v>381.19</v>
+        <v>458.07</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:51:53</t>
+          <t>10:46:21</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.26</v>
+        <v>5.18</v>
       </c>
       <c r="F88" t="n">
-        <v>14.37</v>
+        <v>14.6</v>
       </c>
       <c r="G88" t="n">
-        <v>81.7</v>
+        <v>87.8</v>
       </c>
       <c r="H88" t="n">
-        <v>79</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>361.76</v>
+        <v>251.36</v>
       </c>
       <c r="K88" t="n">
-        <v>-101.97</v>
+        <v>256.96</v>
       </c>
       <c r="L88" t="n">
-        <v>375.85</v>
+        <v>359.46</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-29.xlsx
+++ b/output/2025-09-29.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.74</v>
+        <v>4.68</v>
       </c>
       <c r="F14" t="n">
-        <v>13.59</v>
+        <v>12.18</v>
       </c>
       <c r="G14" t="n">
-        <v>87.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="H14" t="n">
-        <v>70.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>119.13</v>
+        <v>-3.59</v>
       </c>
       <c r="K14" t="n">
-        <v>-40.65</v>
+        <v>106.79</v>
       </c>
       <c r="L14" t="n">
-        <v>125.88</v>
+        <v>106.85</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:16:24</t>
+          <t>07:15:38</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.41</v>
+        <v>3.97</v>
       </c>
       <c r="F15" t="n">
-        <v>10.25</v>
+        <v>9.43</v>
       </c>
       <c r="G15" t="n">
-        <v>88.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="H15" t="n">
-        <v>33.9</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>114.34</v>
+        <v>13.06</v>
       </c>
       <c r="K15" t="n">
-        <v>64.09</v>
+        <v>-72.54000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>131.08</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:17:01</t>
+          <t>07:17:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>5.13</v>
       </c>
       <c r="F16" t="n">
-        <v>7.88</v>
+        <v>12.53</v>
       </c>
       <c r="G16" t="n">
-        <v>85.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="H16" t="n">
-        <v>73</v>
+        <v>50.8</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>-18.7</v>
+        <v>121.11</v>
       </c>
       <c r="K16" t="n">
-        <v>47.4</v>
+        <v>-78.73999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>50.96</v>
+        <v>144.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:21:48</t>
+          <t>07:21:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.53</v>
+        <v>4.51</v>
       </c>
       <c r="F17" t="n">
-        <v>7.65</v>
+        <v>11.15</v>
       </c>
       <c r="G17" t="n">
-        <v>88.8</v>
+        <v>81.7</v>
       </c>
       <c r="H17" t="n">
-        <v>93.09999999999999</v>
+        <v>41.4</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>73.79000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="K17" t="n">
-        <v>-26.62</v>
+        <v>-94.61</v>
       </c>
       <c r="L17" t="n">
-        <v>78.44</v>
+        <v>119.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:22:58</t>
+          <t>07:23:03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.65</v>
+        <v>5.12</v>
       </c>
       <c r="F18" t="n">
-        <v>8.279999999999999</v>
+        <v>12.34</v>
       </c>
       <c r="G18" t="n">
-        <v>94.3</v>
+        <v>85</v>
       </c>
       <c r="H18" t="n">
-        <v>32.4</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>44.14</v>
+        <v>73.81</v>
       </c>
       <c r="K18" t="n">
-        <v>-50.56</v>
+        <v>156.46</v>
       </c>
       <c r="L18" t="n">
-        <v>67.12</v>
+        <v>172.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:24:32</t>
+          <t>07:24:58</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.86</v>
+        <v>4.8</v>
       </c>
       <c r="F19" t="n">
-        <v>7.62</v>
+        <v>14.6</v>
       </c>
       <c r="G19" t="n">
-        <v>95.7</v>
+        <v>83.7</v>
       </c>
       <c r="H19" t="n">
-        <v>35.2</v>
+        <v>38.5</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>-23.19</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-86.29000000000001</v>
+        <v>44.11</v>
       </c>
       <c r="L19" t="n">
-        <v>89.34999999999999</v>
+        <v>90.78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:30:31</t>
+          <t>07:30:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5.17</v>
+        <v>4.5</v>
       </c>
       <c r="F20" t="n">
-        <v>11.74</v>
+        <v>10.65</v>
       </c>
       <c r="G20" t="n">
-        <v>85</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>89.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>115.67</v>
+        <v>149.42</v>
       </c>
       <c r="K20" t="n">
-        <v>186.58</v>
+        <v>44.42</v>
       </c>
       <c r="L20" t="n">
-        <v>219.53</v>
+        <v>155.88</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:31:49</t>
+          <t>07:32:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.24</v>
+        <v>4.39</v>
       </c>
       <c r="F21" t="n">
-        <v>10.37</v>
+        <v>11.19</v>
       </c>
       <c r="G21" t="n">
-        <v>91</v>
+        <v>94.2</v>
       </c>
       <c r="H21" t="n">
-        <v>39.3</v>
+        <v>80.5</v>
       </c>
       <c r="I21" t="n">
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-67</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-149.04</v>
+        <v>63.86</v>
       </c>
       <c r="L21" t="n">
-        <v>163.41</v>
+        <v>118.22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:33:13</t>
+          <t>07:33:06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
       <c r="F22" t="n">
-        <v>11.84</v>
+        <v>11.52</v>
       </c>
       <c r="G22" t="n">
-        <v>89.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>39</v>
+        <v>6.5</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>34.54</v>
+        <v>-167.35</v>
       </c>
       <c r="K22" t="n">
-        <v>154.73</v>
+        <v>-76.91</v>
       </c>
       <c r="L22" t="n">
-        <v>158.54</v>
+        <v>184.18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:37:25</t>
+          <t>07:36:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.68</v>
+        <v>4.61</v>
       </c>
       <c r="F23" t="n">
-        <v>10.86</v>
+        <v>12.89</v>
       </c>
       <c r="G23" t="n">
-        <v>90.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>29.4</v>
+        <v>50.5</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>94.16</v>
+        <v>98.59</v>
       </c>
       <c r="K23" t="n">
-        <v>-48.67</v>
+        <v>-224.88</v>
       </c>
       <c r="L23" t="n">
-        <v>105.99</v>
+        <v>245.54</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:39:37</t>
+          <t>07:38:28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.23</v>
+        <v>4.41</v>
       </c>
       <c r="F24" t="n">
-        <v>9.99</v>
+        <v>10.63</v>
       </c>
       <c r="G24" t="n">
-        <v>85</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>85.2</v>
+        <v>60.4</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>211.96</v>
+        <v>196.78</v>
       </c>
       <c r="K24" t="n">
-        <v>54.56</v>
+        <v>-122.26</v>
       </c>
       <c r="L24" t="n">
-        <v>218.87</v>
+        <v>231.67</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:41:37</t>
+          <t>07:39:24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5.34</v>
+        <v>5.15</v>
       </c>
       <c r="F25" t="n">
-        <v>9.6</v>
+        <v>10.06</v>
       </c>
       <c r="G25" t="n">
-        <v>78.90000000000001</v>
+        <v>100.3</v>
       </c>
       <c r="H25" t="n">
-        <v>87.8</v>
+        <v>37.4</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-104.43</v>
+        <v>-266.33</v>
       </c>
       <c r="K25" t="n">
-        <v>369.7</v>
+        <v>99.81</v>
       </c>
       <c r="L25" t="n">
-        <v>384.17</v>
+        <v>284.42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:45:50</t>
+          <t>07:42:47</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.63</v>
+        <v>4.66</v>
       </c>
       <c r="F26" t="n">
-        <v>12.44</v>
+        <v>12.31</v>
       </c>
       <c r="G26" t="n">
-        <v>89.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>55.8</v>
+        <v>59.7</v>
       </c>
       <c r="I26" t="n">
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>175.42</v>
+        <v>44.33</v>
       </c>
       <c r="K26" t="n">
-        <v>-145.55</v>
+        <v>276.03</v>
       </c>
       <c r="L26" t="n">
-        <v>227.94</v>
+        <v>279.56</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:47:56</t>
+          <t>07:45:18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.21</v>
+        <v>4.98</v>
       </c>
       <c r="F27" t="n">
-        <v>8.77</v>
+        <v>14.6</v>
       </c>
       <c r="G27" t="n">
-        <v>84.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>52.8</v>
+        <v>40.5</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>167.88</v>
+        <v>-277.08</v>
       </c>
       <c r="K27" t="n">
-        <v>331.42</v>
+        <v>-367.79</v>
       </c>
       <c r="L27" t="n">
-        <v>371.51</v>
+        <v>460.48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:49:14</t>
+          <t>07:47:17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.83</v>
+        <v>4.24</v>
       </c>
       <c r="F28" t="n">
-        <v>13.45</v>
+        <v>11.87</v>
       </c>
       <c r="G28" t="n">
-        <v>73</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>65.90000000000001</v>
+        <v>58.2</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>300.43</v>
+        <v>-158.1</v>
       </c>
       <c r="K28" t="n">
-        <v>225.66</v>
+        <v>-266.93</v>
       </c>
       <c r="L28" t="n">
-        <v>375.74</v>
+        <v>310.24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:57:45</t>
+          <t>08:00:03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.1</v>
+        <v>4.48</v>
       </c>
       <c r="F29" t="n">
-        <v>12.73</v>
+        <v>12.77</v>
       </c>
       <c r="G29" t="n">
-        <v>101.4</v>
+        <v>95.8</v>
       </c>
       <c r="H29" t="n">
-        <v>67.5</v>
+        <v>51.7</v>
       </c>
       <c r="I29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>57.5</v>
+        <v>90.23</v>
       </c>
       <c r="K29" t="n">
-        <v>35.11</v>
+        <v>23.34</v>
       </c>
       <c r="L29" t="n">
-        <v>67.37</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:59:20</t>
+          <t>08:01:20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.57</v>
+        <v>4.31</v>
       </c>
       <c r="F30" t="n">
-        <v>12.11</v>
+        <v>9.75</v>
       </c>
       <c r="G30" t="n">
-        <v>88.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>71.09999999999999</v>
+        <v>46.1</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>93.40000000000001</v>
+        <v>26.01</v>
       </c>
       <c r="K30" t="n">
-        <v>-82.86</v>
+        <v>-57.46</v>
       </c>
       <c r="L30" t="n">
-        <v>124.86</v>
+        <v>63.07</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:00:21</t>
+          <t>08:03:29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.4</v>
+        <v>4.07</v>
       </c>
       <c r="F31" t="n">
-        <v>12.78</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>83.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>26.2</v>
+        <v>44.8</v>
       </c>
       <c r="I31" t="n">
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>3.06</v>
+        <v>67.7</v>
       </c>
       <c r="K31" t="n">
-        <v>59.2</v>
+        <v>-41.96</v>
       </c>
       <c r="L31" t="n">
-        <v>59.28</v>
+        <v>79.65000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:03:25</t>
+          <t>08:07:47</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>5.06</v>
+        <v>4.88</v>
       </c>
       <c r="F32" t="n">
-        <v>14.01</v>
+        <v>12.84</v>
       </c>
       <c r="G32" t="n">
-        <v>90.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>53.1</v>
+        <v>63.9</v>
       </c>
       <c r="I32" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>192.96</v>
+        <v>114.18</v>
       </c>
       <c r="K32" t="n">
-        <v>-17.44</v>
+        <v>-21.65</v>
       </c>
       <c r="L32" t="n">
-        <v>193.75</v>
+        <v>116.21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:04:50</t>
+          <t>08:10:01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.56</v>
+        <v>4.21</v>
       </c>
       <c r="F33" t="n">
-        <v>12.18</v>
+        <v>12.09</v>
       </c>
       <c r="G33" t="n">
-        <v>90.7</v>
+        <v>90</v>
       </c>
       <c r="H33" t="n">
-        <v>61.2</v>
+        <v>40.8</v>
       </c>
       <c r="I33" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>342.54</v>
+        <v>50.23</v>
       </c>
       <c r="K33" t="n">
-        <v>156.68</v>
+        <v>113.89</v>
       </c>
       <c r="L33" t="n">
-        <v>376.67</v>
+        <v>124.47</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:07:11</t>
+          <t>08:10:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.68</v>
+        <v>3.69</v>
       </c>
       <c r="F34" t="n">
-        <v>14.5</v>
+        <v>9.75</v>
       </c>
       <c r="G34" t="n">
-        <v>79</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>38.9</v>
+        <v>9.5</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>28.12</v>
+        <v>93.53</v>
       </c>
       <c r="K34" t="n">
-        <v>-120.94</v>
+        <v>3.75</v>
       </c>
       <c r="L34" t="n">
-        <v>124.17</v>
+        <v>93.61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:11:35</t>
+          <t>08:16:05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.2</v>
+        <v>4.83</v>
       </c>
       <c r="F35" t="n">
-        <v>12.95</v>
+        <v>14.6</v>
       </c>
       <c r="G35" t="n">
-        <v>94.2</v>
+        <v>100.3</v>
       </c>
       <c r="H35" t="n">
-        <v>65.90000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>64.89</v>
+        <v>110.22</v>
       </c>
       <c r="K35" t="n">
-        <v>236.56</v>
+        <v>59.98</v>
       </c>
       <c r="L35" t="n">
-        <v>245.3</v>
+        <v>125.48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:13:00</t>
+          <t>08:16:43</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>5.72</v>
+        <v>4.46</v>
       </c>
       <c r="F36" t="n">
-        <v>13.49</v>
+        <v>10.9</v>
       </c>
       <c r="G36" t="n">
-        <v>91</v>
+        <v>81.3</v>
       </c>
       <c r="H36" t="n">
-        <v>60</v>
+        <v>64.2</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J36" t="n">
-        <v>93.20999999999999</v>
+        <v>188.14</v>
       </c>
       <c r="K36" t="n">
-        <v>-243.69</v>
+        <v>-15.45</v>
       </c>
       <c r="L36" t="n">
-        <v>260.91</v>
+        <v>188.78</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:14:56</t>
+          <t>08:18:13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.99</v>
+        <v>5.25</v>
       </c>
       <c r="F37" t="n">
-        <v>13.3</v>
+        <v>14.15</v>
       </c>
       <c r="G37" t="n">
-        <v>91</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>88.2</v>
+        <v>33.5</v>
       </c>
       <c r="I37" t="n">
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>137.2</v>
+        <v>276.46</v>
       </c>
       <c r="K37" t="n">
-        <v>165.99</v>
+        <v>102.62</v>
       </c>
       <c r="L37" t="n">
-        <v>215.35</v>
+        <v>294.89</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:19:04</t>
+          <t>08:23:24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.25</v>
+        <v>4.46</v>
       </c>
       <c r="F38" t="n">
-        <v>10.67</v>
+        <v>13.65</v>
       </c>
       <c r="G38" t="n">
-        <v>72.8</v>
+        <v>82.8</v>
       </c>
       <c r="H38" t="n">
-        <v>71.7</v>
+        <v>56.9</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>243.14</v>
+        <v>222.15</v>
       </c>
       <c r="K38" t="n">
-        <v>-87.64</v>
+        <v>97.17</v>
       </c>
       <c r="L38" t="n">
-        <v>258.45</v>
+        <v>242.47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:21:39</t>
+          <t>08:25:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.97</v>
+        <v>4.79</v>
       </c>
       <c r="F39" t="n">
-        <v>10.79</v>
+        <v>14.6</v>
       </c>
       <c r="G39" t="n">
-        <v>85.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>57.1</v>
+        <v>62.2</v>
       </c>
       <c r="I39" t="n">
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>106.61</v>
+        <v>17.18</v>
       </c>
       <c r="K39" t="n">
-        <v>-310.14</v>
+        <v>314.35</v>
       </c>
       <c r="L39" t="n">
-        <v>327.95</v>
+        <v>314.82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:24:06</t>
+          <t>08:27:56</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.79</v>
+        <v>4.07</v>
       </c>
       <c r="F40" t="n">
-        <v>14.6</v>
+        <v>8.91</v>
       </c>
       <c r="G40" t="n">
-        <v>82.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="H40" t="n">
-        <v>59.5</v>
+        <v>19.1</v>
       </c>
       <c r="I40" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>385.3</v>
+        <v>-287.28</v>
       </c>
       <c r="K40" t="n">
-        <v>-174.74</v>
+        <v>73.75</v>
       </c>
       <c r="L40" t="n">
-        <v>423.07</v>
+        <v>296.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:28:00</t>
+          <t>08:33:18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="F41" t="n">
-        <v>14.55</v>
+        <v>9.6</v>
       </c>
       <c r="G41" t="n">
-        <v>81.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="H41" t="n">
-        <v>51.9</v>
+        <v>62</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-312.04</v>
+        <v>372.18</v>
       </c>
       <c r="K41" t="n">
-        <v>196.45</v>
+        <v>-29.11</v>
       </c>
       <c r="L41" t="n">
-        <v>368.73</v>
+        <v>373.32</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:30:27</t>
+          <t>08:35:20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.19</v>
+        <v>4.7</v>
       </c>
       <c r="F42" t="n">
-        <v>10.99</v>
+        <v>10.04</v>
       </c>
       <c r="G42" t="n">
-        <v>99.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>36.1</v>
+        <v>58.2</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>204.51</v>
+        <v>367.12</v>
       </c>
       <c r="K42" t="n">
-        <v>-234.93</v>
+        <v>-10.58</v>
       </c>
       <c r="L42" t="n">
-        <v>311.48</v>
+        <v>367.27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:32:00</t>
+          <t>08:36:45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>5.86</v>
+        <v>5.6</v>
       </c>
       <c r="F43" t="n">
-        <v>14.6</v>
+        <v>13.78</v>
       </c>
       <c r="G43" t="n">
-        <v>68.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>215.2</v>
+        <v>-361.17</v>
       </c>
       <c r="K43" t="n">
-        <v>337.03</v>
+        <v>-172.21</v>
       </c>
       <c r="L43" t="n">
-        <v>399.88</v>
+        <v>400.12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:40:27</t>
+          <t>08:44:45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.17</v>
+        <v>4.9</v>
       </c>
       <c r="F44" t="n">
-        <v>14.6</v>
+        <v>13.28</v>
       </c>
       <c r="G44" t="n">
-        <v>96.3</v>
+        <v>80</v>
       </c>
       <c r="H44" t="n">
-        <v>29.8</v>
+        <v>56.2</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>101.01</v>
+        <v>116.04</v>
       </c>
       <c r="K44" t="n">
-        <v>-33.08</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>106.29</v>
+        <v>116.35</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:42:03</t>
+          <t>08:47:06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>5.22</v>
+        <v>4.46</v>
       </c>
       <c r="F45" t="n">
         <v>14.6</v>
       </c>
       <c r="G45" t="n">
-        <v>83.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>71.7</v>
+        <v>55.2</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>70.34</v>
+        <v>-89.7</v>
       </c>
       <c r="K45" t="n">
-        <v>-58.75</v>
+        <v>-13.75</v>
       </c>
       <c r="L45" t="n">
-        <v>91.65000000000001</v>
+        <v>90.73999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:43:46</t>
+          <t>08:48:35</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>5.27</v>
+        <v>4.51</v>
       </c>
       <c r="F46" t="n">
-        <v>13.79</v>
+        <v>10.42</v>
       </c>
       <c r="G46" t="n">
-        <v>95.2</v>
+        <v>86</v>
       </c>
       <c r="H46" t="n">
-        <v>27.1</v>
+        <v>75.5</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-78.84</v>
+        <v>90.02</v>
       </c>
       <c r="K46" t="n">
-        <v>-91.59999999999999</v>
+        <v>58.87</v>
       </c>
       <c r="L46" t="n">
-        <v>120.86</v>
+        <v>107.56</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:47:56</t>
+          <t>08:53:03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.38</v>
+        <v>4.66</v>
       </c>
       <c r="F47" t="n">
-        <v>14.6</v>
+        <v>12.33</v>
       </c>
       <c r="G47" t="n">
-        <v>101</v>
+        <v>82.7</v>
       </c>
       <c r="H47" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>-67.97</v>
+        <v>-57.97</v>
       </c>
       <c r="K47" t="n">
-        <v>-166.41</v>
+        <v>-147.03</v>
       </c>
       <c r="L47" t="n">
-        <v>179.76</v>
+        <v>158.05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:48:49</t>
+          <t>08:54:28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.92</v>
+        <v>5.1</v>
       </c>
       <c r="F48" t="n">
-        <v>12.46</v>
+        <v>13.61</v>
       </c>
       <c r="G48" t="n">
-        <v>80.2</v>
+        <v>90.8</v>
       </c>
       <c r="H48" t="n">
-        <v>41.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>110.83</v>
+        <v>146.47</v>
       </c>
       <c r="K48" t="n">
-        <v>109.81</v>
+        <v>6.8</v>
       </c>
       <c r="L48" t="n">
-        <v>156.02</v>
+        <v>146.62</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:51:01</t>
+          <t>08:56:05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.66</v>
+        <v>4.74</v>
       </c>
       <c r="F49" t="n">
-        <v>9.85</v>
+        <v>11.97</v>
       </c>
       <c r="G49" t="n">
-        <v>88</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>3.7</v>
+        <v>48.3</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-118.88</v>
+        <v>-120.52</v>
       </c>
       <c r="K49" t="n">
-        <v>154.4</v>
+        <v>-42.75</v>
       </c>
       <c r="L49" t="n">
-        <v>194.87</v>
+        <v>127.88</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:55:20</t>
+          <t>09:00:15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.65</v>
+        <v>4.13</v>
       </c>
       <c r="F50" t="n">
-        <v>12.46</v>
+        <v>13.18</v>
       </c>
       <c r="G50" t="n">
-        <v>90.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="H50" t="n">
-        <v>87.3</v>
+        <v>89.8</v>
       </c>
       <c r="I50" t="n">
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>190.03</v>
+        <v>34.88</v>
       </c>
       <c r="K50" t="n">
-        <v>-113.78</v>
+        <v>129.89</v>
       </c>
       <c r="L50" t="n">
-        <v>221.49</v>
+        <v>134.49</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:56:33</t>
+          <t>09:02:56</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.87</v>
+        <v>4.16</v>
       </c>
       <c r="F51" t="n">
-        <v>10.25</v>
+        <v>13.16</v>
       </c>
       <c r="G51" t="n">
-        <v>85.3</v>
+        <v>90.3</v>
       </c>
       <c r="H51" t="n">
-        <v>67.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>199.25</v>
+        <v>-170.43</v>
       </c>
       <c r="K51" t="n">
-        <v>28.81</v>
+        <v>6.45</v>
       </c>
       <c r="L51" t="n">
-        <v>201.32</v>
+        <v>170.55</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:58:31</t>
+          <t>09:03:59</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.22</v>
+        <v>5.74</v>
       </c>
       <c r="F52" t="n">
         <v>14.6</v>
       </c>
       <c r="G52" t="n">
-        <v>100.7</v>
+        <v>68.7</v>
       </c>
       <c r="H52" t="n">
-        <v>56.9</v>
+        <v>48.1</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-3.93</v>
+        <v>281.3</v>
       </c>
       <c r="K52" t="n">
-        <v>-45.16</v>
+        <v>69.73</v>
       </c>
       <c r="L52" t="n">
-        <v>45.33</v>
+        <v>289.82</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:03:08</t>
+          <t>09:07:40</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.94</v>
+        <v>5.33</v>
       </c>
       <c r="F53" t="n">
-        <v>14.6</v>
+        <v>13.4</v>
       </c>
       <c r="G53" t="n">
-        <v>98.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>41.7</v>
+        <v>31.2</v>
       </c>
       <c r="I53" t="n">
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-87.81</v>
+        <v>-249.6</v>
       </c>
       <c r="K53" t="n">
-        <v>306.97</v>
+        <v>-219.06</v>
       </c>
       <c r="L53" t="n">
-        <v>319.29</v>
+        <v>332.09</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:05:38</t>
+          <t>09:09:04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.56</v>
+        <v>4.81</v>
       </c>
       <c r="F54" t="n">
-        <v>11.73</v>
+        <v>14.6</v>
       </c>
       <c r="G54" t="n">
-        <v>88.3</v>
+        <v>88.8</v>
       </c>
       <c r="H54" t="n">
-        <v>93</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>131.82</v>
+        <v>252.06</v>
       </c>
       <c r="K54" t="n">
-        <v>293.19</v>
+        <v>-112.76</v>
       </c>
       <c r="L54" t="n">
-        <v>321.47</v>
+        <v>276.13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:06:53</t>
+          <t>09:10:06</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.39</v>
+        <v>4.26</v>
       </c>
       <c r="F55" t="n">
-        <v>14.6</v>
+        <v>10.78</v>
       </c>
       <c r="G55" t="n">
-        <v>96.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>94.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>352.78</v>
+        <v>-85.54000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>133.45</v>
+        <v>177.74</v>
       </c>
       <c r="L55" t="n">
-        <v>377.18</v>
+        <v>197.25</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:11:55</t>
+          <t>09:14:59</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.41</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
-        <v>13.28</v>
+        <v>14.13</v>
       </c>
       <c r="G56" t="n">
-        <v>76.5</v>
+        <v>95.7</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>35.2</v>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>-54.31</v>
+        <v>-169.75</v>
       </c>
       <c r="K56" t="n">
-        <v>-330.99</v>
+        <v>-336.07</v>
       </c>
       <c r="L56" t="n">
-        <v>335.42</v>
+        <v>376.51</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:13:51</t>
+          <t>09:16:47</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.87</v>
+        <v>5.77</v>
       </c>
       <c r="F57" t="n">
-        <v>14.22</v>
+        <v>14.54</v>
       </c>
       <c r="G57" t="n">
-        <v>77</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>65.7</v>
+        <v>57.2</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>84.68000000000001</v>
+        <v>-75.75</v>
       </c>
       <c r="K57" t="n">
-        <v>-393.21</v>
+        <v>365.89</v>
       </c>
       <c r="L57" t="n">
-        <v>402.22</v>
+        <v>373.65</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:15:05</t>
+          <t>09:18:18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.82</v>
+        <v>4.77</v>
       </c>
       <c r="F58" t="n">
-        <v>13.76</v>
+        <v>12.43</v>
       </c>
       <c r="G58" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="H58" t="n">
-        <v>58.7</v>
+        <v>39.3</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>-161.95</v>
+        <v>-242.48</v>
       </c>
       <c r="K58" t="n">
-        <v>348.53</v>
+        <v>-319.6</v>
       </c>
       <c r="L58" t="n">
-        <v>384.32</v>
+        <v>401.17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:25:11</t>
+          <t>09:26:55</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.93</v>
+        <v>4.56</v>
       </c>
       <c r="F59" t="n">
-        <v>14.6</v>
+        <v>14.51</v>
       </c>
       <c r="G59" t="n">
-        <v>93.8</v>
+        <v>81.5</v>
       </c>
       <c r="H59" t="n">
-        <v>76.3</v>
+        <v>67.7</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-33.38</v>
+        <v>108.72</v>
       </c>
       <c r="K59" t="n">
-        <v>88.88</v>
+        <v>31.64</v>
       </c>
       <c r="L59" t="n">
-        <v>94.94</v>
+        <v>113.23</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:26:31</t>
+          <t>09:29:09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.06</v>
+        <v>6.13</v>
       </c>
       <c r="F60" t="n">
         <v>14.6</v>
       </c>
       <c r="G60" t="n">
-        <v>81</v>
+        <v>90.5</v>
       </c>
       <c r="H60" t="n">
-        <v>41.9</v>
+        <v>29.4</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>96.38</v>
+        <v>49.89</v>
       </c>
       <c r="K60" t="n">
-        <v>19.45</v>
+        <v>-37.83</v>
       </c>
       <c r="L60" t="n">
-        <v>98.33</v>
+        <v>62.61</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:27:31</t>
+          <t>09:30:20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.47</v>
+        <v>4.83</v>
       </c>
       <c r="F61" t="n">
-        <v>14.6</v>
+        <v>12.62</v>
       </c>
       <c r="G61" t="n">
-        <v>103.1</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>55.3</v>
+        <v>57.2</v>
       </c>
       <c r="I61" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>39.54</v>
+        <v>39.63</v>
       </c>
       <c r="K61" t="n">
-        <v>-44.32</v>
+        <v>-103.1</v>
       </c>
       <c r="L61" t="n">
-        <v>59.39</v>
+        <v>110.45</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:32:12</t>
+          <t>09:34:16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.78</v>
+        <v>4.98</v>
       </c>
       <c r="F62" t="n">
-        <v>14.6</v>
+        <v>12.6</v>
       </c>
       <c r="G62" t="n">
-        <v>74.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="H62" t="n">
-        <v>71.59999999999999</v>
+        <v>58.2</v>
       </c>
       <c r="I62" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>59.3</v>
+        <v>125.98</v>
       </c>
       <c r="K62" t="n">
-        <v>80.01000000000001</v>
+        <v>33.89</v>
       </c>
       <c r="L62" t="n">
-        <v>99.59</v>
+        <v>130.46</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:33:31</t>
+          <t>09:35:17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.92</v>
+        <v>6.02</v>
       </c>
       <c r="F63" t="n">
-        <v>12.3</v>
+        <v>14.6</v>
       </c>
       <c r="G63" t="n">
-        <v>102.6</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>94</v>
+        <v>56.9</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-55.36</v>
+        <v>144.73</v>
       </c>
       <c r="K63" t="n">
-        <v>-133.5</v>
+        <v>-78.43000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>144.52</v>
+        <v>164.62</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:34:48</t>
+          <t>09:36:53</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>5.17</v>
+        <v>5.01</v>
       </c>
       <c r="F64" t="n">
-        <v>13.48</v>
+        <v>14.6</v>
       </c>
       <c r="G64" t="n">
-        <v>70.8</v>
+        <v>93.8</v>
       </c>
       <c r="H64" t="n">
-        <v>85.59999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J64" t="n">
-        <v>128.25</v>
+        <v>-79.81</v>
       </c>
       <c r="K64" t="n">
-        <v>24.8</v>
+        <v>-128.54</v>
       </c>
       <c r="L64" t="n">
-        <v>130.62</v>
+        <v>151.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:39:50</t>
+          <t>09:41:19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
       <c r="F65" t="n">
-        <v>12.22</v>
+        <v>13.34</v>
       </c>
       <c r="G65" t="n">
-        <v>94.59999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="H65" t="n">
-        <v>68.2</v>
+        <v>77.3</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-111.92</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>92.51000000000001</v>
+        <v>-177.8</v>
       </c>
       <c r="L65" t="n">
-        <v>145.2</v>
+        <v>200.57</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:42:25</t>
+          <t>09:43:16</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.93</v>
+        <v>5.62</v>
       </c>
       <c r="F66" t="n">
         <v>14.6</v>
       </c>
       <c r="G66" t="n">
-        <v>87.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="H66" t="n">
-        <v>48.1</v>
+        <v>52.6</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>186.23</v>
+        <v>47.72</v>
       </c>
       <c r="K66" t="n">
-        <v>-58.08</v>
+        <v>-186.14</v>
       </c>
       <c r="L66" t="n">
-        <v>195.08</v>
+        <v>192.16</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:44:14</t>
+          <t>09:45:13</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.13</v>
+        <v>5.17</v>
       </c>
       <c r="F67" t="n">
-        <v>11.73</v>
+        <v>14.6</v>
       </c>
       <c r="G67" t="n">
-        <v>88.5</v>
+        <v>79</v>
       </c>
       <c r="H67" t="n">
-        <v>74.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>146.36</v>
+        <v>-189.47</v>
       </c>
       <c r="K67" t="n">
-        <v>24.09</v>
+        <v>136.99</v>
       </c>
       <c r="L67" t="n">
-        <v>148.33</v>
+        <v>233.81</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:48:53</t>
+          <t>09:49:52</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.82</v>
+        <v>4.93</v>
       </c>
       <c r="F68" t="n">
-        <v>14.6</v>
+        <v>13.53</v>
       </c>
       <c r="G68" t="n">
-        <v>92.5</v>
+        <v>80.3</v>
       </c>
       <c r="H68" t="n">
-        <v>73.09999999999999</v>
+        <v>42.2</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>266.44</v>
+        <v>341.99</v>
       </c>
       <c r="K68" t="n">
-        <v>-98.69</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>284.13</v>
+        <v>342.09</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:50:05</t>
+          <t>09:52:30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.69</v>
+        <v>5.41</v>
       </c>
       <c r="F69" t="n">
         <v>14.6</v>
       </c>
       <c r="G69" t="n">
-        <v>97.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>71.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J69" t="n">
-        <v>-282.29</v>
+        <v>-251.47</v>
       </c>
       <c r="K69" t="n">
-        <v>574.6</v>
+        <v>239.83</v>
       </c>
       <c r="L69" t="n">
-        <v>640.2</v>
+        <v>347.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:52:40</t>
+          <t>09:53:27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.86</v>
+        <v>5.42</v>
       </c>
       <c r="F70" t="n">
         <v>14.6</v>
       </c>
       <c r="G70" t="n">
-        <v>88.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="H70" t="n">
-        <v>36.1</v>
+        <v>100</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>140.66</v>
+        <v>382.48</v>
       </c>
       <c r="K70" t="n">
-        <v>224.57</v>
+        <v>-126.84</v>
       </c>
       <c r="L70" t="n">
-        <v>264.98</v>
+        <v>402.96</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:55:40</t>
+          <t>09:58:06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
       <c r="F71" t="n">
-        <v>14.6</v>
+        <v>13.75</v>
       </c>
       <c r="G71" t="n">
-        <v>69.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="H71" t="n">
-        <v>47.7</v>
+        <v>30.6</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-322.63</v>
+        <v>459.25</v>
       </c>
       <c r="K71" t="n">
-        <v>241.15</v>
+        <v>113.05</v>
       </c>
       <c r="L71" t="n">
-        <v>402.8</v>
+        <v>472.97</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:57:15</t>
+          <t>10:00:03</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.95</v>
+        <v>5.04</v>
       </c>
       <c r="F72" t="n">
-        <v>12.44</v>
+        <v>14.01</v>
       </c>
       <c r="G72" t="n">
-        <v>81.7</v>
+        <v>84.5</v>
       </c>
       <c r="H72" t="n">
-        <v>95.5</v>
+        <v>54.6</v>
       </c>
       <c r="I72" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>285.77</v>
+        <v>582.91</v>
       </c>
       <c r="K72" t="n">
-        <v>-90.72</v>
+        <v>-299.66</v>
       </c>
       <c r="L72" t="n">
-        <v>299.82</v>
+        <v>655.42</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:58:56</t>
+          <t>10:01:04</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.65</v>
+        <v>5.22</v>
       </c>
       <c r="F73" t="n">
-        <v>14.51</v>
+        <v>12.8</v>
       </c>
       <c r="G73" t="n">
-        <v>70.8</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>47.7</v>
+        <v>61.6</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>372.21</v>
+        <v>-408.38</v>
       </c>
       <c r="K73" t="n">
-        <v>165.92</v>
+        <v>-197.91</v>
       </c>
       <c r="L73" t="n">
-        <v>407.52</v>
+        <v>453.81</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:08:25</t>
+          <t>10:12:21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.08</v>
+        <v>5.83</v>
       </c>
       <c r="F74" t="n">
-        <v>10.51</v>
+        <v>14.6</v>
       </c>
       <c r="G74" t="n">
-        <v>79.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="H74" t="n">
-        <v>52</v>
+        <v>68.5</v>
       </c>
       <c r="I74" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>221.09</v>
+        <v>135.07</v>
       </c>
       <c r="K74" t="n">
-        <v>-67</v>
+        <v>89.41</v>
       </c>
       <c r="L74" t="n">
-        <v>231.02</v>
+        <v>161.98</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:10:15</t>
+          <t>10:14:43</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="F75" t="n">
-        <v>13.36</v>
+        <v>14.6</v>
       </c>
       <c r="G75" t="n">
-        <v>85.5</v>
+        <v>71.3</v>
       </c>
       <c r="H75" t="n">
-        <v>91</v>
+        <v>57.2</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.36</v>
+        <v>32.38</v>
       </c>
       <c r="K75" t="n">
-        <v>-118.9</v>
+        <v>-84.70999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>119.07</v>
+        <v>90.69</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:12:20</t>
+          <t>10:15:44</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.28</v>
+        <v>5.21</v>
       </c>
       <c r="F76" t="n">
         <v>14.6</v>
       </c>
       <c r="G76" t="n">
-        <v>81.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="H76" t="n">
-        <v>57.7</v>
+        <v>47.2</v>
       </c>
       <c r="I76" t="n">
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>83.23999999999999</v>
+        <v>59.83</v>
       </c>
       <c r="K76" t="n">
-        <v>-112.74</v>
+        <v>94.03</v>
       </c>
       <c r="L76" t="n">
-        <v>140.14</v>
+        <v>111.45</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:17:41</t>
+          <t>10:19:53</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.13</v>
+        <v>6.03</v>
       </c>
       <c r="F77" t="n">
-        <v>10.86</v>
+        <v>14.6</v>
       </c>
       <c r="G77" t="n">
-        <v>95.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>65.2</v>
+        <v>73</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-20.85</v>
+        <v>157.72</v>
       </c>
       <c r="K77" t="n">
-        <v>-54.11</v>
+        <v>-36.87</v>
       </c>
       <c r="L77" t="n">
-        <v>57.99</v>
+        <v>161.98</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:18:43</t>
+          <t>10:21:17</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.68</v>
+        <v>5.06</v>
       </c>
       <c r="F78" t="n">
-        <v>14.6</v>
+        <v>14.37</v>
       </c>
       <c r="G78" t="n">
-        <v>85.5</v>
+        <v>67.2</v>
       </c>
       <c r="H78" t="n">
-        <v>42.6</v>
+        <v>61.5</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J78" t="n">
-        <v>95</v>
+        <v>159.75</v>
       </c>
       <c r="K78" t="n">
-        <v>-63.73</v>
+        <v>-50.41</v>
       </c>
       <c r="L78" t="n">
-        <v>114.39</v>
+        <v>167.52</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:20:43</t>
+          <t>10:23:35</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.64</v>
+        <v>4.53</v>
       </c>
       <c r="F79" t="n">
-        <v>14.17</v>
+        <v>14.6</v>
       </c>
       <c r="G79" t="n">
-        <v>87.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="H79" t="n">
-        <v>73.09999999999999</v>
+        <v>37.4</v>
       </c>
       <c r="I79" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-70.16</v>
+        <v>77.11</v>
       </c>
       <c r="K79" t="n">
-        <v>-97.5</v>
+        <v>-100.24</v>
       </c>
       <c r="L79" t="n">
-        <v>120.11</v>
+        <v>126.47</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:24:17</t>
+          <t>10:28:50</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.79</v>
+        <v>5.39</v>
       </c>
       <c r="F80" t="n">
-        <v>11.82</v>
+        <v>12.16</v>
       </c>
       <c r="G80" t="n">
-        <v>82</v>
+        <v>80.3</v>
       </c>
       <c r="H80" t="n">
-        <v>79.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J80" t="n">
-        <v>145.08</v>
+        <v>125.97</v>
       </c>
       <c r="K80" t="n">
-        <v>-17.78</v>
+        <v>220.84</v>
       </c>
       <c r="L80" t="n">
-        <v>146.17</v>
+        <v>254.25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:25:56</t>
+          <t>10:30:28</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>5.7</v>
+        <v>5.64</v>
       </c>
       <c r="F81" t="n">
-        <v>14.45</v>
+        <v>14.6</v>
       </c>
       <c r="G81" t="n">
-        <v>100.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H81" t="n">
-        <v>57</v>
+        <v>85.3</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>171.7</v>
+        <v>-129.45</v>
       </c>
       <c r="K81" t="n">
-        <v>-87.5</v>
+        <v>143.99</v>
       </c>
       <c r="L81" t="n">
-        <v>192.71</v>
+        <v>193.62</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:27:49</t>
+          <t>10:32:32</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.01</v>
+        <v>5.48</v>
       </c>
       <c r="F82" t="n">
-        <v>13.29</v>
+        <v>14.6</v>
       </c>
       <c r="G82" t="n">
-        <v>82.40000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>71.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J82" t="n">
-        <v>213.46</v>
+        <v>-69.01000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-130.89</v>
+        <v>194.47</v>
       </c>
       <c r="L82" t="n">
-        <v>250.4</v>
+        <v>206.35</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:32:45</t>
+          <t>10:36:41</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.21</v>
+        <v>5.33</v>
       </c>
       <c r="F83" t="n">
-        <v>12.98</v>
+        <v>14.6</v>
       </c>
       <c r="G83" t="n">
-        <v>63.1</v>
+        <v>73</v>
       </c>
       <c r="H83" t="n">
-        <v>34.3</v>
+        <v>52.7</v>
       </c>
       <c r="I83" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>241.09</v>
+        <v>-305.36</v>
       </c>
       <c r="K83" t="n">
-        <v>162.4</v>
+        <v>43.68</v>
       </c>
       <c r="L83" t="n">
-        <v>290.69</v>
+        <v>308.46</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:34:49</t>
+          <t>10:37:54</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>5.4</v>
+        <v>6.12</v>
       </c>
       <c r="F84" t="n">
         <v>14.6</v>
       </c>
       <c r="G84" t="n">
-        <v>83.5</v>
+        <v>94</v>
       </c>
       <c r="H84" t="n">
-        <v>60.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-235.93</v>
+        <v>-405.58</v>
       </c>
       <c r="K84" t="n">
-        <v>163.71</v>
+        <v>22.68</v>
       </c>
       <c r="L84" t="n">
-        <v>287.17</v>
+        <v>406.21</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:36:30</t>
+          <t>10:39:02</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.43</v>
+        <v>5.33</v>
       </c>
       <c r="F85" t="n">
         <v>14.6</v>
       </c>
       <c r="G85" t="n">
-        <v>96.3</v>
+        <v>78.7</v>
       </c>
       <c r="H85" t="n">
-        <v>43.7</v>
+        <v>47.3</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-148.1</v>
+        <v>241.98</v>
       </c>
       <c r="K85" t="n">
-        <v>-333.36</v>
+        <v>149.35</v>
       </c>
       <c r="L85" t="n">
-        <v>364.78</v>
+        <v>284.36</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:42:01</t>
+          <t>10:45:12</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.6</v>
+        <v>4.41</v>
       </c>
       <c r="F86" t="n">
-        <v>13.68</v>
+        <v>11.69</v>
       </c>
       <c r="G86" t="n">
-        <v>65</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>50.5</v>
+        <v>23.3</v>
       </c>
       <c r="I86" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-23.78</v>
+        <v>68.08</v>
       </c>
       <c r="K86" t="n">
-        <v>-272.6</v>
+        <v>-164.95</v>
       </c>
       <c r="L86" t="n">
-        <v>273.64</v>
+        <v>178.45</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:44:07</t>
+          <t>10:47:29</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.65</v>
+        <v>4.59</v>
       </c>
       <c r="F87" t="n">
-        <v>14.6</v>
+        <v>12.36</v>
       </c>
       <c r="G87" t="n">
-        <v>75.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H87" t="n">
-        <v>73.8</v>
+        <v>55.6</v>
       </c>
       <c r="I87" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>443.81</v>
+        <v>-228.14</v>
       </c>
       <c r="K87" t="n">
-        <v>-113.42</v>
+        <v>-174.88</v>
       </c>
       <c r="L87" t="n">
-        <v>458.07</v>
+        <v>287.46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:46:21</t>
+          <t>10:49:43</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.18</v>
+        <v>5.27</v>
       </c>
       <c r="F88" t="n">
         <v>14.6</v>
       </c>
       <c r="G88" t="n">
-        <v>87.8</v>
+        <v>104.5</v>
       </c>
       <c r="H88" t="n">
-        <v>85.40000000000001</v>
+        <v>20.5</v>
       </c>
       <c r="I88" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>251.36</v>
+        <v>396.5</v>
       </c>
       <c r="K88" t="n">
-        <v>256.96</v>
+        <v>-19.41</v>
       </c>
       <c r="L88" t="n">
-        <v>359.46</v>
+        <v>396.97</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-29.xlsx
+++ b/output/2025-09-29.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-72.61</v>
+        <v>-75.90000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>50.78</v>
+        <v>53.08</v>
       </c>
       <c r="L14" t="n">
-        <v>88.59999999999999</v>
+        <v>92.62</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-46.21</v>
+        <v>-57.29</v>
       </c>
       <c r="K15" t="n">
-        <v>24.41</v>
+        <v>30.27</v>
       </c>
       <c r="L15" t="n">
-        <v>52.26</v>
+        <v>64.79000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>88.06999999999999</v>
+        <v>95.12</v>
       </c>
       <c r="K16" t="n">
-        <v>-30.5</v>
+        <v>-32.94</v>
       </c>
       <c r="L16" t="n">
-        <v>93.20999999999999</v>
+        <v>100.67</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-29.69</v>
+        <v>-33.14</v>
       </c>
       <c r="K17" t="n">
-        <v>-89.92</v>
+        <v>-100.36</v>
       </c>
       <c r="L17" t="n">
-        <v>94.69</v>
+        <v>105.69</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-85.92</v>
+        <v>-96.63</v>
       </c>
       <c r="K18" t="n">
-        <v>-40.66</v>
+        <v>-45.73</v>
       </c>
       <c r="L18" t="n">
-        <v>95.06</v>
+        <v>106.9</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>125.7</v>
+        <v>130.06</v>
       </c>
       <c r="K19" t="n">
-        <v>46.3</v>
+        <v>47.9</v>
       </c>
       <c r="L19" t="n">
-        <v>133.95</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>32.19</v>
+        <v>39.29</v>
       </c>
       <c r="K20" t="n">
-        <v>-109.83</v>
+        <v>-134.07</v>
       </c>
       <c r="L20" t="n">
-        <v>114.45</v>
+        <v>139.71</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>101.44</v>
+        <v>120.06</v>
       </c>
       <c r="K21" t="n">
-        <v>113.59</v>
+        <v>134.43</v>
       </c>
       <c r="L21" t="n">
-        <v>152.29</v>
+        <v>180.24</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-74.23999999999999</v>
+        <v>-94.7</v>
       </c>
       <c r="K22" t="n">
-        <v>-88.56999999999999</v>
+        <v>-112.98</v>
       </c>
       <c r="L22" t="n">
-        <v>115.57</v>
+        <v>147.42</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>15.81</v>
+        <v>18.65</v>
       </c>
       <c r="K23" t="n">
-        <v>183.28</v>
+        <v>216.1</v>
       </c>
       <c r="L23" t="n">
-        <v>183.96</v>
+        <v>216.9</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>159.61</v>
+        <v>198.94</v>
       </c>
       <c r="K24" t="n">
-        <v>-40.6</v>
+        <v>-50.61</v>
       </c>
       <c r="L24" t="n">
-        <v>164.69</v>
+        <v>205.27</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>107.15</v>
+        <v>143.48</v>
       </c>
       <c r="K25" t="n">
-        <v>153.42</v>
+        <v>205.45</v>
       </c>
       <c r="L25" t="n">
-        <v>187.13</v>
+        <v>250.59</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.57</v>
+        <v>-6.17</v>
       </c>
       <c r="K26" t="n">
-        <v>178.88</v>
+        <v>241.74</v>
       </c>
       <c r="L26" t="n">
-        <v>178.94</v>
+        <v>241.82</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-235.3</v>
+        <v>-299.61</v>
       </c>
       <c r="K27" t="n">
-        <v>159.01</v>
+        <v>202.46</v>
       </c>
       <c r="L27" t="n">
-        <v>283.99</v>
+        <v>361.6</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>189.81</v>
+        <v>257.67</v>
       </c>
       <c r="K28" t="n">
-        <v>-178.28</v>
+        <v>-242.02</v>
       </c>
       <c r="L28" t="n">
-        <v>260.4</v>
+        <v>353.51</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>36.87</v>
+        <v>45.53</v>
       </c>
       <c r="K29" t="n">
-        <v>35.55</v>
+        <v>43.91</v>
       </c>
       <c r="L29" t="n">
-        <v>51.22</v>
+        <v>63.26</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>54.39</v>
+        <v>61.69</v>
       </c>
       <c r="K30" t="n">
-        <v>-51.83</v>
+        <v>-58.78</v>
       </c>
       <c r="L30" t="n">
-        <v>75.13</v>
+        <v>85.20999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>23.76</v>
+        <v>29.76</v>
       </c>
       <c r="K31" t="n">
-        <v>-40.87</v>
+        <v>-51.18</v>
       </c>
       <c r="L31" t="n">
-        <v>47.28</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-22.33</v>
+        <v>-25.3</v>
       </c>
       <c r="K32" t="n">
-        <v>74.20999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>77.48999999999999</v>
+        <v>87.81999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-65.28</v>
+        <v>-81.18000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>3.48</v>
+        <v>4.33</v>
       </c>
       <c r="L33" t="n">
-        <v>65.37</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>18.29</v>
+        <v>22.14</v>
       </c>
       <c r="K34" t="n">
-        <v>66.47</v>
+        <v>80.44</v>
       </c>
       <c r="L34" t="n">
-        <v>68.94</v>
+        <v>83.43000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-85.34</v>
+        <v>-107.06</v>
       </c>
       <c r="K35" t="n">
-        <v>-67.48</v>
+        <v>-84.66</v>
       </c>
       <c r="L35" t="n">
-        <v>108.8</v>
+        <v>136.49</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>3.18</v>
+        <v>3.87</v>
       </c>
       <c r="K36" t="n">
-        <v>-122.67</v>
+        <v>-149.66</v>
       </c>
       <c r="L36" t="n">
-        <v>122.71</v>
+        <v>149.71</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-133.49</v>
+        <v>-156.81</v>
       </c>
       <c r="K37" t="n">
-        <v>66.22</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>149.01</v>
+        <v>175.04</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>160.08</v>
+        <v>214.01</v>
       </c>
       <c r="K38" t="n">
-        <v>-31.57</v>
+        <v>-42.2</v>
       </c>
       <c r="L38" t="n">
-        <v>163.16</v>
+        <v>218.13</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>26.71</v>
+        <v>34.47</v>
       </c>
       <c r="K39" t="n">
-        <v>166.09</v>
+        <v>214.36</v>
       </c>
       <c r="L39" t="n">
-        <v>168.23</v>
+        <v>217.11</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>49.75</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>213.38</v>
+        <v>274.92</v>
       </c>
       <c r="L40" t="n">
-        <v>219.1</v>
+        <v>282.29</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-66.06999999999999</v>
+        <v>-97.97</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.21</v>
+        <v>-4.75</v>
       </c>
       <c r="L41" t="n">
-        <v>66.15000000000001</v>
+        <v>98.08</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>269.56</v>
+        <v>392.75</v>
       </c>
       <c r="K42" t="n">
-        <v>-117.77</v>
+        <v>-171.59</v>
       </c>
       <c r="L42" t="n">
-        <v>294.16</v>
+        <v>428.59</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>95.31999999999999</v>
+        <v>137.14</v>
       </c>
       <c r="K43" t="n">
-        <v>190.05</v>
+        <v>273.42</v>
       </c>
       <c r="L43" t="n">
-        <v>212.61</v>
+        <v>305.89</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-60.45</v>
+        <v>-65.31</v>
       </c>
       <c r="K44" t="n">
-        <v>62.49</v>
+        <v>67.52</v>
       </c>
       <c r="L44" t="n">
-        <v>86.94</v>
+        <v>93.94</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>64.94</v>
+        <v>71.8</v>
       </c>
       <c r="K45" t="n">
-        <v>-32.48</v>
+        <v>-35.92</v>
       </c>
       <c r="L45" t="n">
-        <v>72.61</v>
+        <v>80.28</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-54.99</v>
+        <v>-64.29000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>24.96</v>
+        <v>29.18</v>
       </c>
       <c r="L46" t="n">
-        <v>60.39</v>
+        <v>70.61</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-95.38</v>
+        <v>-103.95</v>
       </c>
       <c r="K47" t="n">
-        <v>14.44</v>
+        <v>15.74</v>
       </c>
       <c r="L47" t="n">
-        <v>96.47</v>
+        <v>105.13</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-8.19</v>
+        <v>-9.32</v>
       </c>
       <c r="K48" t="n">
-        <v>-89.66</v>
+        <v>-102.03</v>
       </c>
       <c r="L48" t="n">
-        <v>90.03</v>
+        <v>102.45</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-26.3</v>
+        <v>-29.35</v>
       </c>
       <c r="K49" t="n">
-        <v>83.92</v>
+        <v>93.62</v>
       </c>
       <c r="L49" t="n">
-        <v>87.94</v>
+        <v>98.11</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-54.11</v>
+        <v>-70.90000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>-79.59</v>
+        <v>-104.3</v>
       </c>
       <c r="L50" t="n">
-        <v>96.23999999999999</v>
+        <v>126.12</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.92</v>
+        <v>-10.4</v>
       </c>
       <c r="K51" t="n">
-        <v>95.01000000000001</v>
+        <v>124.75</v>
       </c>
       <c r="L51" t="n">
-        <v>95.34</v>
+        <v>125.18</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>40.97</v>
+        <v>55.56</v>
       </c>
       <c r="K52" t="n">
-        <v>-92.09999999999999</v>
+        <v>-124.89</v>
       </c>
       <c r="L52" t="n">
-        <v>100.8</v>
+        <v>136.69</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>78.26000000000001</v>
+        <v>114.52</v>
       </c>
       <c r="K53" t="n">
-        <v>120.51</v>
+        <v>176.33</v>
       </c>
       <c r="L53" t="n">
-        <v>143.69</v>
+        <v>210.25</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>104.44</v>
+        <v>127.72</v>
       </c>
       <c r="K54" t="n">
-        <v>-295.83</v>
+        <v>-361.77</v>
       </c>
       <c r="L54" t="n">
-        <v>313.72</v>
+        <v>383.65</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>-149.78</v>
+        <v>-183.78</v>
       </c>
       <c r="K55" t="n">
-        <v>-80.95</v>
+        <v>-99.31999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>170.26</v>
+        <v>208.91</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>366.47</v>
+        <v>472.2</v>
       </c>
       <c r="K56" t="n">
-        <v>223.67</v>
+        <v>288.19</v>
       </c>
       <c r="L56" t="n">
-        <v>429.34</v>
+        <v>553.1900000000001</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-170.75</v>
+        <v>-249.24</v>
       </c>
       <c r="K57" t="n">
-        <v>195.64</v>
+        <v>285.57</v>
       </c>
       <c r="L57" t="n">
-        <v>259.67</v>
+        <v>379.04</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>1.52</v>
+        <v>2.21</v>
       </c>
       <c r="K58" t="n">
-        <v>-214.4</v>
+        <v>-311.71</v>
       </c>
       <c r="L58" t="n">
-        <v>214.41</v>
+        <v>311.72</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>72.15000000000001</v>
+        <v>78.25</v>
       </c>
       <c r="K59" t="n">
-        <v>-57.88</v>
+        <v>-62.77</v>
       </c>
       <c r="L59" t="n">
-        <v>92.5</v>
+        <v>100.31</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-77.06</v>
+        <v>-86.26000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>-34.21</v>
+        <v>-38.29</v>
       </c>
       <c r="L60" t="n">
-        <v>84.31</v>
+        <v>94.37</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-28.78</v>
+        <v>-31.73</v>
       </c>
       <c r="K61" t="n">
-        <v>76.92</v>
+        <v>84.81</v>
       </c>
       <c r="L61" t="n">
-        <v>82.13</v>
+        <v>90.55</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>30.64</v>
+        <v>34.69</v>
       </c>
       <c r="K62" t="n">
-        <v>78.55</v>
+        <v>88.91</v>
       </c>
       <c r="L62" t="n">
-        <v>84.31999999999999</v>
+        <v>95.44</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-77.33</v>
+        <v>-82.67</v>
       </c>
       <c r="K63" t="n">
-        <v>96.09</v>
+        <v>102.73</v>
       </c>
       <c r="L63" t="n">
-        <v>123.35</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-118.77</v>
+        <v>-137.79</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.8</v>
+        <v>-2.09</v>
       </c>
       <c r="L64" t="n">
-        <v>118.78</v>
+        <v>137.81</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>190.75</v>
+        <v>225.13</v>
       </c>
       <c r="K65" t="n">
-        <v>-112.52</v>
+        <v>-132.81</v>
       </c>
       <c r="L65" t="n">
-        <v>221.46</v>
+        <v>261.39</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>97.94</v>
+        <v>124.96</v>
       </c>
       <c r="K66" t="n">
-        <v>-71.89</v>
+        <v>-91.70999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>121.49</v>
+        <v>155</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-130.18</v>
+        <v>-163.29</v>
       </c>
       <c r="K67" t="n">
-        <v>30.32</v>
+        <v>38.03</v>
       </c>
       <c r="L67" t="n">
-        <v>133.67</v>
+        <v>167.66</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-119.24</v>
+        <v>-168.12</v>
       </c>
       <c r="K68" t="n">
-        <v>-66.20999999999999</v>
+        <v>-93.36</v>
       </c>
       <c r="L68" t="n">
-        <v>136.39</v>
+        <v>192.3</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>247.03</v>
+        <v>326.11</v>
       </c>
       <c r="K69" t="n">
-        <v>44.47</v>
+        <v>58.71</v>
       </c>
       <c r="L69" t="n">
-        <v>251</v>
+        <v>331.35</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>138.03</v>
+        <v>197.79</v>
       </c>
       <c r="K70" t="n">
-        <v>-30.25</v>
+        <v>-43.35</v>
       </c>
       <c r="L70" t="n">
-        <v>141.31</v>
+        <v>202.49</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>308.29</v>
+        <v>447.89</v>
       </c>
       <c r="K71" t="n">
-        <v>-39.6</v>
+        <v>-57.54</v>
       </c>
       <c r="L71" t="n">
-        <v>310.82</v>
+        <v>451.57</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-219.06</v>
+        <v>-324.06</v>
       </c>
       <c r="K72" t="n">
-        <v>140.49</v>
+        <v>207.83</v>
       </c>
       <c r="L72" t="n">
-        <v>260.24</v>
+        <v>384.98</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>69.34</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="K73" t="n">
-        <v>-249.41</v>
+        <v>-359.03</v>
       </c>
       <c r="L73" t="n">
-        <v>258.87</v>
+        <v>372.65</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>33.71</v>
+        <v>40.18</v>
       </c>
       <c r="K74" t="n">
-        <v>-46.16</v>
+        <v>-55.03</v>
       </c>
       <c r="L74" t="n">
-        <v>57.16</v>
+        <v>68.14</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-58.9</v>
+        <v>-65.63</v>
       </c>
       <c r="K75" t="n">
-        <v>-62.41</v>
+        <v>-69.54000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>85.81</v>
+        <v>95.62</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>43.66</v>
+        <v>51.71</v>
       </c>
       <c r="K76" t="n">
-        <v>35.68</v>
+        <v>42.26</v>
       </c>
       <c r="L76" t="n">
-        <v>56.38</v>
+        <v>66.78</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>19.3</v>
+        <v>21.92</v>
       </c>
       <c r="K77" t="n">
-        <v>108.98</v>
+        <v>123.76</v>
       </c>
       <c r="L77" t="n">
-        <v>110.67</v>
+        <v>125.69</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-20.52</v>
+        <v>-25.52</v>
       </c>
       <c r="K78" t="n">
-        <v>59.19</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>62.65</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-43.18</v>
+        <v>-52.94</v>
       </c>
       <c r="K79" t="n">
-        <v>56.26</v>
+        <v>68.97</v>
       </c>
       <c r="L79" t="n">
-        <v>70.92</v>
+        <v>86.94</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>173.8</v>
+        <v>206.52</v>
       </c>
       <c r="K80" t="n">
-        <v>-76.04000000000001</v>
+        <v>-90.36</v>
       </c>
       <c r="L80" t="n">
-        <v>189.71</v>
+        <v>225.43</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>-112.69</v>
+        <v>-143.44</v>
       </c>
       <c r="K81" t="n">
-        <v>-18.23</v>
+        <v>-23.2</v>
       </c>
       <c r="L81" t="n">
-        <v>114.16</v>
+        <v>145.3</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-136.66</v>
+        <v>-173.1</v>
       </c>
       <c r="K82" t="n">
-        <v>-56.16</v>
+        <v>-71.14</v>
       </c>
       <c r="L82" t="n">
-        <v>147.75</v>
+        <v>187.14</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-197.34</v>
+        <v>-271.54</v>
       </c>
       <c r="K83" t="n">
-        <v>-170.92</v>
+        <v>-235.18</v>
       </c>
       <c r="L83" t="n">
-        <v>261.07</v>
+        <v>359.23</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-45.66</v>
+        <v>-64.36</v>
       </c>
       <c r="K84" t="n">
-        <v>-123.48</v>
+        <v>-174.06</v>
       </c>
       <c r="L84" t="n">
-        <v>131.65</v>
+        <v>185.58</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>132.95</v>
+        <v>186.18</v>
       </c>
       <c r="K85" t="n">
-        <v>-97.09999999999999</v>
+        <v>-135.98</v>
       </c>
       <c r="L85" t="n">
-        <v>164.63</v>
+        <v>230.55</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-216.98</v>
+        <v>-317.78</v>
       </c>
       <c r="K86" t="n">
-        <v>210.72</v>
+        <v>308.62</v>
       </c>
       <c r="L86" t="n">
-        <v>302.46</v>
+        <v>442.98</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>197.09</v>
+        <v>280.22</v>
       </c>
       <c r="K87" t="n">
-        <v>204.73</v>
+        <v>291.07</v>
       </c>
       <c r="L87" t="n">
-        <v>284.18</v>
+        <v>404.04</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>-19.65</v>
+        <v>-27.38</v>
       </c>
       <c r="K88" t="n">
-        <v>-286.46</v>
+        <v>-399.07</v>
       </c>
       <c r="L88" t="n">
-        <v>287.14</v>
+        <v>400.01</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-29.xlsx
+++ b/output/2025-09-29.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-75.90000000000001</v>
+        <v>-98.89</v>
       </c>
       <c r="K14" t="n">
-        <v>53.08</v>
+        <v>69.16</v>
       </c>
       <c r="L14" t="n">
-        <v>92.62</v>
+        <v>120.68</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-57.29</v>
+        <v>-87.48999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>30.27</v>
+        <v>46.23</v>
       </c>
       <c r="L15" t="n">
-        <v>64.79000000000001</v>
+        <v>98.95999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>95.12</v>
+        <v>131.35</v>
       </c>
       <c r="K16" t="n">
-        <v>-32.94</v>
+        <v>-45.49</v>
       </c>
       <c r="L16" t="n">
-        <v>100.67</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-33.14</v>
+        <v>-41.07</v>
       </c>
       <c r="K17" t="n">
-        <v>-100.36</v>
+        <v>-124.36</v>
       </c>
       <c r="L17" t="n">
-        <v>105.69</v>
+        <v>130.96</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-96.63</v>
+        <v>-121.78</v>
       </c>
       <c r="K18" t="n">
-        <v>-45.73</v>
+        <v>-57.63</v>
       </c>
       <c r="L18" t="n">
-        <v>106.9</v>
+        <v>134.73</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>130.06</v>
+        <v>152.2</v>
       </c>
       <c r="K19" t="n">
-        <v>47.9</v>
+        <v>56.06</v>
       </c>
       <c r="L19" t="n">
-        <v>138.6</v>
+        <v>162.2</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>45.53</v>
+        <v>64.38</v>
       </c>
       <c r="K29" t="n">
-        <v>43.91</v>
+        <v>62.08</v>
       </c>
       <c r="L29" t="n">
-        <v>63.26</v>
+        <v>89.44</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>61.69</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-58.78</v>
+        <v>-86.56999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>85.20999999999999</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>29.76</v>
+        <v>43.66</v>
       </c>
       <c r="K31" t="n">
-        <v>-51.18</v>
+        <v>-75.08</v>
       </c>
       <c r="L31" t="n">
-        <v>59.2</v>
+        <v>86.84999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-25.3</v>
+        <v>-31.06</v>
       </c>
       <c r="K32" t="n">
-        <v>84.09999999999999</v>
+        <v>103.24</v>
       </c>
       <c r="L32" t="n">
-        <v>87.81999999999999</v>
+        <v>107.82</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-81.18000000000001</v>
+        <v>-109.09</v>
       </c>
       <c r="K33" t="n">
-        <v>4.33</v>
+        <v>5.82</v>
       </c>
       <c r="L33" t="n">
-        <v>81.3</v>
+        <v>109.25</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>22.14</v>
+        <v>30.56</v>
       </c>
       <c r="K34" t="n">
-        <v>80.44</v>
+        <v>111.06</v>
       </c>
       <c r="L34" t="n">
-        <v>83.43000000000001</v>
+        <v>115.19</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-65.31</v>
+        <v>-87</v>
       </c>
       <c r="K44" t="n">
-        <v>67.52</v>
+        <v>89.95</v>
       </c>
       <c r="L44" t="n">
-        <v>93.94</v>
+        <v>125.14</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>71.8</v>
+        <v>100.13</v>
       </c>
       <c r="K45" t="n">
-        <v>-35.92</v>
+        <v>-50.09</v>
       </c>
       <c r="L45" t="n">
-        <v>80.28</v>
+        <v>111.96</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-64.29000000000001</v>
+        <v>-85.98999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>29.18</v>
+        <v>39.03</v>
       </c>
       <c r="L46" t="n">
-        <v>70.61</v>
+        <v>94.43000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-103.95</v>
+        <v>-133.24</v>
       </c>
       <c r="K47" t="n">
-        <v>15.74</v>
+        <v>20.17</v>
       </c>
       <c r="L47" t="n">
-        <v>105.13</v>
+        <v>134.76</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-9.32</v>
+        <v>-12.04</v>
       </c>
       <c r="K48" t="n">
-        <v>-102.03</v>
+        <v>-131.78</v>
       </c>
       <c r="L48" t="n">
-        <v>102.45</v>
+        <v>132.33</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-29.35</v>
+        <v>-37.04</v>
       </c>
       <c r="K49" t="n">
-        <v>93.62</v>
+        <v>118.18</v>
       </c>
       <c r="L49" t="n">
-        <v>98.11</v>
+        <v>123.85</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>78.25</v>
+        <v>119.73</v>
       </c>
       <c r="K59" t="n">
-        <v>-62.77</v>
+        <v>-96.04000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>100.31</v>
+        <v>153.49</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-86.26000000000001</v>
+        <v>-131.98</v>
       </c>
       <c r="K60" t="n">
-        <v>-38.29</v>
+        <v>-58.59</v>
       </c>
       <c r="L60" t="n">
-        <v>94.37</v>
+        <v>144.4</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-31.73</v>
+        <v>-49.65</v>
       </c>
       <c r="K61" t="n">
-        <v>84.81</v>
+        <v>132.72</v>
       </c>
       <c r="L61" t="n">
-        <v>90.55</v>
+        <v>141.71</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>34.69</v>
+        <v>43.99</v>
       </c>
       <c r="K62" t="n">
-        <v>88.91</v>
+        <v>112.75</v>
       </c>
       <c r="L62" t="n">
-        <v>95.44</v>
+        <v>121.03</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-82.67</v>
+        <v>-98.40000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>102.73</v>
+        <v>122.27</v>
       </c>
       <c r="L63" t="n">
-        <v>131.86</v>
+        <v>156.95</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-137.79</v>
+        <v>-202.73</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.09</v>
+        <v>-3.08</v>
       </c>
       <c r="L64" t="n">
-        <v>137.81</v>
+        <v>202.75</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>40.18</v>
+        <v>59.87</v>
       </c>
       <c r="K74" t="n">
-        <v>-55.03</v>
+        <v>-81.98</v>
       </c>
       <c r="L74" t="n">
-        <v>68.14</v>
+        <v>101.52</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-65.63</v>
+        <v>-98.90000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>-69.54000000000001</v>
+        <v>-104.8</v>
       </c>
       <c r="L75" t="n">
-        <v>95.62</v>
+        <v>144.1</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>51.71</v>
+        <v>77.34</v>
       </c>
       <c r="K76" t="n">
-        <v>42.26</v>
+        <v>63.2</v>
       </c>
       <c r="L76" t="n">
-        <v>66.78</v>
+        <v>99.88</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>21.92</v>
+        <v>32.2</v>
       </c>
       <c r="K77" t="n">
-        <v>123.76</v>
+        <v>181.82</v>
       </c>
       <c r="L77" t="n">
-        <v>125.69</v>
+        <v>184.65</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-25.52</v>
+        <v>-34.24</v>
       </c>
       <c r="K78" t="n">
-        <v>73.59999999999999</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>77.90000000000001</v>
+        <v>104.53</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-52.94</v>
+        <v>-73.09</v>
       </c>
       <c r="K79" t="n">
-        <v>68.97</v>
+        <v>95.22</v>
       </c>
       <c r="L79" t="n">
-        <v>86.94</v>
+        <v>120.04</v>
       </c>
     </row>
     <row r="80">
